--- a/diseases/d007/2026-2029.xlsx
+++ b/diseases/d007/2026-2029.xlsx
@@ -76001,13 +76001,13 @@
         </is>
       </c>
       <c r="N406" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O406" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="R406" t="n">
-        <v>0.2480601502453819</v>
+        <v>0.2499981201691739</v>
       </c>
       <c r="S406" t="inlineStr">
         <is>
@@ -76510,12 +76510,12 @@
       </c>
       <c r="F409" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G409" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H409" t="inlineStr">
@@ -76549,13 +76549,13 @@
         </is>
       </c>
       <c r="N409" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="O409" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="R409" t="n">
-        <v>0.05649400180367965</v>
+        <v>0.1868976085656669</v>
       </c>
       <c r="S409" t="inlineStr">
         <is>
@@ -76564,7 +76564,7 @@
       </c>
       <c r="U409" t="inlineStr">
         <is>
-          <t>SER_TW_HEPATITIS_A_0701</t>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_A</t>
         </is>
       </c>
       <c r="AA409" t="inlineStr">
@@ -76579,7 +76579,7 @@
       </c>
       <c r="AP409" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ409" t="inlineStr">
@@ -76587,57 +76587,62 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR409" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS409" t="inlineStr">
         <is>
-          <t>SER_TW_HEPATITIS_A_0701</t>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_A</t>
         </is>
       </c>
       <c r="AT409" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU409" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV409" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW409" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX409" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY409" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ409" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA409" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB409" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC409" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -76669,12 +76674,12 @@
       </c>
       <c r="F410" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G410" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H410" t="inlineStr">
@@ -76708,29 +76713,29 @@
         </is>
       </c>
       <c r="N410" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="O410" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="U410" t="inlineStr">
         <is>
-          <t>SER_TW_HEPATITIS_A_0701</t>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_A</t>
         </is>
       </c>
       <c r="V410" t="inlineStr">
         <is>
-          <t>SER_TW_HEPATITIS_A_0701</t>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_A</t>
         </is>
       </c>
       <c r="W410" t="inlineStr">
         <is>
-          <t>SRC_TW_NIDSS</t>
+          <t>SRC_SE_FOHM_SMINET</t>
         </is>
       </c>
       <c r="X410" t="inlineStr">
         <is>
-          <t>急性病毒性Ａ型肝炎</t>
+          <t>Hepatit A</t>
         </is>
       </c>
       <c r="Y410" t="inlineStr">
@@ -76740,7 +76745,7 @@
       </c>
       <c r="Z410" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA410" t="inlineStr">
@@ -76755,7 +76760,7 @@
       </c>
       <c r="AC410" t="inlineStr">
         <is>
-          <t>country:TW:national</t>
+          <t>country:SE:national</t>
         </is>
       </c>
       <c r="AD410" t="inlineStr">
@@ -76770,7 +76775,7 @@
       </c>
       <c r="AF410" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>conditional</t>
         </is>
       </c>
       <c r="AG410" t="inlineStr">
@@ -76790,17 +76795,17 @@
       </c>
       <c r="AJ410" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>SE_FOHM_SMINET_current</t>
         </is>
       </c>
       <c r="AK410" t="inlineStr">
         <is>
-          <t>Acute hepatitis A, code 0701. D067 remains deprecated.</t>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
         </is>
       </c>
       <c r="AM410" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>revised</t>
         </is>
       </c>
       <c r="AN410" t="b">
@@ -76813,7 +76818,7 @@
       </c>
       <c r="AP410" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ410" t="inlineStr">
@@ -76821,57 +76826,62 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR410" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS410" t="inlineStr">
         <is>
-          <t>SER_TW_HEPATITIS_A_0701</t>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_A</t>
         </is>
       </c>
       <c r="AT410" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU410" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV410" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW410" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX410" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY410" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ410" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA410" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB410" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC410" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -76903,12 +76913,12 @@
       </c>
       <c r="F411" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G411" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H411" t="inlineStr">
@@ -76942,16 +76952,13 @@
         </is>
       </c>
       <c r="N411" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="O411" t="n">
-        <v>2</v>
-      </c>
-      <c r="P411" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="R411" t="n">
-        <v>0.0005730076265538771</v>
+        <v>0.05649400180367965</v>
       </c>
       <c r="S411" t="inlineStr">
         <is>
@@ -76960,17 +76967,17 @@
       </c>
       <c r="U411" t="inlineStr">
         <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+          <t>SER_TW_HEPATITIS_A_0701</t>
         </is>
       </c>
       <c r="AA411" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO411" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP411" t="inlineStr">
@@ -76980,12 +76987,12 @@
       </c>
       <c r="AQ411" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS411" t="inlineStr">
         <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+          <t>SER_TW_HEPATITIS_A_0701</t>
         </is>
       </c>
       <c r="AT411" t="n">
@@ -76993,47 +77000,47 @@
       </c>
       <c r="AU411" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV411" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW411" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX411" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY411" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ411" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA411" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB411" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC411" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -77065,12 +77072,12 @@
       </c>
       <c r="F412" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G412" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H412" t="inlineStr">
@@ -77104,32 +77111,29 @@
         </is>
       </c>
       <c r="N412" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="O412" t="n">
-        <v>2</v>
-      </c>
-      <c r="P412" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="U412" t="inlineStr">
         <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+          <t>SER_TW_HEPATITIS_A_0701</t>
         </is>
       </c>
       <c r="V412" t="inlineStr">
         <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+          <t>SER_TW_HEPATITIS_A_0701</t>
         </is>
       </c>
       <c r="W412" t="inlineStr">
         <is>
-          <t>SRC_US_NNDSS</t>
+          <t>SRC_TW_NIDSS</t>
         </is>
       </c>
       <c r="X412" t="inlineStr">
         <is>
-          <t>Hepatitis A, Confirmed</t>
+          <t>急性病毒性Ａ型肝炎</t>
         </is>
       </c>
       <c r="Y412" t="inlineStr">
@@ -77144,7 +77148,7 @@
       </c>
       <c r="AA412" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AB412" t="inlineStr">
@@ -77154,7 +77158,7 @@
       </c>
       <c r="AC412" t="inlineStr">
         <is>
-          <t>country:US:national</t>
+          <t>country:TW:national</t>
         </is>
       </c>
       <c r="AD412" t="inlineStr">
@@ -77194,12 +77198,12 @@
       </c>
       <c r="AK412" t="inlineStr">
         <is>
-          <t>Confirmed hepatitis A component reported by NNDSS.</t>
+          <t>Acute hepatitis A, code 0701. D067 remains deprecated.</t>
         </is>
       </c>
       <c r="AM412" t="inlineStr">
         <is>
-          <t>provisional</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN412" t="b">
@@ -77207,7 +77211,7 @@
       </c>
       <c r="AO412" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP412" t="inlineStr">
@@ -77217,12 +77221,12 @@
       </c>
       <c r="AQ412" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS412" t="inlineStr">
         <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+          <t>SER_TW_HEPATITIS_A_0701</t>
         </is>
       </c>
       <c r="AT412" t="n">
@@ -77230,47 +77234,47 @@
       </c>
       <c r="AU412" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV412" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW412" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX412" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY412" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ412" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA412" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB412" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC412" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -77302,12 +77306,12 @@
       </c>
       <c r="F413" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G413" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H413" t="inlineStr">
@@ -77332,7 +77336,7 @@
       </c>
       <c r="L413" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M413" t="inlineStr">
@@ -77341,81 +77345,98 @@
         </is>
       </c>
       <c r="N413" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="O413" t="n">
-        <v>14</v>
+        <v>2</v>
+      </c>
+      <c r="P413" t="n">
+        <v>2</v>
       </c>
       <c r="R413" t="n">
-        <v>0.01143531770592073</v>
+        <v>0.0005730076265538771</v>
       </c>
       <c r="S413" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U413" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AA413" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO413" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP413" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR413" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS413" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ413" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS413" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
       <c r="AT413" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU413" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV413" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW413" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX413" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY413" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ413" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA413" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB413" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC413" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -77442,17 +77463,17 @@
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F414" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G414" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H414" t="inlineStr">
@@ -77477,7 +77498,7 @@
       </c>
       <c r="L414" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M414" t="inlineStr">
@@ -77486,93 +77507,173 @@
         </is>
       </c>
       <c r="N414" t="n">
+        <v>2</v>
+      </c>
+      <c r="O414" t="n">
+        <v>2</v>
+      </c>
+      <c r="P414" t="n">
+        <v>2</v>
+      </c>
+      <c r="U414" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="V414" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="W414" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X414" t="inlineStr">
+        <is>
+          <t>Hepatitis A, Confirmed</t>
+        </is>
+      </c>
+      <c r="Y414" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z414" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA414" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB414" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC414" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD414" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE414" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF414" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG414" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH414" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI414" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ414" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK414" t="inlineStr">
+        <is>
+          <t>Confirmed hepatitis A component reported by NNDSS.</t>
+        </is>
+      </c>
+      <c r="AM414" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN414" t="b">
         <v>1</v>
       </c>
-      <c r="O414" t="n">
+      <c r="AO414" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP414" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ414" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS414" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AT414" t="n">
         <v>1</v>
       </c>
-      <c r="P414" t="n">
-        <v>1</v>
-      </c>
-      <c r="R414" t="n">
-        <v>0.01693265755097047</v>
-      </c>
-      <c r="S414" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AA414" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AO414" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP414" t="inlineStr">
-        <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ414" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS414" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_A</t>
-        </is>
-      </c>
-      <c r="AT414" t="n">
-        <v>2</v>
-      </c>
       <c r="AU414" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV414" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW414" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX414" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY414" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ414" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA414" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB414" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC414" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -77599,17 +77700,17 @@
       </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F415" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G415" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H415" t="inlineStr">
@@ -77643,173 +77744,81 @@
         </is>
       </c>
       <c r="N415" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="O415" t="n">
-        <v>1</v>
-      </c>
-      <c r="P415" t="n">
-        <v>1</v>
-      </c>
-      <c r="U415" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A</t>
-        </is>
-      </c>
-      <c r="V415" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A</t>
-        </is>
-      </c>
-      <c r="W415" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X415" t="inlineStr">
-        <is>
-          <t>Acute Viral Hepatitis A</t>
-        </is>
-      </c>
-      <c r="Y415" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z415" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA415" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB415" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC415" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD415" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE415" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF415" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG415" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH415" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI415" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ415" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK415" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM415" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN415" t="b">
-        <v>1</v>
+        <v>14</v>
+      </c>
+      <c r="R415" t="n">
+        <v>0.01143531770592073</v>
+      </c>
+      <c r="S415" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO415" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP415" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ415" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS415" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_A</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR415" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS415" t="inlineStr"/>
       <c r="AT415" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU415" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV415" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW415" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX415" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY415" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ415" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA415" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB415" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC415" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -77841,12 +77850,12 @@
       </c>
       <c r="F416" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G416" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H416" t="inlineStr">
@@ -77871,7 +77880,7 @@
       </c>
       <c r="L416" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M416" t="inlineStr">
@@ -77880,27 +77889,22 @@
         </is>
       </c>
       <c r="N416" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="O416" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="P416" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="R416" t="n">
-        <v>0.001719022879661631</v>
+        <v>0.01693265755097047</v>
       </c>
       <c r="S416" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U416" t="inlineStr">
-        <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
-        </is>
-      </c>
       <c r="AA416" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -77908,70 +77912,70 @@
       </c>
       <c r="AO416" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP416" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ416" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS416" t="inlineStr">
         <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_A</t>
         </is>
       </c>
       <c r="AT416" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU416" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV416" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW416" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX416" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY416" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ416" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA416" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB416" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC416" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -78003,12 +78007,12 @@
       </c>
       <c r="F417" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G417" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H417" t="inlineStr">
@@ -78033,7 +78037,7 @@
       </c>
       <c r="L417" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M417" t="inlineStr">
@@ -78042,32 +78046,32 @@
         </is>
       </c>
       <c r="N417" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="O417" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="P417" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="U417" t="inlineStr">
         <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A</t>
         </is>
       </c>
       <c r="V417" t="inlineStr">
         <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A</t>
         </is>
       </c>
       <c r="W417" t="inlineStr">
         <is>
-          <t>SRC_US_NNDSS</t>
+          <t>SRC_SG_CDA_WIDB</t>
         </is>
       </c>
       <c r="X417" t="inlineStr">
         <is>
-          <t>Hepatitis A, Confirmed</t>
+          <t>Acute Viral Hepatitis A</t>
         </is>
       </c>
       <c r="Y417" t="inlineStr">
@@ -78077,7 +78081,7 @@
       </c>
       <c r="Z417" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA417" t="inlineStr">
@@ -78092,7 +78096,7 @@
       </c>
       <c r="AC417" t="inlineStr">
         <is>
-          <t>country:US:national</t>
+          <t>country:SG:national</t>
         </is>
       </c>
       <c r="AD417" t="inlineStr">
@@ -78107,7 +78111,7 @@
       </c>
       <c r="AF417" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>conditional</t>
         </is>
       </c>
       <c r="AG417" t="inlineStr">
@@ -78127,17 +78131,17 @@
       </c>
       <c r="AJ417" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
         </is>
       </c>
       <c r="AK417" t="inlineStr">
         <is>
-          <t>Confirmed hepatitis A component reported by NNDSS.</t>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
         </is>
       </c>
       <c r="AM417" t="inlineStr">
         <is>
-          <t>provisional</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN417" t="b">
@@ -78145,70 +78149,70 @@
       </c>
       <c r="AO417" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP417" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ417" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS417" t="inlineStr">
         <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_A</t>
         </is>
       </c>
       <c r="AT417" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU417" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV417" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW417" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX417" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY417" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ417" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA417" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB417" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC417" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -78240,12 +78244,12 @@
       </c>
       <c r="F418" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G418" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H418" t="inlineStr">
@@ -78270,7 +78274,7 @@
       </c>
       <c r="L418" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="M418" t="inlineStr">
@@ -78279,81 +78283,98 @@
         </is>
       </c>
       <c r="N418" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="O418" t="n">
-        <v>11</v>
+        <v>6</v>
+      </c>
+      <c r="P418" t="n">
+        <v>6</v>
       </c>
       <c r="R418" t="n">
-        <v>0.00898489248322343</v>
+        <v>0.001719022879661631</v>
       </c>
       <c r="S418" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U418" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AA418" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO418" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP418" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR418" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS418" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ418" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS418" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
       <c r="AT418" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU418" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV418" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW418" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX418" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY418" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ418" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA418" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB418" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC418" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -78380,17 +78401,17 @@
       </c>
       <c r="E419" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F419" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G419" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H419" t="inlineStr">
@@ -78415,7 +78436,7 @@
       </c>
       <c r="L419" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="M419" t="inlineStr">
@@ -78424,20 +78445,42 @@
         </is>
       </c>
       <c r="N419" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O419" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="P419" t="n">
-        <v>2</v>
-      </c>
-      <c r="R419" t="n">
-        <v>0.03386531510194095</v>
-      </c>
-      <c r="S419" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+        <v>6</v>
+      </c>
+      <c r="U419" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="V419" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="W419" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X419" t="inlineStr">
+        <is>
+          <t>Hepatitis A, Confirmed</t>
+        </is>
+      </c>
+      <c r="Y419" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z419" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA419" t="inlineStr">
@@ -78445,72 +78488,130 @@
           <t>weekly</t>
         </is>
       </c>
+      <c r="AB419" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC419" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD419" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE419" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF419" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG419" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH419" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI419" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ419" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK419" t="inlineStr">
+        <is>
+          <t>Confirmed hepatitis A component reported by NNDSS.</t>
+        </is>
+      </c>
+      <c r="AM419" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN419" t="b">
+        <v>1</v>
+      </c>
       <c r="AO419" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP419" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ419" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS419" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_A</t>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
         </is>
       </c>
       <c r="AT419" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU419" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV419" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW419" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX419" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY419" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ419" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA419" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB419" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC419" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -78537,17 +78638,17 @@
       </c>
       <c r="E420" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F420" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G420" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H420" t="inlineStr">
@@ -78581,173 +78682,81 @@
         </is>
       </c>
       <c r="N420" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="O420" t="n">
-        <v>2</v>
-      </c>
-      <c r="P420" t="n">
-        <v>2</v>
-      </c>
-      <c r="U420" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A</t>
-        </is>
-      </c>
-      <c r="V420" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A</t>
-        </is>
-      </c>
-      <c r="W420" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X420" t="inlineStr">
-        <is>
-          <t>Acute Viral Hepatitis A</t>
-        </is>
-      </c>
-      <c r="Y420" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z420" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA420" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB420" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC420" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD420" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE420" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF420" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG420" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH420" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI420" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ420" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK420" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM420" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN420" t="b">
-        <v>1</v>
+        <v>11</v>
+      </c>
+      <c r="R420" t="n">
+        <v>0.00898489248322343</v>
+      </c>
+      <c r="S420" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO420" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP420" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ420" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS420" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_A</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR420" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS420" t="inlineStr"/>
       <c r="AT420" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU420" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV420" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW420" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX420" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY420" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ420" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA420" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB420" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC420" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -78779,12 +78788,12 @@
       </c>
       <c r="F421" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G421" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H421" t="inlineStr">
@@ -78809,7 +78818,7 @@
       </c>
       <c r="L421" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M421" t="inlineStr">
@@ -78818,27 +78827,22 @@
         </is>
       </c>
       <c r="N421" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="O421" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="P421" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="R421" t="n">
-        <v>0.002578534319492447</v>
+        <v>0.03386531510194095</v>
       </c>
       <c r="S421" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U421" t="inlineStr">
-        <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
-        </is>
-      </c>
       <c r="AA421" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -78846,70 +78850,70 @@
       </c>
       <c r="AO421" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP421" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ421" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS421" t="inlineStr">
         <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_A</t>
         </is>
       </c>
       <c r="AT421" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU421" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV421" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW421" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX421" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY421" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ421" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA421" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB421" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC421" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -78941,12 +78945,12 @@
       </c>
       <c r="F422" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G422" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H422" t="inlineStr">
@@ -78971,7 +78975,7 @@
       </c>
       <c r="L422" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M422" t="inlineStr">
@@ -78980,32 +78984,32 @@
         </is>
       </c>
       <c r="N422" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="O422" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="P422" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="U422" t="inlineStr">
         <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A</t>
         </is>
       </c>
       <c r="V422" t="inlineStr">
         <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A</t>
         </is>
       </c>
       <c r="W422" t="inlineStr">
         <is>
-          <t>SRC_US_NNDSS</t>
+          <t>SRC_SG_CDA_WIDB</t>
         </is>
       </c>
       <c r="X422" t="inlineStr">
         <is>
-          <t>Hepatitis A, Confirmed</t>
+          <t>Acute Viral Hepatitis A</t>
         </is>
       </c>
       <c r="Y422" t="inlineStr">
@@ -79015,7 +79019,7 @@
       </c>
       <c r="Z422" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA422" t="inlineStr">
@@ -79030,7 +79034,7 @@
       </c>
       <c r="AC422" t="inlineStr">
         <is>
-          <t>country:US:national</t>
+          <t>country:SG:national</t>
         </is>
       </c>
       <c r="AD422" t="inlineStr">
@@ -79045,7 +79049,7 @@
       </c>
       <c r="AF422" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>conditional</t>
         </is>
       </c>
       <c r="AG422" t="inlineStr">
@@ -79065,17 +79069,17 @@
       </c>
       <c r="AJ422" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
         </is>
       </c>
       <c r="AK422" t="inlineStr">
         <is>
-          <t>Confirmed hepatitis A component reported by NNDSS.</t>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
         </is>
       </c>
       <c r="AM422" t="inlineStr">
         <is>
-          <t>provisional</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN422" t="b">
@@ -79083,70 +79087,70 @@
       </c>
       <c r="AO422" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP422" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ422" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS422" t="inlineStr">
         <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_A</t>
         </is>
       </c>
       <c r="AT422" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU422" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV422" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW422" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX422" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY422" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ422" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA422" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB422" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC422" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -79178,12 +79182,12 @@
       </c>
       <c r="F423" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G423" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H423" t="inlineStr">
@@ -79208,7 +79212,7 @@
       </c>
       <c r="L423" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="M423" t="inlineStr">
@@ -79217,81 +79221,98 @@
         </is>
       </c>
       <c r="N423" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O423" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="P423" t="n">
+        <v>9</v>
       </c>
       <c r="R423" t="n">
-        <v>0.00653446726052613</v>
+        <v>0.002578534319492447</v>
       </c>
       <c r="S423" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U423" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AA423" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO423" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP423" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR423" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS423" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ423" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS423" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
       <c r="AT423" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU423" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV423" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW423" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX423" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY423" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ423" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA423" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB423" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC423" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -79318,17 +79339,17 @@
       </c>
       <c r="E424" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F424" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G424" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H424" t="inlineStr">
@@ -79353,7 +79374,7 @@
       </c>
       <c r="L424" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="M424" t="inlineStr">
@@ -79362,93 +79383,173 @@
         </is>
       </c>
       <c r="N424" t="n">
+        <v>9</v>
+      </c>
+      <c r="O424" t="n">
+        <v>9</v>
+      </c>
+      <c r="P424" t="n">
+        <v>9</v>
+      </c>
+      <c r="U424" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="V424" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="W424" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X424" t="inlineStr">
+        <is>
+          <t>Hepatitis A, Confirmed</t>
+        </is>
+      </c>
+      <c r="Y424" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z424" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA424" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB424" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC424" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD424" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE424" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF424" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG424" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH424" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI424" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ424" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK424" t="inlineStr">
+        <is>
+          <t>Confirmed hepatitis A component reported by NNDSS.</t>
+        </is>
+      </c>
+      <c r="AM424" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN424" t="b">
         <v>1</v>
       </c>
-      <c r="O424" t="n">
+      <c r="AO424" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP424" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ424" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS424" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AT424" t="n">
         <v>1</v>
       </c>
-      <c r="P424" t="n">
-        <v>1</v>
-      </c>
-      <c r="R424" t="n">
-        <v>0.01693265755097047</v>
-      </c>
-      <c r="S424" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AA424" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AO424" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP424" t="inlineStr">
-        <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ424" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS424" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_A</t>
-        </is>
-      </c>
-      <c r="AT424" t="n">
-        <v>2</v>
-      </c>
       <c r="AU424" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV424" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW424" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX424" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY424" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ424" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA424" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB424" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC424" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -79475,17 +79576,17 @@
       </c>
       <c r="E425" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F425" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G425" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H425" t="inlineStr">
@@ -79519,173 +79620,81 @@
         </is>
       </c>
       <c r="N425" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="O425" t="n">
-        <v>1</v>
-      </c>
-      <c r="P425" t="n">
-        <v>1</v>
-      </c>
-      <c r="U425" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A</t>
-        </is>
-      </c>
-      <c r="V425" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A</t>
-        </is>
-      </c>
-      <c r="W425" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X425" t="inlineStr">
-        <is>
-          <t>Acute Viral Hepatitis A</t>
-        </is>
-      </c>
-      <c r="Y425" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z425" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA425" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB425" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC425" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD425" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE425" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF425" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG425" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH425" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI425" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ425" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK425" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM425" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN425" t="b">
-        <v>1</v>
+        <v>8</v>
+      </c>
+      <c r="R425" t="n">
+        <v>0.00653446726052613</v>
+      </c>
+      <c r="S425" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO425" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP425" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ425" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS425" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_A</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR425" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS425" t="inlineStr"/>
       <c r="AT425" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU425" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV425" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW425" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX425" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY425" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ425" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA425" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB425" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC425" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -79717,12 +79726,12 @@
       </c>
       <c r="F426" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G426" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H426" t="inlineStr">
@@ -79747,7 +79756,7 @@
       </c>
       <c r="L426" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M426" t="inlineStr">
@@ -79756,27 +79765,22 @@
         </is>
       </c>
       <c r="N426" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O426" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P426" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R426" t="n">
-        <v>0.0008595114398308156</v>
+        <v>0.01693265755097047</v>
       </c>
       <c r="S426" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U426" t="inlineStr">
-        <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
-        </is>
-      </c>
       <c r="AA426" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -79784,70 +79788,70 @@
       </c>
       <c r="AO426" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP426" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ426" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS426" t="inlineStr">
         <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_A</t>
         </is>
       </c>
       <c r="AT426" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU426" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV426" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW426" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX426" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY426" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ426" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA426" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB426" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC426" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -79879,12 +79883,12 @@
       </c>
       <c r="F427" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G427" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H427" t="inlineStr">
@@ -79909,7 +79913,7 @@
       </c>
       <c r="L427" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M427" t="inlineStr">
@@ -79918,32 +79922,32 @@
         </is>
       </c>
       <c r="N427" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O427" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P427" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U427" t="inlineStr">
         <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A</t>
         </is>
       </c>
       <c r="V427" t="inlineStr">
         <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A</t>
         </is>
       </c>
       <c r="W427" t="inlineStr">
         <is>
-          <t>SRC_US_NNDSS</t>
+          <t>SRC_SG_CDA_WIDB</t>
         </is>
       </c>
       <c r="X427" t="inlineStr">
         <is>
-          <t>Hepatitis A, Confirmed</t>
+          <t>Acute Viral Hepatitis A</t>
         </is>
       </c>
       <c r="Y427" t="inlineStr">
@@ -79953,7 +79957,7 @@
       </c>
       <c r="Z427" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA427" t="inlineStr">
@@ -79968,7 +79972,7 @@
       </c>
       <c r="AC427" t="inlineStr">
         <is>
-          <t>country:US:national</t>
+          <t>country:SG:national</t>
         </is>
       </c>
       <c r="AD427" t="inlineStr">
@@ -79983,7 +79987,7 @@
       </c>
       <c r="AF427" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>conditional</t>
         </is>
       </c>
       <c r="AG427" t="inlineStr">
@@ -80003,17 +80007,17 @@
       </c>
       <c r="AJ427" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
         </is>
       </c>
       <c r="AK427" t="inlineStr">
         <is>
-          <t>Confirmed hepatitis A component reported by NNDSS.</t>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
         </is>
       </c>
       <c r="AM427" t="inlineStr">
         <is>
-          <t>provisional</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN427" t="b">
@@ -80021,70 +80025,70 @@
       </c>
       <c r="AO427" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP427" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ427" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS427" t="inlineStr">
         <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_A</t>
         </is>
       </c>
       <c r="AT427" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU427" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV427" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW427" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX427" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY427" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ427" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA427" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB427" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC427" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -80116,12 +80120,12 @@
       </c>
       <c r="F428" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G428" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H428" t="inlineStr">
@@ -80146,7 +80150,7 @@
       </c>
       <c r="L428" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="M428" t="inlineStr">
@@ -80155,81 +80159,98 @@
         </is>
       </c>
       <c r="N428" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="O428" t="n">
-        <v>21</v>
+        <v>3</v>
+      </c>
+      <c r="P428" t="n">
+        <v>3</v>
       </c>
       <c r="R428" t="n">
-        <v>0.01715297655888109</v>
+        <v>0.0008595114398308156</v>
       </c>
       <c r="S428" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U428" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AA428" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO428" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP428" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR428" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS428" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ428" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS428" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
       <c r="AT428" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU428" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV428" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW428" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX428" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY428" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ428" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA428" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB428" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC428" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -80256,17 +80277,17 @@
       </c>
       <c r="E429" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F429" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G429" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H429" t="inlineStr">
@@ -80291,7 +80312,7 @@
       </c>
       <c r="L429" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="M429" t="inlineStr">
@@ -80300,20 +80321,42 @@
         </is>
       </c>
       <c r="N429" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O429" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P429" t="n">
-        <v>0</v>
-      </c>
-      <c r="R429" t="n">
-        <v>0</v>
-      </c>
-      <c r="S429" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+        <v>3</v>
+      </c>
+      <c r="U429" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="V429" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="W429" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X429" t="inlineStr">
+        <is>
+          <t>Hepatitis A, Confirmed</t>
+        </is>
+      </c>
+      <c r="Y429" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z429" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA429" t="inlineStr">
@@ -80321,72 +80364,130 @@
           <t>weekly</t>
         </is>
       </c>
+      <c r="AB429" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC429" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD429" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE429" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF429" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG429" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH429" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI429" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ429" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK429" t="inlineStr">
+        <is>
+          <t>Confirmed hepatitis A component reported by NNDSS.</t>
+        </is>
+      </c>
+      <c r="AM429" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN429" t="b">
+        <v>1</v>
+      </c>
       <c r="AO429" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP429" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ429" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS429" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_A</t>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
         </is>
       </c>
       <c r="AT429" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU429" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV429" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW429" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX429" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY429" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ429" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA429" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB429" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC429" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -80413,17 +80514,17 @@
       </c>
       <c r="E430" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F430" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G430" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H430" t="inlineStr">
@@ -80457,173 +80558,81 @@
         </is>
       </c>
       <c r="N430" t="n">
+        <v>21</v>
+      </c>
+      <c r="O430" t="n">
+        <v>21</v>
+      </c>
+      <c r="R430" t="n">
+        <v>0.01715297655888109</v>
+      </c>
+      <c r="S430" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO430" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP430" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR430" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS430" t="inlineStr"/>
+      <c r="AT430" t="n">
         <v>0</v>
       </c>
-      <c r="O430" t="n">
-        <v>0</v>
-      </c>
-      <c r="P430" t="n">
-        <v>0</v>
-      </c>
-      <c r="U430" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A</t>
-        </is>
-      </c>
-      <c r="V430" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A</t>
-        </is>
-      </c>
-      <c r="W430" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X430" t="inlineStr">
-        <is>
-          <t>Acute Viral Hepatitis A</t>
-        </is>
-      </c>
-      <c r="Y430" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z430" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA430" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB430" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC430" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD430" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE430" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF430" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG430" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH430" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI430" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ430" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK430" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM430" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN430" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO430" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP430" t="inlineStr">
-        <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ430" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS430" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_A</t>
-        </is>
-      </c>
-      <c r="AT430" t="n">
-        <v>2</v>
-      </c>
       <c r="AU430" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV430" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW430" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX430" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY430" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ430" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA430" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB430" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC430" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -80655,12 +80664,12 @@
       </c>
       <c r="F431" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G431" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H431" t="inlineStr">
@@ -80685,7 +80694,7 @@
       </c>
       <c r="L431" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M431" t="inlineStr">
@@ -80694,27 +80703,22 @@
         </is>
       </c>
       <c r="N431" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O431" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P431" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="R431" t="n">
-        <v>0.001719022879661631</v>
+        <v>0</v>
       </c>
       <c r="S431" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U431" t="inlineStr">
-        <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
-        </is>
-      </c>
       <c r="AA431" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -80722,70 +80726,70 @@
       </c>
       <c r="AO431" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP431" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ431" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS431" t="inlineStr">
         <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_A</t>
         </is>
       </c>
       <c r="AT431" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU431" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV431" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW431" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX431" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY431" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ431" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA431" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB431" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC431" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -80817,12 +80821,12 @@
       </c>
       <c r="F432" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G432" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H432" t="inlineStr">
@@ -80847,7 +80851,7 @@
       </c>
       <c r="L432" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M432" t="inlineStr">
@@ -80856,32 +80860,32 @@
         </is>
       </c>
       <c r="N432" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O432" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P432" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="U432" t="inlineStr">
         <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A</t>
         </is>
       </c>
       <c r="V432" t="inlineStr">
         <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A</t>
         </is>
       </c>
       <c r="W432" t="inlineStr">
         <is>
-          <t>SRC_US_NNDSS</t>
+          <t>SRC_SG_CDA_WIDB</t>
         </is>
       </c>
       <c r="X432" t="inlineStr">
         <is>
-          <t>Hepatitis A, Confirmed</t>
+          <t>Acute Viral Hepatitis A</t>
         </is>
       </c>
       <c r="Y432" t="inlineStr">
@@ -80891,7 +80895,7 @@
       </c>
       <c r="Z432" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA432" t="inlineStr">
@@ -80906,7 +80910,7 @@
       </c>
       <c r="AC432" t="inlineStr">
         <is>
-          <t>country:US:national</t>
+          <t>country:SG:national</t>
         </is>
       </c>
       <c r="AD432" t="inlineStr">
@@ -80921,7 +80925,7 @@
       </c>
       <c r="AF432" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>conditional</t>
         </is>
       </c>
       <c r="AG432" t="inlineStr">
@@ -80941,17 +80945,17 @@
       </c>
       <c r="AJ432" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
         </is>
       </c>
       <c r="AK432" t="inlineStr">
         <is>
-          <t>Confirmed hepatitis A component reported by NNDSS.</t>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
         </is>
       </c>
       <c r="AM432" t="inlineStr">
         <is>
-          <t>provisional</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN432" t="b">
@@ -80959,70 +80963,70 @@
       </c>
       <c r="AO432" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP432" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ432" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS432" t="inlineStr">
         <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_A</t>
         </is>
       </c>
       <c r="AT432" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU432" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV432" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW432" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX432" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY432" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ432" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA432" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB432" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC432" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -81054,12 +81058,12 @@
       </c>
       <c r="F433" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G433" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H433" t="inlineStr">
@@ -81084,90 +81088,107 @@
       </c>
       <c r="L433" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="M433" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N433" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O433" t="n">
-        <v>0</v>
+        <v>6</v>
+      </c>
+      <c r="P433" t="n">
+        <v>6</v>
       </c>
       <c r="R433" t="n">
-        <v>0</v>
+        <v>0.001719022879661631</v>
       </c>
       <c r="S433" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U433" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AA433" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO433" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP433" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR433" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS433" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ433" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS433" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
       <c r="AT433" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU433" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV433" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW433" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX433" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY433" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ433" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA433" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB433" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC433" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -81194,17 +81215,17 @@
       </c>
       <c r="E434" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F434" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G434" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H434" t="inlineStr">
@@ -81229,109 +81250,182 @@
       </c>
       <c r="L434" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="M434" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N434" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O434" t="n">
-        <v>0</v>
-      </c>
-      <c r="R434" t="n">
-        <v>0</v>
-      </c>
-      <c r="S434" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>6</v>
+      </c>
+      <c r="P434" t="n">
+        <v>6</v>
       </c>
       <c r="U434" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_115</t>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="V434" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="W434" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X434" t="inlineStr">
+        <is>
+          <t>Hepatitis A, Confirmed</t>
+        </is>
+      </c>
+      <c r="Y434" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z434" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA434" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB434" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC434" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD434" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE434" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF434" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG434" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH434" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI434" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ434" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK434" t="inlineStr">
+        <is>
+          <t>Confirmed hepatitis A component reported by NNDSS.</t>
+        </is>
+      </c>
+      <c r="AM434" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN434" t="b">
+        <v>1</v>
       </c>
       <c r="AO434" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP434" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ434" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR434" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS434" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_115</t>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
         </is>
       </c>
       <c r="AT434" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU434" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV434" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW434" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX434" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY434" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ434" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA434" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB434" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC434" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -81358,17 +81452,17 @@
       </c>
       <c r="E435" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F435" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G435" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H435" t="inlineStr">
@@ -81407,170 +81501,76 @@
       <c r="O435" t="n">
         <v>0</v>
       </c>
-      <c r="U435" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_115</t>
-        </is>
-      </c>
-      <c r="V435" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_115</t>
-        </is>
-      </c>
-      <c r="W435" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X435" t="inlineStr">
-        <is>
-          <t>Hepatitis A</t>
-        </is>
-      </c>
-      <c r="Y435" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z435" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA435" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB435" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC435" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD435" t="inlineStr">
+      <c r="R435" t="n">
+        <v>0</v>
+      </c>
+      <c r="S435" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO435" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP435" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR435" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS435" t="inlineStr"/>
+      <c r="AT435" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU435" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV435" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE435" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF435" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG435" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH435" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI435" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ435" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK435" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 115.</t>
-        </is>
-      </c>
-      <c r="AM435" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN435" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO435" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP435" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ435" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR435" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS435" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_115</t>
-        </is>
-      </c>
-      <c r="AT435" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU435" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
-      </c>
-      <c r="AV435" t="inlineStr">
-        <is>
-          <t>thl_ttr</t>
-        </is>
-      </c>
       <c r="AW435" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX435" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY435" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ435" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA435" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB435" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC435" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -81602,12 +81602,12 @@
       </c>
       <c r="F436" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G436" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H436" t="inlineStr">
@@ -81641,81 +81641,100 @@
         </is>
       </c>
       <c r="N436" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O436" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="R436" t="n">
-        <v>0.01162781954275227</v>
+        <v>0</v>
       </c>
       <c r="S436" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U436" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_115</t>
+        </is>
+      </c>
+      <c r="AA436" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO436" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP436" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ436" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR436" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS436" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS436" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_115</t>
+        </is>
+      </c>
       <c r="AT436" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU436" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV436" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW436" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX436" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY436" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ436" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA436" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB436" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC436" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -81742,17 +81761,17 @@
       </c>
       <c r="E437" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F437" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G437" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H437" t="inlineStr">
@@ -81791,17 +81810,34 @@
       <c r="O437" t="n">
         <v>0</v>
       </c>
-      <c r="R437" t="n">
-        <v>0</v>
-      </c>
-      <c r="S437" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U437" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_201_MONTHLY</t>
+          <t>SER_FI_THL_TTR_115</t>
+        </is>
+      </c>
+      <c r="V437" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_115</t>
+        </is>
+      </c>
+      <c r="W437" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X437" t="inlineStr">
+        <is>
+          <t>Hepatitis A</t>
+        </is>
+      </c>
+      <c r="Y437" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z437" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA437" t="inlineStr">
@@ -81809,6 +81845,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB437" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC437" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD437" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE437" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF437" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG437" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH437" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI437" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ437" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK437" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 115.</t>
+        </is>
+      </c>
+      <c r="AM437" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN437" t="b">
+        <v>1</v>
+      </c>
       <c r="AO437" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -81821,7 +81915,7 @@
       </c>
       <c r="AQ437" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR437" t="inlineStr">
@@ -81831,7 +81925,7 @@
       </c>
       <c r="AS437" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_201_MONTHLY</t>
+          <t>SER_FI_THL_TTR_115</t>
         </is>
       </c>
       <c r="AT437" t="n">
@@ -81839,47 +81933,47 @@
       </c>
       <c r="AU437" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV437" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW437" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX437" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY437" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ437" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA437" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB437" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC437" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -81906,217 +82000,526 @@
       </c>
       <c r="E438" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F438" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G438" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H438" t="inlineStr">
+        <is>
+          <t>D007</t>
+        </is>
+      </c>
+      <c r="I438" t="inlineStr">
+        <is>
+          <t>Hepatitis A</t>
+        </is>
+      </c>
+      <c r="J438" t="inlineStr">
+        <is>
+          <t>甲型肝炎</t>
+        </is>
+      </c>
+      <c r="K438" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L438" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M438" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N438" t="n">
+        <v>10</v>
+      </c>
+      <c r="O438" t="n">
+        <v>10</v>
+      </c>
+      <c r="R438" t="n">
+        <v>0.01937969923792046</v>
+      </c>
+      <c r="S438" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO438" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP438" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR438" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS438" t="inlineStr"/>
+      <c r="AT438" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU438" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV438" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW438" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX438" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY438" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ438" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA438" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB438" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC438" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>D007</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>hepatitis-a</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>Hepatitis A</t>
+        </is>
+      </c>
+      <c r="E439" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F439" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G439" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H439" t="inlineStr">
+        <is>
+          <t>D007</t>
+        </is>
+      </c>
+      <c r="I439" t="inlineStr">
+        <is>
+          <t>Hepatitis A</t>
+        </is>
+      </c>
+      <c r="J439" t="inlineStr">
+        <is>
+          <t>甲型肝炎</t>
+        </is>
+      </c>
+      <c r="K439" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L439" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M439" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N439" t="n">
+        <v>0</v>
+      </c>
+      <c r="O439" t="n">
+        <v>0</v>
+      </c>
+      <c r="R439" t="n">
+        <v>0</v>
+      </c>
+      <c r="S439" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U439" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_201_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA439" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO439" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP439" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ439" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR439" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS439" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_201_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT439" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU439" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV439" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW439" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX439" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY439" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ439" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA439" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB439" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC439" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>D007</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>hepatitis-a</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>Hepatitis A</t>
+        </is>
+      </c>
+      <c r="E440" t="inlineStr">
+        <is>
           <t>source_series_observation</t>
         </is>
       </c>
-      <c r="F438" t="inlineStr">
+      <c r="F440" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G438" t="inlineStr">
+      <c r="G440" t="inlineStr">
         <is>
           <t>Norway</t>
         </is>
       </c>
-      <c r="H438" t="inlineStr">
-        <is>
-          <t>D007</t>
-        </is>
-      </c>
-      <c r="I438" t="inlineStr">
-        <is>
-          <t>Hepatitis A</t>
-        </is>
-      </c>
-      <c r="J438" t="inlineStr">
+      <c r="H440" t="inlineStr">
+        <is>
+          <t>D007</t>
+        </is>
+      </c>
+      <c r="I440" t="inlineStr">
+        <is>
+          <t>Hepatitis A</t>
+        </is>
+      </c>
+      <c r="J440" t="inlineStr">
         <is>
           <t>甲型肝炎</t>
         </is>
       </c>
-      <c r="K438" t="inlineStr">
+      <c r="K440" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="L438" t="inlineStr">
+      <c r="L440" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="M438" t="inlineStr">
+      <c r="M440" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="N438" t="n">
+      <c r="N440" t="n">
         <v>0</v>
       </c>
-      <c r="O438" t="n">
+      <c r="O440" t="n">
         <v>0</v>
       </c>
-      <c r="U438" t="inlineStr">
+      <c r="U440" t="inlineStr">
         <is>
           <t>SER_NO_FHI_201_MONTHLY</t>
         </is>
       </c>
-      <c r="V438" t="inlineStr">
+      <c r="V440" t="inlineStr">
         <is>
           <t>SER_NO_FHI_201_MONTHLY</t>
         </is>
       </c>
-      <c r="W438" t="inlineStr">
+      <c r="W440" t="inlineStr">
         <is>
           <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
-      <c r="X438" t="inlineStr">
+      <c r="X440" t="inlineStr">
         <is>
           <t>Hepatitt A</t>
         </is>
       </c>
-      <c r="Y438" t="inlineStr">
+      <c r="Y440" t="inlineStr">
         <is>
           <t>case_notifications</t>
         </is>
       </c>
-      <c r="Z438" t="inlineStr">
+      <c r="Z440" t="inlineStr">
         <is>
           <t>national_notifiable_disease_registry</t>
         </is>
       </c>
-      <c r="AA438" t="inlineStr">
+      <c r="AA440" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB438" t="inlineStr">
+      <c r="AB440" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="AC438" t="inlineStr">
+      <c r="AC440" t="inlineStr">
         <is>
           <t>country:NO:national</t>
         </is>
       </c>
-      <c r="AD438" t="inlineStr">
+      <c r="AD440" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE438" t="inlineStr">
+      <c r="AE440" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="AF438" t="inlineStr">
+      <c r="AF440" t="inlineStr">
         <is>
           <t>conditional</t>
         </is>
       </c>
-      <c r="AG438" t="inlineStr">
+      <c r="AG440" t="inlineStr">
         <is>
           <t>non_additive</t>
         </is>
       </c>
-      <c r="AH438" t="inlineStr">
+      <c r="AH440" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="AI438" t="inlineStr">
+      <c r="AI440" t="inlineStr">
         <is>
           <t>missing_is_unknown</t>
         </is>
       </c>
-      <c r="AJ438" t="inlineStr">
+      <c r="AJ440" t="inlineStr">
         <is>
           <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
-      <c r="AK438" t="inlineStr">
+      <c r="AK440" t="inlineStr">
         <is>
           <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
         </is>
       </c>
-      <c r="AM438" t="inlineStr">
+      <c r="AM440" t="inlineStr">
         <is>
           <t>provisional; raw; revised</t>
         </is>
       </c>
-      <c r="AN438" t="b">
+      <c r="AN440" t="b">
         <v>1</v>
       </c>
-      <c r="AO438" t="inlineStr">
+      <c r="AO440" t="inlineStr">
         <is>
           <t>series_registry</t>
         </is>
       </c>
-      <c r="AP438" t="inlineStr">
+      <c r="AP440" t="inlineStr">
         <is>
           <t>representative_series</t>
         </is>
       </c>
-      <c r="AQ438" t="inlineStr">
+      <c r="AQ440" t="inlineStr">
         <is>
           <t>parity</t>
         </is>
       </c>
-      <c r="AR438" t="inlineStr">
+      <c r="AR440" t="inlineStr">
         <is>
           <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
-      <c r="AS438" t="inlineStr">
+      <c r="AS440" t="inlineStr">
         <is>
           <t>SER_NO_FHI_201_MONTHLY</t>
         </is>
       </c>
-      <c r="AT438" t="n">
+      <c r="AT440" t="n">
         <v>2</v>
       </c>
-      <c r="AU438" t="inlineStr">
+      <c r="AU440" t="inlineStr">
         <is>
           <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
-      <c r="AV438" t="inlineStr">
+      <c r="AV440" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="AW438" t="inlineStr">
+      <c r="AW440" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="AX438" t="inlineStr">
+      <c r="AX440" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="AY438" t="inlineStr">
+      <c r="AY440" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
       </c>
-      <c r="AZ438" t="inlineStr">
+      <c r="AZ440" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="BA438" t="inlineStr">
+      <c r="BA440" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="BB438" t="inlineStr">
+      <c r="BB440" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="BC438" t="inlineStr">
+      <c r="BC440" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
@@ -82238,7 +82641,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="10">
@@ -82248,7 +82651,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="11">
@@ -82268,7 +82671,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="13">
@@ -82300,7 +82703,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>17597</v>
+        <v>17622</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d007/2026-2029.xlsx
+++ b/diseases/d007/2026-2029.xlsx
@@ -63943,13 +63943,13 @@
         </is>
       </c>
       <c r="N339" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O339" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R339" t="n">
-        <v>0.04774655365375727</v>
+        <v>0.05141936547327706</v>
       </c>
       <c r="S339" t="inlineStr">
         <is>
@@ -74743,13 +74743,13 @@
         </is>
       </c>
       <c r="N398" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="O398" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="R398" t="n">
-        <v>0.05141936547327706</v>
+        <v>0.04407374183423748</v>
       </c>
       <c r="S398" t="inlineStr">
         <is>
@@ -76001,13 +76001,13 @@
         </is>
       </c>
       <c r="N406" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="O406" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="R406" t="n">
-        <v>0.2499981201691739</v>
+        <v>0.251936090092966</v>
       </c>
       <c r="S406" t="inlineStr">
         <is>
@@ -81457,12 +81457,12 @@
       </c>
       <c r="F435" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G435" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H435" t="inlineStr">
@@ -81487,22 +81487,22 @@
       </c>
       <c r="L435" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M435" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N435" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="O435" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="R435" t="n">
-        <v>0</v>
+        <v>0.01551935974374956</v>
       </c>
       <c r="S435" t="inlineStr">
         <is>
@@ -81535,42 +81535,42 @@
       </c>
       <c r="AV435" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW435" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX435" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY435" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ435" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA435" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB435" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC435" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -81602,12 +81602,12 @@
       </c>
       <c r="F436" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G436" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H436" t="inlineStr">
@@ -81654,87 +81654,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U436" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_115</t>
-        </is>
-      </c>
-      <c r="AA436" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO436" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP436" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ436" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR436" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS436" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_115</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS436" t="inlineStr"/>
       <c r="AT436" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU436" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV436" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW436" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX436" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY436" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ436" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA436" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB436" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC436" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -81761,7 +81742,7 @@
       </c>
       <c r="E437" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F437" t="inlineStr">
@@ -81810,98 +81791,23 @@
       <c r="O437" t="n">
         <v>0</v>
       </c>
+      <c r="R437" t="n">
+        <v>0</v>
+      </c>
+      <c r="S437" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U437" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_115</t>
         </is>
       </c>
-      <c r="V437" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_115</t>
-        </is>
-      </c>
-      <c r="W437" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X437" t="inlineStr">
-        <is>
-          <t>Hepatitis A</t>
-        </is>
-      </c>
-      <c r="Y437" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z437" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA437" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB437" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC437" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD437" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE437" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF437" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG437" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH437" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI437" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ437" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK437" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 115.</t>
-        </is>
-      </c>
-      <c r="AM437" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN437" t="b">
-        <v>1</v>
       </c>
       <c r="AO437" t="inlineStr">
         <is>
@@ -82000,17 +81906,17 @@
       </c>
       <c r="E438" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F438" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G438" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H438" t="inlineStr">
@@ -82044,81 +81950,175 @@
         </is>
       </c>
       <c r="N438" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O438" t="n">
-        <v>10</v>
-      </c>
-      <c r="R438" t="n">
-        <v>0.01937969923792046</v>
-      </c>
-      <c r="S438" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="U438" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_115</t>
+        </is>
+      </c>
+      <c r="V438" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_115</t>
+        </is>
+      </c>
+      <c r="W438" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X438" t="inlineStr">
+        <is>
+          <t>Hepatitis A</t>
+        </is>
+      </c>
+      <c r="Y438" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z438" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA438" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB438" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC438" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD438" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE438" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF438" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG438" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH438" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI438" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ438" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK438" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 115.</t>
+        </is>
+      </c>
+      <c r="AM438" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN438" t="b">
+        <v>1</v>
       </c>
       <c r="AO438" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP438" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ438" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR438" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS438" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS438" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_115</t>
+        </is>
+      </c>
       <c r="AT438" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU438" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV438" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW438" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX438" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY438" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ438" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA438" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB438" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC438" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -82150,12 +82150,12 @@
       </c>
       <c r="F439" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G439" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H439" t="inlineStr">
@@ -82189,100 +82189,81 @@
         </is>
       </c>
       <c r="N439" t="n">
+        <v>21</v>
+      </c>
+      <c r="O439" t="n">
+        <v>21</v>
+      </c>
+      <c r="R439" t="n">
+        <v>0.04069736839963296</v>
+      </c>
+      <c r="S439" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO439" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP439" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR439" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS439" t="inlineStr"/>
+      <c r="AT439" t="n">
         <v>0</v>
       </c>
-      <c r="O439" t="n">
-        <v>0</v>
-      </c>
-      <c r="R439" t="n">
-        <v>0</v>
-      </c>
-      <c r="S439" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U439" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_201_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA439" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO439" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP439" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ439" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AR439" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS439" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_201_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AT439" t="n">
-        <v>2</v>
-      </c>
       <c r="AU439" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV439" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW439" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX439" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY439" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ439" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA439" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB439" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC439" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -82309,7 +82290,7 @@
       </c>
       <c r="E440" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F440" t="inlineStr">
@@ -82358,98 +82339,23 @@
       <c r="O440" t="n">
         <v>0</v>
       </c>
+      <c r="R440" t="n">
+        <v>0</v>
+      </c>
+      <c r="S440" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U440" t="inlineStr">
         <is>
           <t>SER_NO_FHI_201_MONTHLY</t>
         </is>
       </c>
-      <c r="V440" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_201_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W440" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X440" t="inlineStr">
-        <is>
-          <t>Hepatitt A</t>
-        </is>
-      </c>
-      <c r="Y440" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z440" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA440" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB440" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC440" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD440" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE440" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF440" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG440" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH440" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI440" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ440" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK440" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM440" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN440" t="b">
-        <v>1</v>
       </c>
       <c r="AO440" t="inlineStr">
         <is>
@@ -82520,6 +82426,245 @@
         </is>
       </c>
       <c r="BC440" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>D007</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>hepatitis-a</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>Hepatitis A</t>
+        </is>
+      </c>
+      <c r="E441" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F441" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G441" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H441" t="inlineStr">
+        <is>
+          <t>D007</t>
+        </is>
+      </c>
+      <c r="I441" t="inlineStr">
+        <is>
+          <t>Hepatitis A</t>
+        </is>
+      </c>
+      <c r="J441" t="inlineStr">
+        <is>
+          <t>甲型肝炎</t>
+        </is>
+      </c>
+      <c r="K441" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L441" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M441" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N441" t="n">
+        <v>0</v>
+      </c>
+      <c r="O441" t="n">
+        <v>0</v>
+      </c>
+      <c r="U441" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_201_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V441" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_201_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W441" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X441" t="inlineStr">
+        <is>
+          <t>Hepatitt A</t>
+        </is>
+      </c>
+      <c r="Y441" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z441" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA441" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB441" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC441" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD441" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE441" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF441" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG441" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH441" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI441" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ441" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK441" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM441" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN441" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO441" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP441" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ441" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR441" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS441" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_201_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT441" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU441" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV441" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW441" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX441" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY441" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ441" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA441" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB441" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC441" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
@@ -82641,7 +82786,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="10">
@@ -82651,7 +82796,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="11">
@@ -82703,7 +82848,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>17622</v>
+        <v>17652</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d007/2026-2029.xlsx
+++ b/diseases/d007/2026-2029.xlsx
@@ -74743,13 +74743,13 @@
         </is>
       </c>
       <c r="N398" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="O398" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="R398" t="n">
-        <v>0.04407374183423748</v>
+        <v>0.06243780093183643</v>
       </c>
       <c r="S398" t="inlineStr">
         <is>
@@ -76146,13 +76146,13 @@
         </is>
       </c>
       <c r="N407" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O407" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="R407" t="n">
-        <v>0.1238283078056854</v>
+        <v>0.1592078243215956</v>
       </c>
       <c r="S407" t="inlineStr">
         <is>
@@ -76310,10 +76310,10 @@
         </is>
       </c>
       <c r="N408" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O408" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="U408" t="inlineStr">
         <is>
@@ -82189,13 +82189,13 @@
         </is>
       </c>
       <c r="N439" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O439" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="R439" t="n">
-        <v>0.04069736839963296</v>
+        <v>0.04457330824721705</v>
       </c>
       <c r="S439" t="inlineStr">
         <is>
@@ -82334,13 +82334,13 @@
         </is>
       </c>
       <c r="N440" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O440" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R440" t="n">
-        <v>0</v>
+        <v>0.07075903303182025</v>
       </c>
       <c r="S440" t="inlineStr">
         <is>
@@ -82498,10 +82498,10 @@
         </is>
       </c>
       <c r="N441" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O441" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U441" t="inlineStr">
         <is>
@@ -82848,7 +82848,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>17652</v>
+        <v>17665</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d007/2026-2029.xlsx
+++ b/diseases/d007/2026-2029.xlsx
@@ -75559,12 +75559,12 @@
       </c>
       <c r="F404" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G404" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H404" t="inlineStr">
@@ -75598,100 +75598,98 @@
         </is>
       </c>
       <c r="N404" t="n">
+        <v>1384</v>
+      </c>
+      <c r="O404" t="n">
+        <v>1384</v>
+      </c>
+      <c r="Q404" t="n">
+        <v>0</v>
+      </c>
+      <c r="R404" t="n">
+        <v>0.09795358481203226</v>
+      </c>
+      <c r="S404" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U404" t="inlineStr">
+        <is>
+          <t>SER_CN_HEPATITIS_A</t>
+        </is>
+      </c>
+      <c r="AA404" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO404" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP404" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ404" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS404" t="inlineStr">
+        <is>
+          <t>SER_CN_HEPATITIS_A</t>
+        </is>
+      </c>
+      <c r="AT404" t="n">
         <v>1</v>
       </c>
-      <c r="O404" t="n">
-        <v>1</v>
-      </c>
-      <c r="R404" t="n">
-        <v>0.01778809170864137</v>
-      </c>
-      <c r="S404" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U404" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_115</t>
-        </is>
-      </c>
-      <c r="AA404" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO404" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP404" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ404" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR404" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS404" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_115</t>
-        </is>
-      </c>
-      <c r="AT404" t="n">
-        <v>2</v>
-      </c>
       <c r="AU404" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV404" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW404" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX404" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY404" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ404" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA404" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB404" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC404" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -75723,12 +75721,12 @@
       </c>
       <c r="F405" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G405" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H405" t="inlineStr">
@@ -75762,29 +75760,29 @@
         </is>
       </c>
       <c r="N405" t="n">
-        <v>1</v>
+        <v>1384</v>
       </c>
       <c r="O405" t="n">
-        <v>1</v>
+        <v>1384</v>
       </c>
       <c r="U405" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_115</t>
+          <t>SER_CN_HEPATITIS_A</t>
         </is>
       </c>
       <c r="V405" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_115</t>
+          <t>SER_CN_HEPATITIS_A</t>
         </is>
       </c>
       <c r="W405" t="inlineStr">
         <is>
-          <t>SRC_FI_THL_TTR</t>
+          <t>SRC_CN_CDC</t>
         </is>
       </c>
       <c r="X405" t="inlineStr">
         <is>
-          <t>Hepatitis A</t>
+          <t>甲型肝炎</t>
         </is>
       </c>
       <c r="Y405" t="inlineStr">
@@ -75794,7 +75792,7 @@
       </c>
       <c r="Z405" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA405" t="inlineStr">
@@ -75809,7 +75807,7 @@
       </c>
       <c r="AC405" t="inlineStr">
         <is>
-          <t>country:FI:national</t>
+          <t>country:CN:national</t>
         </is>
       </c>
       <c r="AD405" t="inlineStr">
@@ -75824,7 +75822,7 @@
       </c>
       <c r="AF405" t="inlineStr">
         <is>
-          <t>conditional</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AG405" t="inlineStr">
@@ -75844,17 +75842,17 @@
       </c>
       <c r="AJ405" t="inlineStr">
         <is>
-          <t>FI_THL_TTR_reporting_group</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK405" t="inlineStr">
         <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 115.</t>
+          <t>China CDC source-reported hepatitis A component.</t>
         </is>
       </c>
       <c r="AM405" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN405" t="b">
@@ -75862,75 +75860,70 @@
       </c>
       <c r="AO405" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP405" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ405" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR405" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS405" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_115</t>
+          <t>SER_CN_HEPATITIS_A</t>
         </is>
       </c>
       <c r="AT405" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU405" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV405" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW405" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX405" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY405" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ405" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA405" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB405" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC405" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -75962,12 +75955,12 @@
       </c>
       <c r="F406" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G406" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H406" t="inlineStr">
@@ -76001,81 +75994,100 @@
         </is>
       </c>
       <c r="N406" t="n">
-        <v>130</v>
+        <v>1</v>
       </c>
       <c r="O406" t="n">
-        <v>130</v>
+        <v>1</v>
       </c>
       <c r="R406" t="n">
-        <v>0.251936090092966</v>
+        <v>0.01778809170864137</v>
       </c>
       <c r="S406" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U406" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_115</t>
+        </is>
+      </c>
+      <c r="AA406" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO406" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP406" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ406" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR406" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS406" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS406" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_115</t>
+        </is>
+      </c>
       <c r="AT406" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU406" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV406" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW406" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX406" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY406" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ406" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA406" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB406" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC406" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -76102,17 +76114,17 @@
       </c>
       <c r="E407" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F407" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G407" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H407" t="inlineStr">
@@ -76146,22 +76158,39 @@
         </is>
       </c>
       <c r="N407" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="O407" t="n">
-        <v>9</v>
-      </c>
-      <c r="R407" t="n">
-        <v>0.1592078243215956</v>
-      </c>
-      <c r="S407" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="U407" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_201_MONTHLY</t>
+          <t>SER_FI_THL_TTR_115</t>
+        </is>
+      </c>
+      <c r="V407" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_115</t>
+        </is>
+      </c>
+      <c r="W407" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X407" t="inlineStr">
+        <is>
+          <t>Hepatitis A</t>
+        </is>
+      </c>
+      <c r="Y407" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z407" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA407" t="inlineStr">
@@ -76169,6 +76198,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB407" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC407" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD407" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE407" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF407" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG407" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH407" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI407" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ407" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK407" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 115.</t>
+        </is>
+      </c>
+      <c r="AM407" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN407" t="b">
+        <v>1</v>
+      </c>
       <c r="AO407" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -76181,7 +76268,7 @@
       </c>
       <c r="AQ407" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR407" t="inlineStr">
@@ -76191,7 +76278,7 @@
       </c>
       <c r="AS407" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_201_MONTHLY</t>
+          <t>SER_FI_THL_TTR_115</t>
         </is>
       </c>
       <c r="AT407" t="n">
@@ -76199,47 +76286,47 @@
       </c>
       <c r="AU407" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV407" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW407" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX407" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY407" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ407" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA407" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB407" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC407" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -76266,17 +76353,17 @@
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F408" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G408" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H408" t="inlineStr">
@@ -76310,175 +76397,81 @@
         </is>
       </c>
       <c r="N408" t="n">
-        <v>9</v>
+        <v>130</v>
       </c>
       <c r="O408" t="n">
-        <v>9</v>
-      </c>
-      <c r="U408" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_201_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V408" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_201_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W408" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X408" t="inlineStr">
-        <is>
-          <t>Hepatitt A</t>
-        </is>
-      </c>
-      <c r="Y408" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z408" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA408" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB408" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC408" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD408" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE408" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF408" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG408" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH408" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI408" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ408" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK408" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM408" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN408" t="b">
-        <v>1</v>
+        <v>130</v>
+      </c>
+      <c r="R408" t="n">
+        <v>0.251936090092966</v>
+      </c>
+      <c r="S408" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO408" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP408" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ408" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR408" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS408" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_201_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS408" t="inlineStr"/>
       <c r="AT408" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU408" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV408" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW408" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX408" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY408" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ408" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA408" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB408" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC408" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -76510,12 +76503,12 @@
       </c>
       <c r="F409" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G409" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H409" t="inlineStr">
@@ -76549,13 +76542,13 @@
         </is>
       </c>
       <c r="N409" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="O409" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="R409" t="n">
-        <v>0.1868976085656669</v>
+        <v>0.1592078243215956</v>
       </c>
       <c r="S409" t="inlineStr">
         <is>
@@ -76564,7 +76557,7 @@
       </c>
       <c r="U409" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_A</t>
+          <t>SER_NO_FHI_201_MONTHLY</t>
         </is>
       </c>
       <c r="AA409" t="inlineStr">
@@ -76594,7 +76587,7 @@
       </c>
       <c r="AS409" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_A</t>
+          <t>SER_NO_FHI_201_MONTHLY</t>
         </is>
       </c>
       <c r="AT409" t="n">
@@ -76607,42 +76600,42 @@
       </c>
       <c r="AV409" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW409" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX409" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY409" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ409" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA409" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB409" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC409" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -76674,12 +76667,12 @@
       </c>
       <c r="F410" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G410" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H410" t="inlineStr">
@@ -76713,29 +76706,29 @@
         </is>
       </c>
       <c r="N410" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="O410" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="U410" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_A</t>
+          <t>SER_NO_FHI_201_MONTHLY</t>
         </is>
       </c>
       <c r="V410" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_A</t>
+          <t>SER_NO_FHI_201_MONTHLY</t>
         </is>
       </c>
       <c r="W410" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X410" t="inlineStr">
         <is>
-          <t>Hepatit A</t>
+          <t>Hepatitt A</t>
         </is>
       </c>
       <c r="Y410" t="inlineStr">
@@ -76760,7 +76753,7 @@
       </c>
       <c r="AC410" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD410" t="inlineStr">
@@ -76795,17 +76788,17 @@
       </c>
       <c r="AJ410" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK410" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
         </is>
       </c>
       <c r="AM410" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN410" t="b">
@@ -76833,7 +76826,7 @@
       </c>
       <c r="AS410" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_A</t>
+          <t>SER_NO_FHI_201_MONTHLY</t>
         </is>
       </c>
       <c r="AT410" t="n">
@@ -76846,42 +76839,42 @@
       </c>
       <c r="AV410" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW410" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX410" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY410" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ410" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA410" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB410" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC410" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -76913,12 +76906,12 @@
       </c>
       <c r="F411" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G411" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H411" t="inlineStr">
@@ -76952,13 +76945,13 @@
         </is>
       </c>
       <c r="N411" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="O411" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="R411" t="n">
-        <v>0.05649400180367965</v>
+        <v>0.1868976085656669</v>
       </c>
       <c r="S411" t="inlineStr">
         <is>
@@ -76967,7 +76960,7 @@
       </c>
       <c r="U411" t="inlineStr">
         <is>
-          <t>SER_TW_HEPATITIS_A_0701</t>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_A</t>
         </is>
       </c>
       <c r="AA411" t="inlineStr">
@@ -76982,7 +76975,7 @@
       </c>
       <c r="AP411" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ411" t="inlineStr">
@@ -76990,57 +76983,62 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR411" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS411" t="inlineStr">
         <is>
-          <t>SER_TW_HEPATITIS_A_0701</t>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_A</t>
         </is>
       </c>
       <c r="AT411" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU411" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV411" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW411" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX411" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY411" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ411" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA411" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB411" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC411" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -77072,12 +77070,12 @@
       </c>
       <c r="F412" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G412" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H412" t="inlineStr">
@@ -77111,29 +77109,29 @@
         </is>
       </c>
       <c r="N412" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="O412" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="U412" t="inlineStr">
         <is>
-          <t>SER_TW_HEPATITIS_A_0701</t>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_A</t>
         </is>
       </c>
       <c r="V412" t="inlineStr">
         <is>
-          <t>SER_TW_HEPATITIS_A_0701</t>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_A</t>
         </is>
       </c>
       <c r="W412" t="inlineStr">
         <is>
-          <t>SRC_TW_NIDSS</t>
+          <t>SRC_SE_FOHM_SMINET</t>
         </is>
       </c>
       <c r="X412" t="inlineStr">
         <is>
-          <t>急性病毒性Ａ型肝炎</t>
+          <t>Hepatit A</t>
         </is>
       </c>
       <c r="Y412" t="inlineStr">
@@ -77143,7 +77141,7 @@
       </c>
       <c r="Z412" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA412" t="inlineStr">
@@ -77158,7 +77156,7 @@
       </c>
       <c r="AC412" t="inlineStr">
         <is>
-          <t>country:TW:national</t>
+          <t>country:SE:national</t>
         </is>
       </c>
       <c r="AD412" t="inlineStr">
@@ -77173,7 +77171,7 @@
       </c>
       <c r="AF412" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>conditional</t>
         </is>
       </c>
       <c r="AG412" t="inlineStr">
@@ -77193,17 +77191,17 @@
       </c>
       <c r="AJ412" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>SE_FOHM_SMINET_current</t>
         </is>
       </c>
       <c r="AK412" t="inlineStr">
         <is>
-          <t>Acute hepatitis A, code 0701. D067 remains deprecated.</t>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
         </is>
       </c>
       <c r="AM412" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>revised</t>
         </is>
       </c>
       <c r="AN412" t="b">
@@ -77216,7 +77214,7 @@
       </c>
       <c r="AP412" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ412" t="inlineStr">
@@ -77224,57 +77222,62 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR412" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS412" t="inlineStr">
         <is>
-          <t>SER_TW_HEPATITIS_A_0701</t>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_A</t>
         </is>
       </c>
       <c r="AT412" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU412" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV412" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW412" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX412" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY412" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ412" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA412" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB412" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC412" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -77306,12 +77309,12 @@
       </c>
       <c r="F413" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G413" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H413" t="inlineStr">
@@ -77345,16 +77348,13 @@
         </is>
       </c>
       <c r="N413" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="O413" t="n">
-        <v>2</v>
-      </c>
-      <c r="P413" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="R413" t="n">
-        <v>0.0005730076265538771</v>
+        <v>0.05649400180367965</v>
       </c>
       <c r="S413" t="inlineStr">
         <is>
@@ -77363,17 +77363,17 @@
       </c>
       <c r="U413" t="inlineStr">
         <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+          <t>SER_TW_HEPATITIS_A_0701</t>
         </is>
       </c>
       <c r="AA413" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO413" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP413" t="inlineStr">
@@ -77383,12 +77383,12 @@
       </c>
       <c r="AQ413" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS413" t="inlineStr">
         <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+          <t>SER_TW_HEPATITIS_A_0701</t>
         </is>
       </c>
       <c r="AT413" t="n">
@@ -77396,47 +77396,47 @@
       </c>
       <c r="AU413" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV413" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW413" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX413" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY413" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ413" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA413" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB413" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC413" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -77468,12 +77468,12 @@
       </c>
       <c r="F414" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G414" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H414" t="inlineStr">
@@ -77507,32 +77507,29 @@
         </is>
       </c>
       <c r="N414" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="O414" t="n">
-        <v>2</v>
-      </c>
-      <c r="P414" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="U414" t="inlineStr">
         <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+          <t>SER_TW_HEPATITIS_A_0701</t>
         </is>
       </c>
       <c r="V414" t="inlineStr">
         <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+          <t>SER_TW_HEPATITIS_A_0701</t>
         </is>
       </c>
       <c r="W414" t="inlineStr">
         <is>
-          <t>SRC_US_NNDSS</t>
+          <t>SRC_TW_NIDSS</t>
         </is>
       </c>
       <c r="X414" t="inlineStr">
         <is>
-          <t>Hepatitis A, Confirmed</t>
+          <t>急性病毒性Ａ型肝炎</t>
         </is>
       </c>
       <c r="Y414" t="inlineStr">
@@ -77547,7 +77544,7 @@
       </c>
       <c r="AA414" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AB414" t="inlineStr">
@@ -77557,7 +77554,7 @@
       </c>
       <c r="AC414" t="inlineStr">
         <is>
-          <t>country:US:national</t>
+          <t>country:TW:national</t>
         </is>
       </c>
       <c r="AD414" t="inlineStr">
@@ -77597,12 +77594,12 @@
       </c>
       <c r="AK414" t="inlineStr">
         <is>
-          <t>Confirmed hepatitis A component reported by NNDSS.</t>
+          <t>Acute hepatitis A, code 0701. D067 remains deprecated.</t>
         </is>
       </c>
       <c r="AM414" t="inlineStr">
         <is>
-          <t>provisional</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN414" t="b">
@@ -77610,7 +77607,7 @@
       </c>
       <c r="AO414" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP414" t="inlineStr">
@@ -77620,12 +77617,12 @@
       </c>
       <c r="AQ414" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS414" t="inlineStr">
         <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+          <t>SER_TW_HEPATITIS_A_0701</t>
         </is>
       </c>
       <c r="AT414" t="n">
@@ -77633,47 +77630,47 @@
       </c>
       <c r="AU414" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV414" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW414" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX414" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY414" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ414" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA414" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB414" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC414" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -77705,12 +77702,12 @@
       </c>
       <c r="F415" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G415" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H415" t="inlineStr">
@@ -77735,7 +77732,7 @@
       </c>
       <c r="L415" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M415" t="inlineStr">
@@ -77744,81 +77741,98 @@
         </is>
       </c>
       <c r="N415" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="O415" t="n">
-        <v>14</v>
+        <v>2</v>
+      </c>
+      <c r="P415" t="n">
+        <v>2</v>
       </c>
       <c r="R415" t="n">
-        <v>0.01143531770592073</v>
+        <v>0.0005730076265538771</v>
       </c>
       <c r="S415" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U415" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AA415" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO415" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP415" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR415" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS415" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ415" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS415" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
       <c r="AT415" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU415" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV415" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW415" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX415" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY415" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ415" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA415" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB415" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC415" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -77845,17 +77859,17 @@
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F416" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G416" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H416" t="inlineStr">
@@ -77880,7 +77894,7 @@
       </c>
       <c r="L416" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M416" t="inlineStr">
@@ -77889,93 +77903,173 @@
         </is>
       </c>
       <c r="N416" t="n">
+        <v>2</v>
+      </c>
+      <c r="O416" t="n">
+        <v>2</v>
+      </c>
+      <c r="P416" t="n">
+        <v>2</v>
+      </c>
+      <c r="U416" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="V416" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="W416" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X416" t="inlineStr">
+        <is>
+          <t>Hepatitis A, Confirmed</t>
+        </is>
+      </c>
+      <c r="Y416" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z416" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA416" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB416" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC416" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD416" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE416" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF416" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG416" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH416" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI416" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ416" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK416" t="inlineStr">
+        <is>
+          <t>Confirmed hepatitis A component reported by NNDSS.</t>
+        </is>
+      </c>
+      <c r="AM416" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN416" t="b">
         <v>1</v>
       </c>
-      <c r="O416" t="n">
+      <c r="AO416" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP416" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ416" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS416" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AT416" t="n">
         <v>1</v>
       </c>
-      <c r="P416" t="n">
-        <v>1</v>
-      </c>
-      <c r="R416" t="n">
-        <v>0.01693265755097047</v>
-      </c>
-      <c r="S416" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AA416" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AO416" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP416" t="inlineStr">
-        <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ416" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS416" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_A</t>
-        </is>
-      </c>
-      <c r="AT416" t="n">
-        <v>2</v>
-      </c>
       <c r="AU416" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV416" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW416" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX416" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY416" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ416" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA416" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB416" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC416" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -78002,17 +78096,17 @@
       </c>
       <c r="E417" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F417" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G417" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H417" t="inlineStr">
@@ -78046,173 +78140,81 @@
         </is>
       </c>
       <c r="N417" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="O417" t="n">
-        <v>1</v>
-      </c>
-      <c r="P417" t="n">
-        <v>1</v>
-      </c>
-      <c r="U417" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A</t>
-        </is>
-      </c>
-      <c r="V417" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A</t>
-        </is>
-      </c>
-      <c r="W417" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X417" t="inlineStr">
-        <is>
-          <t>Acute Viral Hepatitis A</t>
-        </is>
-      </c>
-      <c r="Y417" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z417" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA417" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB417" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC417" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD417" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE417" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF417" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG417" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH417" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI417" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ417" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK417" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM417" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN417" t="b">
-        <v>1</v>
+        <v>14</v>
+      </c>
+      <c r="R417" t="n">
+        <v>0.01143531770592073</v>
+      </c>
+      <c r="S417" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO417" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP417" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ417" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS417" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_A</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR417" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS417" t="inlineStr"/>
       <c r="AT417" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU417" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV417" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW417" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX417" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY417" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ417" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA417" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB417" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC417" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -78244,12 +78246,12 @@
       </c>
       <c r="F418" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G418" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H418" t="inlineStr">
@@ -78274,7 +78276,7 @@
       </c>
       <c r="L418" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M418" t="inlineStr">
@@ -78283,27 +78285,22 @@
         </is>
       </c>
       <c r="N418" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="O418" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="P418" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="R418" t="n">
-        <v>0.001719022879661631</v>
+        <v>0.01693265755097047</v>
       </c>
       <c r="S418" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U418" t="inlineStr">
-        <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
-        </is>
-      </c>
       <c r="AA418" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -78311,70 +78308,70 @@
       </c>
       <c r="AO418" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP418" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ418" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS418" t="inlineStr">
         <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_A</t>
         </is>
       </c>
       <c r="AT418" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU418" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV418" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW418" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX418" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY418" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ418" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA418" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB418" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC418" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -78406,12 +78403,12 @@
       </c>
       <c r="F419" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G419" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H419" t="inlineStr">
@@ -78436,7 +78433,7 @@
       </c>
       <c r="L419" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M419" t="inlineStr">
@@ -78445,32 +78442,32 @@
         </is>
       </c>
       <c r="N419" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="O419" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="P419" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="U419" t="inlineStr">
         <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A</t>
         </is>
       </c>
       <c r="V419" t="inlineStr">
         <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A</t>
         </is>
       </c>
       <c r="W419" t="inlineStr">
         <is>
-          <t>SRC_US_NNDSS</t>
+          <t>SRC_SG_CDA_WIDB</t>
         </is>
       </c>
       <c r="X419" t="inlineStr">
         <is>
-          <t>Hepatitis A, Confirmed</t>
+          <t>Acute Viral Hepatitis A</t>
         </is>
       </c>
       <c r="Y419" t="inlineStr">
@@ -78480,7 +78477,7 @@
       </c>
       <c r="Z419" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA419" t="inlineStr">
@@ -78495,7 +78492,7 @@
       </c>
       <c r="AC419" t="inlineStr">
         <is>
-          <t>country:US:national</t>
+          <t>country:SG:national</t>
         </is>
       </c>
       <c r="AD419" t="inlineStr">
@@ -78510,7 +78507,7 @@
       </c>
       <c r="AF419" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>conditional</t>
         </is>
       </c>
       <c r="AG419" t="inlineStr">
@@ -78530,17 +78527,17 @@
       </c>
       <c r="AJ419" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
         </is>
       </c>
       <c r="AK419" t="inlineStr">
         <is>
-          <t>Confirmed hepatitis A component reported by NNDSS.</t>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
         </is>
       </c>
       <c r="AM419" t="inlineStr">
         <is>
-          <t>provisional</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN419" t="b">
@@ -78548,70 +78545,70 @@
       </c>
       <c r="AO419" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP419" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ419" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS419" t="inlineStr">
         <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_A</t>
         </is>
       </c>
       <c r="AT419" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU419" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV419" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW419" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX419" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY419" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ419" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA419" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB419" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC419" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -78643,12 +78640,12 @@
       </c>
       <c r="F420" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G420" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H420" t="inlineStr">
@@ -78673,7 +78670,7 @@
       </c>
       <c r="L420" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="M420" t="inlineStr">
@@ -78682,81 +78679,98 @@
         </is>
       </c>
       <c r="N420" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="O420" t="n">
-        <v>11</v>
+        <v>6</v>
+      </c>
+      <c r="P420" t="n">
+        <v>6</v>
       </c>
       <c r="R420" t="n">
-        <v>0.00898489248322343</v>
+        <v>0.001719022879661631</v>
       </c>
       <c r="S420" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U420" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AA420" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO420" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP420" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR420" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS420" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ420" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS420" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
       <c r="AT420" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU420" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV420" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW420" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX420" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY420" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ420" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA420" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB420" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC420" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -78783,17 +78797,17 @@
       </c>
       <c r="E421" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F421" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G421" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H421" t="inlineStr">
@@ -78818,7 +78832,7 @@
       </c>
       <c r="L421" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="M421" t="inlineStr">
@@ -78827,20 +78841,42 @@
         </is>
       </c>
       <c r="N421" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O421" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="P421" t="n">
-        <v>2</v>
-      </c>
-      <c r="R421" t="n">
-        <v>0.03386531510194095</v>
-      </c>
-      <c r="S421" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+        <v>6</v>
+      </c>
+      <c r="U421" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="V421" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="W421" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X421" t="inlineStr">
+        <is>
+          <t>Hepatitis A, Confirmed</t>
+        </is>
+      </c>
+      <c r="Y421" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z421" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA421" t="inlineStr">
@@ -78848,72 +78884,130 @@
           <t>weekly</t>
         </is>
       </c>
+      <c r="AB421" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC421" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD421" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE421" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF421" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG421" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH421" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI421" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ421" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK421" t="inlineStr">
+        <is>
+          <t>Confirmed hepatitis A component reported by NNDSS.</t>
+        </is>
+      </c>
+      <c r="AM421" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN421" t="b">
+        <v>1</v>
+      </c>
       <c r="AO421" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP421" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ421" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS421" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_A</t>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
         </is>
       </c>
       <c r="AT421" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU421" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV421" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW421" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX421" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY421" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ421" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA421" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB421" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC421" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -78940,17 +79034,17 @@
       </c>
       <c r="E422" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F422" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G422" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H422" t="inlineStr">
@@ -78984,173 +79078,81 @@
         </is>
       </c>
       <c r="N422" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="O422" t="n">
-        <v>2</v>
-      </c>
-      <c r="P422" t="n">
-        <v>2</v>
-      </c>
-      <c r="U422" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A</t>
-        </is>
-      </c>
-      <c r="V422" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A</t>
-        </is>
-      </c>
-      <c r="W422" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X422" t="inlineStr">
-        <is>
-          <t>Acute Viral Hepatitis A</t>
-        </is>
-      </c>
-      <c r="Y422" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z422" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA422" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB422" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC422" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD422" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE422" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF422" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG422" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH422" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI422" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ422" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK422" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM422" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN422" t="b">
-        <v>1</v>
+        <v>11</v>
+      </c>
+      <c r="R422" t="n">
+        <v>0.00898489248322343</v>
+      </c>
+      <c r="S422" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO422" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP422" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ422" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS422" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_A</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR422" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS422" t="inlineStr"/>
       <c r="AT422" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU422" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV422" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW422" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX422" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY422" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ422" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA422" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB422" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC422" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -79182,12 +79184,12 @@
       </c>
       <c r="F423" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G423" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H423" t="inlineStr">
@@ -79212,7 +79214,7 @@
       </c>
       <c r="L423" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M423" t="inlineStr">
@@ -79221,27 +79223,22 @@
         </is>
       </c>
       <c r="N423" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="O423" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="P423" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="R423" t="n">
-        <v>0.002578534319492447</v>
+        <v>0.03386531510194095</v>
       </c>
       <c r="S423" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U423" t="inlineStr">
-        <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
-        </is>
-      </c>
       <c r="AA423" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -79249,70 +79246,70 @@
       </c>
       <c r="AO423" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP423" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ423" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS423" t="inlineStr">
         <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_A</t>
         </is>
       </c>
       <c r="AT423" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU423" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV423" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW423" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX423" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY423" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ423" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA423" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB423" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC423" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -79344,12 +79341,12 @@
       </c>
       <c r="F424" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G424" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H424" t="inlineStr">
@@ -79374,7 +79371,7 @@
       </c>
       <c r="L424" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M424" t="inlineStr">
@@ -79383,32 +79380,32 @@
         </is>
       </c>
       <c r="N424" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="O424" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="P424" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="U424" t="inlineStr">
         <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A</t>
         </is>
       </c>
       <c r="V424" t="inlineStr">
         <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A</t>
         </is>
       </c>
       <c r="W424" t="inlineStr">
         <is>
-          <t>SRC_US_NNDSS</t>
+          <t>SRC_SG_CDA_WIDB</t>
         </is>
       </c>
       <c r="X424" t="inlineStr">
         <is>
-          <t>Hepatitis A, Confirmed</t>
+          <t>Acute Viral Hepatitis A</t>
         </is>
       </c>
       <c r="Y424" t="inlineStr">
@@ -79418,7 +79415,7 @@
       </c>
       <c r="Z424" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA424" t="inlineStr">
@@ -79433,7 +79430,7 @@
       </c>
       <c r="AC424" t="inlineStr">
         <is>
-          <t>country:US:national</t>
+          <t>country:SG:national</t>
         </is>
       </c>
       <c r="AD424" t="inlineStr">
@@ -79448,7 +79445,7 @@
       </c>
       <c r="AF424" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>conditional</t>
         </is>
       </c>
       <c r="AG424" t="inlineStr">
@@ -79468,17 +79465,17 @@
       </c>
       <c r="AJ424" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
         </is>
       </c>
       <c r="AK424" t="inlineStr">
         <is>
-          <t>Confirmed hepatitis A component reported by NNDSS.</t>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
         </is>
       </c>
       <c r="AM424" t="inlineStr">
         <is>
-          <t>provisional</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN424" t="b">
@@ -79486,70 +79483,70 @@
       </c>
       <c r="AO424" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP424" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ424" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS424" t="inlineStr">
         <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_A</t>
         </is>
       </c>
       <c r="AT424" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU424" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV424" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW424" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX424" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY424" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ424" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA424" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB424" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC424" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -79581,12 +79578,12 @@
       </c>
       <c r="F425" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G425" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H425" t="inlineStr">
@@ -79611,7 +79608,7 @@
       </c>
       <c r="L425" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="M425" t="inlineStr">
@@ -79620,81 +79617,98 @@
         </is>
       </c>
       <c r="N425" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O425" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="P425" t="n">
+        <v>9</v>
       </c>
       <c r="R425" t="n">
-        <v>0.00653446726052613</v>
+        <v>0.002578534319492447</v>
       </c>
       <c r="S425" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U425" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AA425" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO425" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP425" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR425" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS425" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ425" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS425" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
       <c r="AT425" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU425" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV425" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW425" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX425" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY425" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ425" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA425" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB425" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC425" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -79721,17 +79735,17 @@
       </c>
       <c r="E426" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F426" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G426" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H426" t="inlineStr">
@@ -79756,7 +79770,7 @@
       </c>
       <c r="L426" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="M426" t="inlineStr">
@@ -79765,93 +79779,173 @@
         </is>
       </c>
       <c r="N426" t="n">
+        <v>9</v>
+      </c>
+      <c r="O426" t="n">
+        <v>9</v>
+      </c>
+      <c r="P426" t="n">
+        <v>9</v>
+      </c>
+      <c r="U426" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="V426" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="W426" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X426" t="inlineStr">
+        <is>
+          <t>Hepatitis A, Confirmed</t>
+        </is>
+      </c>
+      <c r="Y426" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z426" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA426" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB426" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC426" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD426" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE426" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF426" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG426" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH426" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI426" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ426" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK426" t="inlineStr">
+        <is>
+          <t>Confirmed hepatitis A component reported by NNDSS.</t>
+        </is>
+      </c>
+      <c r="AM426" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN426" t="b">
         <v>1</v>
       </c>
-      <c r="O426" t="n">
+      <c r="AO426" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP426" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ426" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS426" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AT426" t="n">
         <v>1</v>
       </c>
-      <c r="P426" t="n">
-        <v>1</v>
-      </c>
-      <c r="R426" t="n">
-        <v>0.01693265755097047</v>
-      </c>
-      <c r="S426" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AA426" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AO426" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP426" t="inlineStr">
-        <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ426" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS426" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_A</t>
-        </is>
-      </c>
-      <c r="AT426" t="n">
-        <v>2</v>
-      </c>
       <c r="AU426" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV426" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW426" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX426" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY426" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ426" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA426" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB426" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC426" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -79878,17 +79972,17 @@
       </c>
       <c r="E427" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F427" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G427" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H427" t="inlineStr">
@@ -79922,173 +80016,81 @@
         </is>
       </c>
       <c r="N427" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="O427" t="n">
-        <v>1</v>
-      </c>
-      <c r="P427" t="n">
-        <v>1</v>
-      </c>
-      <c r="U427" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A</t>
-        </is>
-      </c>
-      <c r="V427" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A</t>
-        </is>
-      </c>
-      <c r="W427" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X427" t="inlineStr">
-        <is>
-          <t>Acute Viral Hepatitis A</t>
-        </is>
-      </c>
-      <c r="Y427" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z427" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA427" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB427" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC427" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD427" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE427" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF427" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG427" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH427" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI427" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ427" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK427" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM427" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN427" t="b">
-        <v>1</v>
+        <v>8</v>
+      </c>
+      <c r="R427" t="n">
+        <v>0.00653446726052613</v>
+      </c>
+      <c r="S427" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO427" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP427" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ427" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS427" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_A</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR427" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS427" t="inlineStr"/>
       <c r="AT427" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU427" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV427" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW427" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX427" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY427" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ427" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA427" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB427" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC427" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -80120,12 +80122,12 @@
       </c>
       <c r="F428" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G428" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H428" t="inlineStr">
@@ -80150,7 +80152,7 @@
       </c>
       <c r="L428" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M428" t="inlineStr">
@@ -80159,27 +80161,22 @@
         </is>
       </c>
       <c r="N428" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O428" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P428" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R428" t="n">
-        <v>0.0008595114398308156</v>
+        <v>0.01693265755097047</v>
       </c>
       <c r="S428" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U428" t="inlineStr">
-        <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
-        </is>
-      </c>
       <c r="AA428" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -80187,70 +80184,70 @@
       </c>
       <c r="AO428" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP428" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ428" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS428" t="inlineStr">
         <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_A</t>
         </is>
       </c>
       <c r="AT428" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU428" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV428" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW428" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX428" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY428" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ428" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA428" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB428" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC428" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -80282,12 +80279,12 @@
       </c>
       <c r="F429" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G429" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H429" t="inlineStr">
@@ -80312,7 +80309,7 @@
       </c>
       <c r="L429" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M429" t="inlineStr">
@@ -80321,32 +80318,32 @@
         </is>
       </c>
       <c r="N429" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O429" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P429" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U429" t="inlineStr">
         <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A</t>
         </is>
       </c>
       <c r="V429" t="inlineStr">
         <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A</t>
         </is>
       </c>
       <c r="W429" t="inlineStr">
         <is>
-          <t>SRC_US_NNDSS</t>
+          <t>SRC_SG_CDA_WIDB</t>
         </is>
       </c>
       <c r="X429" t="inlineStr">
         <is>
-          <t>Hepatitis A, Confirmed</t>
+          <t>Acute Viral Hepatitis A</t>
         </is>
       </c>
       <c r="Y429" t="inlineStr">
@@ -80356,7 +80353,7 @@
       </c>
       <c r="Z429" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA429" t="inlineStr">
@@ -80371,7 +80368,7 @@
       </c>
       <c r="AC429" t="inlineStr">
         <is>
-          <t>country:US:national</t>
+          <t>country:SG:national</t>
         </is>
       </c>
       <c r="AD429" t="inlineStr">
@@ -80386,7 +80383,7 @@
       </c>
       <c r="AF429" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>conditional</t>
         </is>
       </c>
       <c r="AG429" t="inlineStr">
@@ -80406,17 +80403,17 @@
       </c>
       <c r="AJ429" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
         </is>
       </c>
       <c r="AK429" t="inlineStr">
         <is>
-          <t>Confirmed hepatitis A component reported by NNDSS.</t>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
         </is>
       </c>
       <c r="AM429" t="inlineStr">
         <is>
-          <t>provisional</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN429" t="b">
@@ -80424,70 +80421,70 @@
       </c>
       <c r="AO429" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP429" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ429" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS429" t="inlineStr">
         <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_A</t>
         </is>
       </c>
       <c r="AT429" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU429" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV429" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW429" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX429" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY429" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ429" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA429" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB429" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC429" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -80519,12 +80516,12 @@
       </c>
       <c r="F430" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G430" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H430" t="inlineStr">
@@ -80549,7 +80546,7 @@
       </c>
       <c r="L430" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="M430" t="inlineStr">
@@ -80558,81 +80555,98 @@
         </is>
       </c>
       <c r="N430" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="O430" t="n">
-        <v>21</v>
+        <v>3</v>
+      </c>
+      <c r="P430" t="n">
+        <v>3</v>
       </c>
       <c r="R430" t="n">
-        <v>0.01715297655888109</v>
+        <v>0.0008595114398308156</v>
       </c>
       <c r="S430" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U430" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AA430" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO430" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP430" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR430" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS430" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ430" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS430" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
       <c r="AT430" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU430" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV430" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW430" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX430" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY430" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ430" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA430" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB430" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC430" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -80659,17 +80673,17 @@
       </c>
       <c r="E431" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F431" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G431" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H431" t="inlineStr">
@@ -80694,7 +80708,7 @@
       </c>
       <c r="L431" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="M431" t="inlineStr">
@@ -80703,20 +80717,42 @@
         </is>
       </c>
       <c r="N431" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O431" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P431" t="n">
-        <v>0</v>
-      </c>
-      <c r="R431" t="n">
-        <v>0</v>
-      </c>
-      <c r="S431" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+        <v>3</v>
+      </c>
+      <c r="U431" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="V431" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="W431" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X431" t="inlineStr">
+        <is>
+          <t>Hepatitis A, Confirmed</t>
+        </is>
+      </c>
+      <c r="Y431" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z431" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA431" t="inlineStr">
@@ -80724,72 +80760,130 @@
           <t>weekly</t>
         </is>
       </c>
+      <c r="AB431" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC431" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD431" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE431" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF431" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG431" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH431" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI431" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ431" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK431" t="inlineStr">
+        <is>
+          <t>Confirmed hepatitis A component reported by NNDSS.</t>
+        </is>
+      </c>
+      <c r="AM431" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN431" t="b">
+        <v>1</v>
+      </c>
       <c r="AO431" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP431" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ431" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS431" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_A</t>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
         </is>
       </c>
       <c r="AT431" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU431" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV431" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW431" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX431" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY431" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ431" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA431" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB431" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC431" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -80816,17 +80910,17 @@
       </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F432" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G432" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H432" t="inlineStr">
@@ -80860,173 +80954,81 @@
         </is>
       </c>
       <c r="N432" t="n">
+        <v>21</v>
+      </c>
+      <c r="O432" t="n">
+        <v>21</v>
+      </c>
+      <c r="R432" t="n">
+        <v>0.01715297655888109</v>
+      </c>
+      <c r="S432" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO432" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP432" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR432" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS432" t="inlineStr"/>
+      <c r="AT432" t="n">
         <v>0</v>
       </c>
-      <c r="O432" t="n">
-        <v>0</v>
-      </c>
-      <c r="P432" t="n">
-        <v>0</v>
-      </c>
-      <c r="U432" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A</t>
-        </is>
-      </c>
-      <c r="V432" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A</t>
-        </is>
-      </c>
-      <c r="W432" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X432" t="inlineStr">
-        <is>
-          <t>Acute Viral Hepatitis A</t>
-        </is>
-      </c>
-      <c r="Y432" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z432" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA432" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB432" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC432" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD432" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE432" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF432" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG432" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH432" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI432" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ432" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK432" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM432" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN432" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO432" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP432" t="inlineStr">
-        <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ432" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS432" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_A</t>
-        </is>
-      </c>
-      <c r="AT432" t="n">
-        <v>2</v>
-      </c>
       <c r="AU432" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV432" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW432" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX432" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY432" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ432" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA432" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB432" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC432" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -81058,12 +81060,12 @@
       </c>
       <c r="F433" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G433" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H433" t="inlineStr">
@@ -81088,7 +81090,7 @@
       </c>
       <c r="L433" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M433" t="inlineStr">
@@ -81097,27 +81099,22 @@
         </is>
       </c>
       <c r="N433" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O433" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P433" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="R433" t="n">
-        <v>0.001719022879661631</v>
+        <v>0</v>
       </c>
       <c r="S433" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U433" t="inlineStr">
-        <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
-        </is>
-      </c>
       <c r="AA433" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -81125,70 +81122,70 @@
       </c>
       <c r="AO433" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP433" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ433" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS433" t="inlineStr">
         <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_A</t>
         </is>
       </c>
       <c r="AT433" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU433" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV433" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW433" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX433" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY433" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ433" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA433" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB433" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC433" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -81220,12 +81217,12 @@
       </c>
       <c r="F434" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G434" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H434" t="inlineStr">
@@ -81250,7 +81247,7 @@
       </c>
       <c r="L434" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M434" t="inlineStr">
@@ -81259,32 +81256,32 @@
         </is>
       </c>
       <c r="N434" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O434" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P434" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="U434" t="inlineStr">
         <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A</t>
         </is>
       </c>
       <c r="V434" t="inlineStr">
         <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A</t>
         </is>
       </c>
       <c r="W434" t="inlineStr">
         <is>
-          <t>SRC_US_NNDSS</t>
+          <t>SRC_SG_CDA_WIDB</t>
         </is>
       </c>
       <c r="X434" t="inlineStr">
         <is>
-          <t>Hepatitis A, Confirmed</t>
+          <t>Acute Viral Hepatitis A</t>
         </is>
       </c>
       <c r="Y434" t="inlineStr">
@@ -81294,7 +81291,7 @@
       </c>
       <c r="Z434" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA434" t="inlineStr">
@@ -81309,7 +81306,7 @@
       </c>
       <c r="AC434" t="inlineStr">
         <is>
-          <t>country:US:national</t>
+          <t>country:SG:national</t>
         </is>
       </c>
       <c r="AD434" t="inlineStr">
@@ -81324,7 +81321,7 @@
       </c>
       <c r="AF434" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>conditional</t>
         </is>
       </c>
       <c r="AG434" t="inlineStr">
@@ -81344,17 +81341,17 @@
       </c>
       <c r="AJ434" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
         </is>
       </c>
       <c r="AK434" t="inlineStr">
         <is>
-          <t>Confirmed hepatitis A component reported by NNDSS.</t>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
         </is>
       </c>
       <c r="AM434" t="inlineStr">
         <is>
-          <t>provisional</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN434" t="b">
@@ -81362,70 +81359,70 @@
       </c>
       <c r="AO434" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP434" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ434" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS434" t="inlineStr">
         <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_A</t>
         </is>
       </c>
       <c r="AT434" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU434" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV434" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW434" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX434" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY434" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ434" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA434" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB434" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC434" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -81457,12 +81454,12 @@
       </c>
       <c r="F435" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G435" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H435" t="inlineStr">
@@ -81487,7 +81484,7 @@
       </c>
       <c r="L435" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="M435" t="inlineStr">
@@ -81496,81 +81493,98 @@
         </is>
       </c>
       <c r="N435" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="O435" t="n">
-        <v>19</v>
+        <v>6</v>
+      </c>
+      <c r="P435" t="n">
+        <v>6</v>
       </c>
       <c r="R435" t="n">
-        <v>0.01551935974374956</v>
+        <v>0.001719022879661631</v>
       </c>
       <c r="S435" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U435" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AA435" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO435" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP435" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR435" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS435" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ435" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS435" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
       <c r="AT435" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU435" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV435" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW435" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX435" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY435" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ435" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA435" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB435" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC435" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -81597,17 +81611,17 @@
       </c>
       <c r="E436" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F436" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G436" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H436" t="inlineStr">
@@ -81632,90 +81646,182 @@
       </c>
       <c r="L436" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="M436" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N436" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O436" t="n">
-        <v>0</v>
-      </c>
-      <c r="R436" t="n">
-        <v>0</v>
-      </c>
-      <c r="S436" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>6</v>
+      </c>
+      <c r="P436" t="n">
+        <v>6</v>
+      </c>
+      <c r="U436" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="V436" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="W436" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X436" t="inlineStr">
+        <is>
+          <t>Hepatitis A, Confirmed</t>
+        </is>
+      </c>
+      <c r="Y436" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z436" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA436" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB436" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC436" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD436" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE436" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF436" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG436" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH436" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI436" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ436" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK436" t="inlineStr">
+        <is>
+          <t>Confirmed hepatitis A component reported by NNDSS.</t>
+        </is>
+      </c>
+      <c r="AM436" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN436" t="b">
+        <v>1</v>
       </c>
       <c r="AO436" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP436" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR436" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS436" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ436" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS436" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
       <c r="AT436" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU436" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV436" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW436" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX436" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY436" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ436" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA436" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB436" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC436" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -81747,12 +81853,12 @@
       </c>
       <c r="F437" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G437" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H437" t="inlineStr">
@@ -81777,109 +81883,90 @@
       </c>
       <c r="L437" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M437" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N437" t="n">
+        <v>19</v>
+      </c>
+      <c r="O437" t="n">
+        <v>19</v>
+      </c>
+      <c r="R437" t="n">
+        <v>0.01551935974374956</v>
+      </c>
+      <c r="S437" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO437" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP437" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR437" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS437" t="inlineStr"/>
+      <c r="AT437" t="n">
         <v>0</v>
       </c>
-      <c r="O437" t="n">
-        <v>0</v>
-      </c>
-      <c r="R437" t="n">
-        <v>0</v>
-      </c>
-      <c r="S437" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U437" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_115</t>
-        </is>
-      </c>
-      <c r="AA437" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AO437" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP437" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ437" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR437" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS437" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_115</t>
-        </is>
-      </c>
-      <c r="AT437" t="n">
-        <v>2</v>
-      </c>
       <c r="AU437" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV437" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW437" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX437" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY437" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ437" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA437" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB437" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC437" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -81906,17 +81993,17 @@
       </c>
       <c r="E438" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F438" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G438" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H438" t="inlineStr">
@@ -81941,112 +82028,35 @@
       </c>
       <c r="L438" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M438" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N438" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O438" t="n">
-        <v>0</v>
-      </c>
-      <c r="U438" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_115</t>
-        </is>
-      </c>
-      <c r="V438" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_115</t>
-        </is>
-      </c>
-      <c r="W438" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X438" t="inlineStr">
-        <is>
-          <t>Hepatitis A</t>
-        </is>
-      </c>
-      <c r="Y438" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z438" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
+        <v>2</v>
+      </c>
+      <c r="P438" t="n">
+        <v>2</v>
+      </c>
+      <c r="R438" t="n">
+        <v>0.03386531510194095</v>
+      </c>
+      <c r="S438" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA438" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB438" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC438" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD438" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE438" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF438" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG438" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH438" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI438" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ438" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK438" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 115.</t>
-        </is>
-      </c>
-      <c r="AM438" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN438" t="b">
-        <v>1</v>
+          <t>weekly</t>
+        </is>
       </c>
       <c r="AO438" t="inlineStr">
         <is>
@@ -82055,22 +82065,17 @@
       </c>
       <c r="AP438" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ438" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR438" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS438" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_115</t>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_A</t>
         </is>
       </c>
       <c r="AT438" t="n">
@@ -82078,47 +82083,47 @@
       </c>
       <c r="AU438" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV438" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW438" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX438" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY438" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ438" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA438" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB438" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC438" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -82145,17 +82150,17 @@
       </c>
       <c r="E439" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F439" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G439" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H439" t="inlineStr">
@@ -82180,90 +82185,182 @@
       </c>
       <c r="L439" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M439" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N439" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="O439" t="n">
-        <v>23</v>
-      </c>
-      <c r="R439" t="n">
-        <v>0.04457330824721705</v>
-      </c>
-      <c r="S439" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="P439" t="n">
+        <v>2</v>
+      </c>
+      <c r="U439" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A</t>
+        </is>
+      </c>
+      <c r="V439" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A</t>
+        </is>
+      </c>
+      <c r="W439" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X439" t="inlineStr">
+        <is>
+          <t>Acute Viral Hepatitis A</t>
+        </is>
+      </c>
+      <c r="Y439" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z439" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA439" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB439" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC439" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD439" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE439" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF439" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG439" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH439" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI439" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ439" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK439" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM439" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN439" t="b">
+        <v>1</v>
       </c>
       <c r="AO439" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP439" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR439" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS439" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ439" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS439" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_A</t>
+        </is>
+      </c>
       <c r="AT439" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU439" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV439" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW439" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX439" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY439" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ439" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA439" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB439" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC439" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -82295,12 +82392,12 @@
       </c>
       <c r="F440" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G440" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H440" t="inlineStr">
@@ -82334,100 +82431,81 @@
         </is>
       </c>
       <c r="N440" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O440" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R440" t="n">
-        <v>0.07075903303182025</v>
+        <v>0</v>
       </c>
       <c r="S440" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U440" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_201_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA440" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO440" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP440" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ440" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR440" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS440" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_201_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS440" t="inlineStr"/>
       <c r="AT440" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU440" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV440" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW440" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX440" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY440" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ440" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA440" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB440" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC440" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -82454,17 +82532,17 @@
       </c>
       <c r="E441" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F441" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G441" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H441" t="inlineStr">
@@ -82498,39 +82576,22 @@
         </is>
       </c>
       <c r="N441" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O441" t="n">
-        <v>4</v>
+        <v>0</v>
+      </c>
+      <c r="R441" t="n">
+        <v>0</v>
+      </c>
+      <c r="S441" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U441" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_201_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V441" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_201_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W441" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X441" t="inlineStr">
-        <is>
-          <t>Hepatitt A</t>
-        </is>
-      </c>
-      <c r="Y441" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z441" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>SER_FI_THL_TTR_115</t>
         </is>
       </c>
       <c r="AA441" t="inlineStr">
@@ -82538,64 +82599,6 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB441" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC441" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD441" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE441" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF441" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG441" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH441" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI441" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ441" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK441" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM441" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN441" t="b">
-        <v>1</v>
-      </c>
       <c r="AO441" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -82608,7 +82611,7 @@
       </c>
       <c r="AQ441" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR441" t="inlineStr">
@@ -82618,7 +82621,7 @@
       </c>
       <c r="AS441" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_201_MONTHLY</t>
+          <t>SER_FI_THL_TTR_115</t>
         </is>
       </c>
       <c r="AT441" t="n">
@@ -82626,47 +82629,1233 @@
       </c>
       <c r="AU441" t="inlineStr">
         <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV441" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW441" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX441" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY441" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ441" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA441" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB441" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC441" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>D007</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>hepatitis-a</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>Hepatitis A</t>
+        </is>
+      </c>
+      <c r="E442" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F442" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G442" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H442" t="inlineStr">
+        <is>
+          <t>D007</t>
+        </is>
+      </c>
+      <c r="I442" t="inlineStr">
+        <is>
+          <t>Hepatitis A</t>
+        </is>
+      </c>
+      <c r="J442" t="inlineStr">
+        <is>
+          <t>甲型肝炎</t>
+        </is>
+      </c>
+      <c r="K442" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L442" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M442" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N442" t="n">
+        <v>0</v>
+      </c>
+      <c r="O442" t="n">
+        <v>0</v>
+      </c>
+      <c r="U442" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_115</t>
+        </is>
+      </c>
+      <c r="V442" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_115</t>
+        </is>
+      </c>
+      <c r="W442" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X442" t="inlineStr">
+        <is>
+          <t>Hepatitis A</t>
+        </is>
+      </c>
+      <c r="Y442" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z442" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA442" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB442" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC442" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD442" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE442" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF442" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG442" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH442" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI442" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ442" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK442" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 115.</t>
+        </is>
+      </c>
+      <c r="AM442" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN442" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO442" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP442" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ442" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR442" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS442" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_115</t>
+        </is>
+      </c>
+      <c r="AT442" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU442" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV442" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW442" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX442" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY442" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ442" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA442" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB442" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC442" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>D007</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>hepatitis-a</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>Hepatitis A</t>
+        </is>
+      </c>
+      <c r="E443" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F443" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G443" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H443" t="inlineStr">
+        <is>
+          <t>D007</t>
+        </is>
+      </c>
+      <c r="I443" t="inlineStr">
+        <is>
+          <t>Hepatitis A</t>
+        </is>
+      </c>
+      <c r="J443" t="inlineStr">
+        <is>
+          <t>甲型肝炎</t>
+        </is>
+      </c>
+      <c r="K443" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L443" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M443" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N443" t="n">
+        <v>23</v>
+      </c>
+      <c r="O443" t="n">
+        <v>23</v>
+      </c>
+      <c r="R443" t="n">
+        <v>0.04457330824721705</v>
+      </c>
+      <c r="S443" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO443" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP443" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR443" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS443" t="inlineStr"/>
+      <c r="AT443" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU443" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV443" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW443" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX443" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY443" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ443" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA443" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB443" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC443" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>D007</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>hepatitis-a</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>Hepatitis A</t>
+        </is>
+      </c>
+      <c r="E444" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F444" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G444" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H444" t="inlineStr">
+        <is>
+          <t>D007</t>
+        </is>
+      </c>
+      <c r="I444" t="inlineStr">
+        <is>
+          <t>Hepatitis A</t>
+        </is>
+      </c>
+      <c r="J444" t="inlineStr">
+        <is>
+          <t>甲型肝炎</t>
+        </is>
+      </c>
+      <c r="K444" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L444" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M444" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N444" t="n">
+        <v>4</v>
+      </c>
+      <c r="O444" t="n">
+        <v>4</v>
+      </c>
+      <c r="R444" t="n">
+        <v>0.07075903303182025</v>
+      </c>
+      <c r="S444" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U444" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_201_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA444" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO444" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP444" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ444" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR444" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS444" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_201_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT444" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU444" t="inlineStr">
+        <is>
           <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
-      <c r="AV441" t="inlineStr">
+      <c r="AV444" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="AW441" t="inlineStr">
+      <c r="AW444" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="AX441" t="inlineStr">
+      <c r="AX444" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="AY441" t="inlineStr">
+      <c r="AY444" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
       </c>
-      <c r="AZ441" t="inlineStr">
+      <c r="AZ444" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="BA441" t="inlineStr">
+      <c r="BA444" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="BB441" t="inlineStr">
+      <c r="BB444" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="BC441" t="inlineStr">
+      <c r="BC444" t="inlineStr">
         <is>
           <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>D007</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>hepatitis-a</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>Hepatitis A</t>
+        </is>
+      </c>
+      <c r="E445" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F445" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G445" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H445" t="inlineStr">
+        <is>
+          <t>D007</t>
+        </is>
+      </c>
+      <c r="I445" t="inlineStr">
+        <is>
+          <t>Hepatitis A</t>
+        </is>
+      </c>
+      <c r="J445" t="inlineStr">
+        <is>
+          <t>甲型肝炎</t>
+        </is>
+      </c>
+      <c r="K445" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L445" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M445" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N445" t="n">
+        <v>4</v>
+      </c>
+      <c r="O445" t="n">
+        <v>4</v>
+      </c>
+      <c r="U445" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_201_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V445" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_201_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W445" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X445" t="inlineStr">
+        <is>
+          <t>Hepatitt A</t>
+        </is>
+      </c>
+      <c r="Y445" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z445" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA445" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB445" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC445" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD445" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE445" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF445" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG445" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH445" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI445" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ445" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK445" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM445" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN445" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO445" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP445" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ445" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR445" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS445" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_201_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT445" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU445" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV445" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW445" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX445" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY445" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ445" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA445" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB445" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC445" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>D007</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>hepatitis-a</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>Hepatitis A</t>
+        </is>
+      </c>
+      <c r="E446" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F446" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G446" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H446" t="inlineStr">
+        <is>
+          <t>D007</t>
+        </is>
+      </c>
+      <c r="I446" t="inlineStr">
+        <is>
+          <t>Hepatitis A</t>
+        </is>
+      </c>
+      <c r="J446" t="inlineStr">
+        <is>
+          <t>甲型肝炎</t>
+        </is>
+      </c>
+      <c r="K446" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L446" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="M446" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N446" t="n">
+        <v>7</v>
+      </c>
+      <c r="O446" t="n">
+        <v>7</v>
+      </c>
+      <c r="P446" t="n">
+        <v>7</v>
+      </c>
+      <c r="R446" t="n">
+        <v>0.00200552669293857</v>
+      </c>
+      <c r="S446" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U446" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AA446" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO446" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP446" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ446" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS446" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AT446" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU446" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV446" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW446" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX446" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY446" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ446" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA446" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB446" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC446" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>D007</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>hepatitis-a</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>Hepatitis A</t>
+        </is>
+      </c>
+      <c r="E447" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F447" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G447" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H447" t="inlineStr">
+        <is>
+          <t>D007</t>
+        </is>
+      </c>
+      <c r="I447" t="inlineStr">
+        <is>
+          <t>Hepatitis A</t>
+        </is>
+      </c>
+      <c r="J447" t="inlineStr">
+        <is>
+          <t>甲型肝炎</t>
+        </is>
+      </c>
+      <c r="K447" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L447" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="M447" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N447" t="n">
+        <v>7</v>
+      </c>
+      <c r="O447" t="n">
+        <v>7</v>
+      </c>
+      <c r="P447" t="n">
+        <v>7</v>
+      </c>
+      <c r="U447" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="V447" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="W447" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X447" t="inlineStr">
+        <is>
+          <t>Hepatitis A, Confirmed</t>
+        </is>
+      </c>
+      <c r="Y447" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z447" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA447" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB447" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC447" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD447" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE447" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF447" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG447" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH447" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI447" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ447" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK447" t="inlineStr">
+        <is>
+          <t>Confirmed hepatitis A component reported by NNDSS.</t>
+        </is>
+      </c>
+      <c r="AM447" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN447" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO447" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP447" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ447" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS447" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AT447" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU447" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV447" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW447" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX447" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY447" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ447" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA447" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB447" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC447" t="inlineStr">
+        <is>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -82703,7 +83892,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
@@ -82786,7 +83975,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>265</v>
+        <v>268</v>
       </c>
     </row>
     <row r="10">
@@ -82796,7 +83985,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>440</v>
+        <v>446</v>
       </c>
     </row>
     <row r="11">
@@ -82816,7 +84005,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>175</v>
+        <v>178</v>
       </c>
     </row>
     <row r="13">
@@ -82848,7 +84037,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>17665</v>
+        <v>19058</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d007/2026-2029.xlsx
+++ b/diseases/d007/2026-2029.xlsx
@@ -76932,13 +76932,13 @@
         </is>
       </c>
       <c r="N411" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="O411" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="R411" t="n">
-        <v>0.251936090092966</v>
+        <v>0.2499981201691739</v>
       </c>
       <c r="S411" t="inlineStr">
         <is>
@@ -83111,13 +83111,13 @@
         </is>
       </c>
       <c r="N444" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O444" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R444" t="n">
-        <v>0</v>
+        <v>0.01778809170864137</v>
       </c>
       <c r="S444" t="inlineStr">
         <is>
@@ -83275,10 +83275,10 @@
         </is>
       </c>
       <c r="N445" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O445" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U445" t="inlineStr">
         <is>
@@ -83514,13 +83514,13 @@
         </is>
       </c>
       <c r="N446" t="n">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="O446" t="n">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="R446" t="n">
-        <v>0.04457330824721705</v>
+        <v>0.06589097740892956</v>
       </c>
       <c r="S446" t="inlineStr">
         <is>
@@ -84572,7 +84572,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>19078</v>
+        <v>19089</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d007/2026-2029.xlsx
+++ b/diseases/d007/2026-2029.xlsx
@@ -75133,13 +75133,13 @@
         </is>
       </c>
       <c r="N400" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="O400" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="R400" t="n">
-        <v>0.06243780093183643</v>
+        <v>0.07712904820991559</v>
       </c>
       <c r="S400" t="inlineStr">
         <is>
@@ -84572,7 +84572,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>19089</v>
+        <v>19093</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d007/2026-2029.xlsx
+++ b/diseases/d007/2026-2029.xlsx
@@ -76932,13 +76932,13 @@
         </is>
       </c>
       <c r="N411" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="O411" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="R411" t="n">
-        <v>0.2499981201691739</v>
+        <v>0.251936090092966</v>
       </c>
       <c r="S411" t="inlineStr">
         <is>
@@ -83111,13 +83111,13 @@
         </is>
       </c>
       <c r="N444" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O444" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R444" t="n">
-        <v>0.01778809170864137</v>
+        <v>0.03557618341728275</v>
       </c>
       <c r="S444" t="inlineStr">
         <is>
@@ -83275,10 +83275,10 @@
         </is>
       </c>
       <c r="N445" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O445" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U445" t="inlineStr">
         <is>
@@ -83514,13 +83514,13 @@
         </is>
       </c>
       <c r="N446" t="n">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="O446" t="n">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="R446" t="n">
-        <v>0.06589097740892956</v>
+        <v>0.09108458641822616</v>
       </c>
       <c r="S446" t="inlineStr">
         <is>
@@ -84391,6 +84391,151 @@
       <c r="BC450" t="inlineStr">
         <is>
           <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>D007</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>hepatitis-a</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>Hepatitis A</t>
+        </is>
+      </c>
+      <c r="E451" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F451" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G451" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H451" t="inlineStr">
+        <is>
+          <t>D007</t>
+        </is>
+      </c>
+      <c r="I451" t="inlineStr">
+        <is>
+          <t>Hepatitis A</t>
+        </is>
+      </c>
+      <c r="J451" t="inlineStr">
+        <is>
+          <t>甲型肝炎</t>
+        </is>
+      </c>
+      <c r="K451" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L451" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M451" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N451" t="n">
+        <v>10</v>
+      </c>
+      <c r="O451" t="n">
+        <v>10</v>
+      </c>
+      <c r="R451" t="n">
+        <v>0.008168084075657663</v>
+      </c>
+      <c r="S451" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO451" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP451" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR451" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS451" t="inlineStr"/>
+      <c r="AT451" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU451" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV451" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW451" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX451" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY451" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ451" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA451" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB451" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC451" t="inlineStr">
+        <is>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -84427,7 +84572,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -84510,7 +84655,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="10">
@@ -84520,7 +84665,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="11">
@@ -84572,7 +84717,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>19093</v>
+        <v>19118</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d007/2026-2029.xlsx
+++ b/diseases/d007/2026-2029.xlsx
@@ -69499,13 +69499,13 @@
         </is>
       </c>
       <c r="N370" t="n">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="O370" t="n">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="R370" t="n">
-        <v>0.2771296991022626</v>
+        <v>0.2751917291784705</v>
       </c>
       <c r="S370" t="inlineStr">
         <is>
@@ -70047,13 +70047,13 @@
         </is>
       </c>
       <c r="N373" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O373" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R373" t="n">
-        <v>0.132388232653028</v>
+        <v>0.1134756279883097</v>
       </c>
       <c r="S373" t="inlineStr">
         <is>
@@ -70206,10 +70206,10 @@
         </is>
       </c>
       <c r="N374" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O374" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U374" t="inlineStr">
         <is>
@@ -77441,12 +77441,12 @@
       </c>
       <c r="F414" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G414" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H414" t="inlineStr">
@@ -77480,13 +77480,13 @@
         </is>
       </c>
       <c r="N414" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="O414" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="R414" t="n">
-        <v>0.1868976085656669</v>
+        <v>0.09456302332359146</v>
       </c>
       <c r="S414" t="inlineStr">
         <is>
@@ -77495,7 +77495,7 @@
       </c>
       <c r="U414" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_A</t>
+          <t>SER_NZ_HEPATITIS_A_MONTHLY</t>
         </is>
       </c>
       <c r="AA414" t="inlineStr">
@@ -77510,7 +77510,7 @@
       </c>
       <c r="AP414" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ414" t="inlineStr">
@@ -77518,62 +77518,57 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR414" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS414" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_A</t>
+          <t>SER_NZ_HEPATITIS_A_MONTHLY</t>
         </is>
       </c>
       <c r="AT414" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU414" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV414" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW414" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX414" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY414" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ414" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA414" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB414" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC414" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -77605,12 +77600,12 @@
       </c>
       <c r="F415" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G415" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H415" t="inlineStr">
@@ -77644,29 +77639,29 @@
         </is>
       </c>
       <c r="N415" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="O415" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="U415" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_A</t>
+          <t>SER_NZ_HEPATITIS_A_MONTHLY</t>
         </is>
       </c>
       <c r="V415" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_A</t>
+          <t>SER_NZ_HEPATITIS_A_MONTHLY</t>
         </is>
       </c>
       <c r="W415" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NZ_PHS</t>
         </is>
       </c>
       <c r="X415" t="inlineStr">
         <is>
-          <t>Hepatit A</t>
+          <t>Hepatitis A</t>
         </is>
       </c>
       <c r="Y415" t="inlineStr">
@@ -77676,7 +77671,7 @@
       </c>
       <c r="Z415" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA415" t="inlineStr">
@@ -77691,7 +77686,7 @@
       </c>
       <c r="AC415" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NZ:national</t>
         </is>
       </c>
       <c r="AD415" t="inlineStr">
@@ -77726,17 +77721,17 @@
       </c>
       <c r="AJ415" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NZ_PHS_current</t>
         </is>
       </c>
       <c r="AK415" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+          <t>New Zealand PHF Science monthly hepatitis A notifications.</t>
         </is>
       </c>
       <c r="AM415" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN415" t="b">
@@ -77749,7 +77744,7 @@
       </c>
       <c r="AP415" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ415" t="inlineStr">
@@ -77757,62 +77752,57 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR415" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS415" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_A</t>
+          <t>SER_NZ_HEPATITIS_A_MONTHLY</t>
         </is>
       </c>
       <c r="AT415" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU415" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV415" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW415" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX415" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY415" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ415" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA415" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB415" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC415" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -77844,12 +77834,12 @@
       </c>
       <c r="F416" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G416" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H416" t="inlineStr">
@@ -77883,13 +77873,13 @@
         </is>
       </c>
       <c r="N416" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="O416" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="R416" t="n">
-        <v>0.05649400180367965</v>
+        <v>0.1868976085656669</v>
       </c>
       <c r="S416" t="inlineStr">
         <is>
@@ -77898,7 +77888,7 @@
       </c>
       <c r="U416" t="inlineStr">
         <is>
-          <t>SER_TW_HEPATITIS_A_0701</t>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_A</t>
         </is>
       </c>
       <c r="AA416" t="inlineStr">
@@ -77913,7 +77903,7 @@
       </c>
       <c r="AP416" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ416" t="inlineStr">
@@ -77921,57 +77911,62 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR416" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS416" t="inlineStr">
         <is>
-          <t>SER_TW_HEPATITIS_A_0701</t>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_A</t>
         </is>
       </c>
       <c r="AT416" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU416" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV416" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW416" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX416" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY416" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ416" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA416" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB416" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC416" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -78003,12 +77998,12 @@
       </c>
       <c r="F417" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G417" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H417" t="inlineStr">
@@ -78042,29 +78037,29 @@
         </is>
       </c>
       <c r="N417" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="O417" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="U417" t="inlineStr">
         <is>
-          <t>SER_TW_HEPATITIS_A_0701</t>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_A</t>
         </is>
       </c>
       <c r="V417" t="inlineStr">
         <is>
-          <t>SER_TW_HEPATITIS_A_0701</t>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_A</t>
         </is>
       </c>
       <c r="W417" t="inlineStr">
         <is>
-          <t>SRC_TW_NIDSS</t>
+          <t>SRC_SE_FOHM_SMINET</t>
         </is>
       </c>
       <c r="X417" t="inlineStr">
         <is>
-          <t>急性病毒性Ａ型肝炎</t>
+          <t>Hepatit A</t>
         </is>
       </c>
       <c r="Y417" t="inlineStr">
@@ -78074,7 +78069,7 @@
       </c>
       <c r="Z417" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA417" t="inlineStr">
@@ -78089,7 +78084,7 @@
       </c>
       <c r="AC417" t="inlineStr">
         <is>
-          <t>country:TW:national</t>
+          <t>country:SE:national</t>
         </is>
       </c>
       <c r="AD417" t="inlineStr">
@@ -78104,7 +78099,7 @@
       </c>
       <c r="AF417" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>conditional</t>
         </is>
       </c>
       <c r="AG417" t="inlineStr">
@@ -78124,17 +78119,17 @@
       </c>
       <c r="AJ417" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>SE_FOHM_SMINET_current</t>
         </is>
       </c>
       <c r="AK417" t="inlineStr">
         <is>
-          <t>Acute hepatitis A, code 0701. D067 remains deprecated.</t>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
         </is>
       </c>
       <c r="AM417" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>revised</t>
         </is>
       </c>
       <c r="AN417" t="b">
@@ -78147,7 +78142,7 @@
       </c>
       <c r="AP417" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ417" t="inlineStr">
@@ -78155,57 +78150,62 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR417" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS417" t="inlineStr">
         <is>
-          <t>SER_TW_HEPATITIS_A_0701</t>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_A</t>
         </is>
       </c>
       <c r="AT417" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU417" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV417" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW417" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX417" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY417" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ417" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA417" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB417" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC417" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -78237,12 +78237,12 @@
       </c>
       <c r="F418" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G418" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H418" t="inlineStr">
@@ -78276,16 +78276,13 @@
         </is>
       </c>
       <c r="N418" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="O418" t="n">
-        <v>2</v>
-      </c>
-      <c r="P418" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="R418" t="n">
-        <v>0.0005730076265538771</v>
+        <v>0.05649400180367965</v>
       </c>
       <c r="S418" t="inlineStr">
         <is>
@@ -78294,17 +78291,17 @@
       </c>
       <c r="U418" t="inlineStr">
         <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+          <t>SER_TW_HEPATITIS_A_0701</t>
         </is>
       </c>
       <c r="AA418" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO418" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP418" t="inlineStr">
@@ -78314,12 +78311,12 @@
       </c>
       <c r="AQ418" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS418" t="inlineStr">
         <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+          <t>SER_TW_HEPATITIS_A_0701</t>
         </is>
       </c>
       <c r="AT418" t="n">
@@ -78327,47 +78324,47 @@
       </c>
       <c r="AU418" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV418" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW418" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX418" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY418" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ418" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA418" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB418" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC418" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -78399,12 +78396,12 @@
       </c>
       <c r="F419" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G419" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H419" t="inlineStr">
@@ -78438,32 +78435,29 @@
         </is>
       </c>
       <c r="N419" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="O419" t="n">
-        <v>2</v>
-      </c>
-      <c r="P419" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="U419" t="inlineStr">
         <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+          <t>SER_TW_HEPATITIS_A_0701</t>
         </is>
       </c>
       <c r="V419" t="inlineStr">
         <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+          <t>SER_TW_HEPATITIS_A_0701</t>
         </is>
       </c>
       <c r="W419" t="inlineStr">
         <is>
-          <t>SRC_US_NNDSS</t>
+          <t>SRC_TW_NIDSS</t>
         </is>
       </c>
       <c r="X419" t="inlineStr">
         <is>
-          <t>Hepatitis A, Confirmed</t>
+          <t>急性病毒性Ａ型肝炎</t>
         </is>
       </c>
       <c r="Y419" t="inlineStr">
@@ -78478,7 +78472,7 @@
       </c>
       <c r="AA419" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AB419" t="inlineStr">
@@ -78488,7 +78482,7 @@
       </c>
       <c r="AC419" t="inlineStr">
         <is>
-          <t>country:US:national</t>
+          <t>country:TW:national</t>
         </is>
       </c>
       <c r="AD419" t="inlineStr">
@@ -78528,12 +78522,12 @@
       </c>
       <c r="AK419" t="inlineStr">
         <is>
-          <t>Confirmed hepatitis A component reported by NNDSS.</t>
+          <t>Acute hepatitis A, code 0701. D067 remains deprecated.</t>
         </is>
       </c>
       <c r="AM419" t="inlineStr">
         <is>
-          <t>provisional</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN419" t="b">
@@ -78541,7 +78535,7 @@
       </c>
       <c r="AO419" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP419" t="inlineStr">
@@ -78551,12 +78545,12 @@
       </c>
       <c r="AQ419" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS419" t="inlineStr">
         <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+          <t>SER_TW_HEPATITIS_A_0701</t>
         </is>
       </c>
       <c r="AT419" t="n">
@@ -78564,47 +78558,47 @@
       </c>
       <c r="AU419" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV419" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW419" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX419" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY419" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ419" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA419" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB419" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC419" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -78636,12 +78630,12 @@
       </c>
       <c r="F420" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G420" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H420" t="inlineStr">
@@ -78666,7 +78660,7 @@
       </c>
       <c r="L420" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M420" t="inlineStr">
@@ -78675,81 +78669,98 @@
         </is>
       </c>
       <c r="N420" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="O420" t="n">
-        <v>14</v>
+        <v>2</v>
+      </c>
+      <c r="P420" t="n">
+        <v>2</v>
       </c>
       <c r="R420" t="n">
-        <v>0.01143531770592073</v>
+        <v>0.0005730076265538771</v>
       </c>
       <c r="S420" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U420" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AA420" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO420" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP420" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR420" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS420" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ420" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS420" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
       <c r="AT420" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU420" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV420" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW420" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX420" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY420" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ420" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA420" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB420" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC420" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -78776,17 +78787,17 @@
       </c>
       <c r="E421" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F421" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G421" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H421" t="inlineStr">
@@ -78811,7 +78822,7 @@
       </c>
       <c r="L421" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M421" t="inlineStr">
@@ -78820,93 +78831,173 @@
         </is>
       </c>
       <c r="N421" t="n">
+        <v>2</v>
+      </c>
+      <c r="O421" t="n">
+        <v>2</v>
+      </c>
+      <c r="P421" t="n">
+        <v>2</v>
+      </c>
+      <c r="U421" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="V421" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="W421" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X421" t="inlineStr">
+        <is>
+          <t>Hepatitis A, Confirmed</t>
+        </is>
+      </c>
+      <c r="Y421" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z421" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA421" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB421" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC421" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD421" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE421" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF421" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG421" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH421" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI421" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ421" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK421" t="inlineStr">
+        <is>
+          <t>Confirmed hepatitis A component reported by NNDSS.</t>
+        </is>
+      </c>
+      <c r="AM421" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN421" t="b">
         <v>1</v>
       </c>
-      <c r="O421" t="n">
+      <c r="AO421" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP421" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ421" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS421" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AT421" t="n">
         <v>1</v>
       </c>
-      <c r="P421" t="n">
-        <v>1</v>
-      </c>
-      <c r="R421" t="n">
-        <v>0.01693265755097047</v>
-      </c>
-      <c r="S421" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AA421" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AO421" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP421" t="inlineStr">
-        <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ421" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS421" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_A</t>
-        </is>
-      </c>
-      <c r="AT421" t="n">
-        <v>2</v>
-      </c>
       <c r="AU421" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV421" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW421" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX421" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY421" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ421" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA421" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB421" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC421" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -78933,17 +79024,17 @@
       </c>
       <c r="E422" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F422" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G422" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H422" t="inlineStr">
@@ -78977,173 +79068,81 @@
         </is>
       </c>
       <c r="N422" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="O422" t="n">
-        <v>1</v>
-      </c>
-      <c r="P422" t="n">
-        <v>1</v>
-      </c>
-      <c r="U422" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A</t>
-        </is>
-      </c>
-      <c r="V422" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A</t>
-        </is>
-      </c>
-      <c r="W422" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X422" t="inlineStr">
-        <is>
-          <t>Acute Viral Hepatitis A</t>
-        </is>
-      </c>
-      <c r="Y422" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z422" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA422" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB422" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC422" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD422" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE422" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF422" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG422" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH422" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI422" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ422" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK422" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM422" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN422" t="b">
-        <v>1</v>
+        <v>14</v>
+      </c>
+      <c r="R422" t="n">
+        <v>0.01143531770592073</v>
+      </c>
+      <c r="S422" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO422" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP422" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ422" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS422" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_A</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR422" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS422" t="inlineStr"/>
       <c r="AT422" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU422" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV422" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW422" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX422" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY422" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ422" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA422" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB422" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC422" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -79175,12 +79174,12 @@
       </c>
       <c r="F423" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G423" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H423" t="inlineStr">
@@ -79205,7 +79204,7 @@
       </c>
       <c r="L423" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M423" t="inlineStr">
@@ -79214,27 +79213,22 @@
         </is>
       </c>
       <c r="N423" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="O423" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="P423" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="R423" t="n">
-        <v>0.001719022879661631</v>
+        <v>0.01693265755097047</v>
       </c>
       <c r="S423" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U423" t="inlineStr">
-        <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
-        </is>
-      </c>
       <c r="AA423" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -79242,70 +79236,70 @@
       </c>
       <c r="AO423" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP423" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ423" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS423" t="inlineStr">
         <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_A</t>
         </is>
       </c>
       <c r="AT423" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU423" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV423" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW423" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX423" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY423" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ423" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA423" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB423" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC423" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -79337,12 +79331,12 @@
       </c>
       <c r="F424" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G424" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H424" t="inlineStr">
@@ -79367,7 +79361,7 @@
       </c>
       <c r="L424" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M424" t="inlineStr">
@@ -79376,32 +79370,32 @@
         </is>
       </c>
       <c r="N424" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="O424" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="P424" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="U424" t="inlineStr">
         <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A</t>
         </is>
       </c>
       <c r="V424" t="inlineStr">
         <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A</t>
         </is>
       </c>
       <c r="W424" t="inlineStr">
         <is>
-          <t>SRC_US_NNDSS</t>
+          <t>SRC_SG_CDA_WIDB</t>
         </is>
       </c>
       <c r="X424" t="inlineStr">
         <is>
-          <t>Hepatitis A, Confirmed</t>
+          <t>Acute Viral Hepatitis A</t>
         </is>
       </c>
       <c r="Y424" t="inlineStr">
@@ -79411,7 +79405,7 @@
       </c>
       <c r="Z424" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA424" t="inlineStr">
@@ -79426,7 +79420,7 @@
       </c>
       <c r="AC424" t="inlineStr">
         <is>
-          <t>country:US:national</t>
+          <t>country:SG:national</t>
         </is>
       </c>
       <c r="AD424" t="inlineStr">
@@ -79441,7 +79435,7 @@
       </c>
       <c r="AF424" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>conditional</t>
         </is>
       </c>
       <c r="AG424" t="inlineStr">
@@ -79461,17 +79455,17 @@
       </c>
       <c r="AJ424" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
         </is>
       </c>
       <c r="AK424" t="inlineStr">
         <is>
-          <t>Confirmed hepatitis A component reported by NNDSS.</t>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
         </is>
       </c>
       <c r="AM424" t="inlineStr">
         <is>
-          <t>provisional</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN424" t="b">
@@ -79479,70 +79473,70 @@
       </c>
       <c r="AO424" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP424" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ424" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS424" t="inlineStr">
         <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_A</t>
         </is>
       </c>
       <c r="AT424" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU424" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV424" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW424" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX424" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY424" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ424" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA424" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB424" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC424" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -79574,12 +79568,12 @@
       </c>
       <c r="F425" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G425" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H425" t="inlineStr">
@@ -79604,7 +79598,7 @@
       </c>
       <c r="L425" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="M425" t="inlineStr">
@@ -79613,81 +79607,98 @@
         </is>
       </c>
       <c r="N425" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="O425" t="n">
-        <v>11</v>
+        <v>6</v>
+      </c>
+      <c r="P425" t="n">
+        <v>6</v>
       </c>
       <c r="R425" t="n">
-        <v>0.00898489248322343</v>
+        <v>0.001719022879661631</v>
       </c>
       <c r="S425" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U425" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AA425" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO425" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP425" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR425" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS425" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ425" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS425" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
       <c r="AT425" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU425" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV425" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW425" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX425" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY425" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ425" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA425" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB425" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC425" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -79714,17 +79725,17 @@
       </c>
       <c r="E426" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F426" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G426" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H426" t="inlineStr">
@@ -79749,7 +79760,7 @@
       </c>
       <c r="L426" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="M426" t="inlineStr">
@@ -79758,20 +79769,42 @@
         </is>
       </c>
       <c r="N426" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O426" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="P426" t="n">
-        <v>2</v>
-      </c>
-      <c r="R426" t="n">
-        <v>0.03386531510194095</v>
-      </c>
-      <c r="S426" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+        <v>6</v>
+      </c>
+      <c r="U426" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="V426" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="W426" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X426" t="inlineStr">
+        <is>
+          <t>Hepatitis A, Confirmed</t>
+        </is>
+      </c>
+      <c r="Y426" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z426" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA426" t="inlineStr">
@@ -79779,72 +79812,130 @@
           <t>weekly</t>
         </is>
       </c>
+      <c r="AB426" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC426" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD426" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE426" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF426" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG426" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH426" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI426" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ426" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK426" t="inlineStr">
+        <is>
+          <t>Confirmed hepatitis A component reported by NNDSS.</t>
+        </is>
+      </c>
+      <c r="AM426" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN426" t="b">
+        <v>1</v>
+      </c>
       <c r="AO426" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP426" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ426" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS426" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_A</t>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
         </is>
       </c>
       <c r="AT426" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU426" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV426" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW426" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX426" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY426" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ426" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA426" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB426" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC426" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -79871,17 +79962,17 @@
       </c>
       <c r="E427" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F427" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G427" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H427" t="inlineStr">
@@ -79915,173 +80006,81 @@
         </is>
       </c>
       <c r="N427" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="O427" t="n">
-        <v>2</v>
-      </c>
-      <c r="P427" t="n">
-        <v>2</v>
-      </c>
-      <c r="U427" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A</t>
-        </is>
-      </c>
-      <c r="V427" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A</t>
-        </is>
-      </c>
-      <c r="W427" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X427" t="inlineStr">
-        <is>
-          <t>Acute Viral Hepatitis A</t>
-        </is>
-      </c>
-      <c r="Y427" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z427" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA427" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB427" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC427" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD427" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE427" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF427" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG427" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH427" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI427" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ427" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK427" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM427" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN427" t="b">
-        <v>1</v>
+        <v>11</v>
+      </c>
+      <c r="R427" t="n">
+        <v>0.00898489248322343</v>
+      </c>
+      <c r="S427" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO427" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP427" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ427" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS427" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_A</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR427" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS427" t="inlineStr"/>
       <c r="AT427" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU427" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV427" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW427" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX427" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY427" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ427" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA427" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB427" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC427" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -80113,12 +80112,12 @@
       </c>
       <c r="F428" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G428" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H428" t="inlineStr">
@@ -80143,7 +80142,7 @@
       </c>
       <c r="L428" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M428" t="inlineStr">
@@ -80152,27 +80151,22 @@
         </is>
       </c>
       <c r="N428" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="O428" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="P428" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="R428" t="n">
-        <v>0.002578534319492447</v>
+        <v>0.03386531510194095</v>
       </c>
       <c r="S428" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U428" t="inlineStr">
-        <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
-        </is>
-      </c>
       <c r="AA428" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -80180,70 +80174,70 @@
       </c>
       <c r="AO428" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP428" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ428" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS428" t="inlineStr">
         <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_A</t>
         </is>
       </c>
       <c r="AT428" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU428" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV428" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW428" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX428" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY428" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ428" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA428" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB428" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC428" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -80275,12 +80269,12 @@
       </c>
       <c r="F429" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G429" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H429" t="inlineStr">
@@ -80305,7 +80299,7 @@
       </c>
       <c r="L429" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M429" t="inlineStr">
@@ -80314,32 +80308,32 @@
         </is>
       </c>
       <c r="N429" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="O429" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="P429" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="U429" t="inlineStr">
         <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A</t>
         </is>
       </c>
       <c r="V429" t="inlineStr">
         <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A</t>
         </is>
       </c>
       <c r="W429" t="inlineStr">
         <is>
-          <t>SRC_US_NNDSS</t>
+          <t>SRC_SG_CDA_WIDB</t>
         </is>
       </c>
       <c r="X429" t="inlineStr">
         <is>
-          <t>Hepatitis A, Confirmed</t>
+          <t>Acute Viral Hepatitis A</t>
         </is>
       </c>
       <c r="Y429" t="inlineStr">
@@ -80349,7 +80343,7 @@
       </c>
       <c r="Z429" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA429" t="inlineStr">
@@ -80364,7 +80358,7 @@
       </c>
       <c r="AC429" t="inlineStr">
         <is>
-          <t>country:US:national</t>
+          <t>country:SG:national</t>
         </is>
       </c>
       <c r="AD429" t="inlineStr">
@@ -80379,7 +80373,7 @@
       </c>
       <c r="AF429" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>conditional</t>
         </is>
       </c>
       <c r="AG429" t="inlineStr">
@@ -80399,17 +80393,17 @@
       </c>
       <c r="AJ429" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
         </is>
       </c>
       <c r="AK429" t="inlineStr">
         <is>
-          <t>Confirmed hepatitis A component reported by NNDSS.</t>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
         </is>
       </c>
       <c r="AM429" t="inlineStr">
         <is>
-          <t>provisional</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN429" t="b">
@@ -80417,70 +80411,70 @@
       </c>
       <c r="AO429" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP429" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ429" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS429" t="inlineStr">
         <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_A</t>
         </is>
       </c>
       <c r="AT429" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU429" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV429" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW429" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX429" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY429" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ429" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA429" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB429" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC429" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -80512,12 +80506,12 @@
       </c>
       <c r="F430" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G430" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H430" t="inlineStr">
@@ -80542,7 +80536,7 @@
       </c>
       <c r="L430" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="M430" t="inlineStr">
@@ -80551,81 +80545,98 @@
         </is>
       </c>
       <c r="N430" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O430" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="P430" t="n">
+        <v>9</v>
       </c>
       <c r="R430" t="n">
-        <v>0.00653446726052613</v>
+        <v>0.002578534319492447</v>
       </c>
       <c r="S430" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U430" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AA430" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO430" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP430" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR430" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS430" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ430" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS430" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
       <c r="AT430" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU430" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV430" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW430" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX430" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY430" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ430" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA430" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB430" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC430" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -80652,17 +80663,17 @@
       </c>
       <c r="E431" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F431" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G431" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H431" t="inlineStr">
@@ -80687,7 +80698,7 @@
       </c>
       <c r="L431" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="M431" t="inlineStr">
@@ -80696,93 +80707,173 @@
         </is>
       </c>
       <c r="N431" t="n">
+        <v>9</v>
+      </c>
+      <c r="O431" t="n">
+        <v>9</v>
+      </c>
+      <c r="P431" t="n">
+        <v>9</v>
+      </c>
+      <c r="U431" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="V431" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="W431" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X431" t="inlineStr">
+        <is>
+          <t>Hepatitis A, Confirmed</t>
+        </is>
+      </c>
+      <c r="Y431" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z431" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA431" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB431" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC431" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD431" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE431" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF431" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG431" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH431" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI431" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ431" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK431" t="inlineStr">
+        <is>
+          <t>Confirmed hepatitis A component reported by NNDSS.</t>
+        </is>
+      </c>
+      <c r="AM431" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN431" t="b">
         <v>1</v>
       </c>
-      <c r="O431" t="n">
+      <c r="AO431" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP431" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ431" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS431" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AT431" t="n">
         <v>1</v>
       </c>
-      <c r="P431" t="n">
-        <v>1</v>
-      </c>
-      <c r="R431" t="n">
-        <v>0.01693265755097047</v>
-      </c>
-      <c r="S431" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AA431" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AO431" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP431" t="inlineStr">
-        <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ431" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS431" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_A</t>
-        </is>
-      </c>
-      <c r="AT431" t="n">
-        <v>2</v>
-      </c>
       <c r="AU431" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV431" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW431" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX431" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY431" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ431" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA431" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB431" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC431" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -80809,17 +80900,17 @@
       </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F432" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G432" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H432" t="inlineStr">
@@ -80853,173 +80944,81 @@
         </is>
       </c>
       <c r="N432" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="O432" t="n">
-        <v>1</v>
-      </c>
-      <c r="P432" t="n">
-        <v>1</v>
-      </c>
-      <c r="U432" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A</t>
-        </is>
-      </c>
-      <c r="V432" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A</t>
-        </is>
-      </c>
-      <c r="W432" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X432" t="inlineStr">
-        <is>
-          <t>Acute Viral Hepatitis A</t>
-        </is>
-      </c>
-      <c r="Y432" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z432" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA432" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB432" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC432" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD432" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE432" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF432" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG432" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH432" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI432" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ432" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK432" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM432" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN432" t="b">
-        <v>1</v>
+        <v>8</v>
+      </c>
+      <c r="R432" t="n">
+        <v>0.00653446726052613</v>
+      </c>
+      <c r="S432" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO432" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP432" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ432" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS432" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_A</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR432" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS432" t="inlineStr"/>
       <c r="AT432" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU432" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV432" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW432" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX432" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY432" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ432" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA432" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB432" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC432" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -81051,12 +81050,12 @@
       </c>
       <c r="F433" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G433" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H433" t="inlineStr">
@@ -81081,7 +81080,7 @@
       </c>
       <c r="L433" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M433" t="inlineStr">
@@ -81090,27 +81089,22 @@
         </is>
       </c>
       <c r="N433" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O433" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P433" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R433" t="n">
-        <v>0.0008595114398308156</v>
+        <v>0.01693265755097047</v>
       </c>
       <c r="S433" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U433" t="inlineStr">
-        <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
-        </is>
-      </c>
       <c r="AA433" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -81118,70 +81112,70 @@
       </c>
       <c r="AO433" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP433" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ433" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS433" t="inlineStr">
         <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_A</t>
         </is>
       </c>
       <c r="AT433" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU433" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV433" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW433" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX433" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY433" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ433" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA433" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB433" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC433" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -81213,12 +81207,12 @@
       </c>
       <c r="F434" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G434" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H434" t="inlineStr">
@@ -81243,7 +81237,7 @@
       </c>
       <c r="L434" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M434" t="inlineStr">
@@ -81252,32 +81246,32 @@
         </is>
       </c>
       <c r="N434" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O434" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P434" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U434" t="inlineStr">
         <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A</t>
         </is>
       </c>
       <c r="V434" t="inlineStr">
         <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A</t>
         </is>
       </c>
       <c r="W434" t="inlineStr">
         <is>
-          <t>SRC_US_NNDSS</t>
+          <t>SRC_SG_CDA_WIDB</t>
         </is>
       </c>
       <c r="X434" t="inlineStr">
         <is>
-          <t>Hepatitis A, Confirmed</t>
+          <t>Acute Viral Hepatitis A</t>
         </is>
       </c>
       <c r="Y434" t="inlineStr">
@@ -81287,7 +81281,7 @@
       </c>
       <c r="Z434" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA434" t="inlineStr">
@@ -81302,7 +81296,7 @@
       </c>
       <c r="AC434" t="inlineStr">
         <is>
-          <t>country:US:national</t>
+          <t>country:SG:national</t>
         </is>
       </c>
       <c r="AD434" t="inlineStr">
@@ -81317,7 +81311,7 @@
       </c>
       <c r="AF434" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>conditional</t>
         </is>
       </c>
       <c r="AG434" t="inlineStr">
@@ -81337,17 +81331,17 @@
       </c>
       <c r="AJ434" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
         </is>
       </c>
       <c r="AK434" t="inlineStr">
         <is>
-          <t>Confirmed hepatitis A component reported by NNDSS.</t>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
         </is>
       </c>
       <c r="AM434" t="inlineStr">
         <is>
-          <t>provisional</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN434" t="b">
@@ -81355,70 +81349,70 @@
       </c>
       <c r="AO434" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP434" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ434" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS434" t="inlineStr">
         <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_A</t>
         </is>
       </c>
       <c r="AT434" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU434" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV434" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW434" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX434" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY434" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ434" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA434" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB434" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC434" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -81450,12 +81444,12 @@
       </c>
       <c r="F435" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G435" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H435" t="inlineStr">
@@ -81480,7 +81474,7 @@
       </c>
       <c r="L435" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="M435" t="inlineStr">
@@ -81489,81 +81483,98 @@
         </is>
       </c>
       <c r="N435" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="O435" t="n">
-        <v>21</v>
+        <v>3</v>
+      </c>
+      <c r="P435" t="n">
+        <v>3</v>
       </c>
       <c r="R435" t="n">
-        <v>0.01715297655888109</v>
+        <v>0.0008595114398308156</v>
       </c>
       <c r="S435" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U435" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AA435" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO435" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP435" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR435" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS435" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ435" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS435" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
       <c r="AT435" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU435" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV435" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW435" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX435" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY435" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ435" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA435" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB435" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC435" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -81590,17 +81601,17 @@
       </c>
       <c r="E436" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F436" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G436" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H436" t="inlineStr">
@@ -81625,7 +81636,7 @@
       </c>
       <c r="L436" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="M436" t="inlineStr">
@@ -81634,20 +81645,42 @@
         </is>
       </c>
       <c r="N436" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O436" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P436" t="n">
-        <v>0</v>
-      </c>
-      <c r="R436" t="n">
-        <v>0</v>
-      </c>
-      <c r="S436" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+        <v>3</v>
+      </c>
+      <c r="U436" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="V436" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="W436" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X436" t="inlineStr">
+        <is>
+          <t>Hepatitis A, Confirmed</t>
+        </is>
+      </c>
+      <c r="Y436" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z436" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA436" t="inlineStr">
@@ -81655,72 +81688,130 @@
           <t>weekly</t>
         </is>
       </c>
+      <c r="AB436" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC436" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD436" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE436" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF436" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG436" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH436" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI436" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ436" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK436" t="inlineStr">
+        <is>
+          <t>Confirmed hepatitis A component reported by NNDSS.</t>
+        </is>
+      </c>
+      <c r="AM436" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN436" t="b">
+        <v>1</v>
+      </c>
       <c r="AO436" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP436" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ436" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS436" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_A</t>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
         </is>
       </c>
       <c r="AT436" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU436" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV436" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW436" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX436" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY436" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ436" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA436" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB436" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC436" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -81747,17 +81838,17 @@
       </c>
       <c r="E437" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F437" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G437" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H437" t="inlineStr">
@@ -81791,173 +81882,81 @@
         </is>
       </c>
       <c r="N437" t="n">
+        <v>21</v>
+      </c>
+      <c r="O437" t="n">
+        <v>21</v>
+      </c>
+      <c r="R437" t="n">
+        <v>0.01715297655888109</v>
+      </c>
+      <c r="S437" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO437" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP437" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR437" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS437" t="inlineStr"/>
+      <c r="AT437" t="n">
         <v>0</v>
       </c>
-      <c r="O437" t="n">
-        <v>0</v>
-      </c>
-      <c r="P437" t="n">
-        <v>0</v>
-      </c>
-      <c r="U437" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A</t>
-        </is>
-      </c>
-      <c r="V437" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A</t>
-        </is>
-      </c>
-      <c r="W437" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X437" t="inlineStr">
-        <is>
-          <t>Acute Viral Hepatitis A</t>
-        </is>
-      </c>
-      <c r="Y437" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z437" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA437" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB437" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC437" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD437" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE437" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF437" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG437" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH437" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI437" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ437" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK437" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM437" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN437" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO437" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP437" t="inlineStr">
-        <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ437" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS437" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_A</t>
-        </is>
-      </c>
-      <c r="AT437" t="n">
-        <v>2</v>
-      </c>
       <c r="AU437" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV437" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW437" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX437" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY437" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ437" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA437" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB437" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC437" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -81989,12 +81988,12 @@
       </c>
       <c r="F438" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G438" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H438" t="inlineStr">
@@ -82019,7 +82018,7 @@
       </c>
       <c r="L438" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M438" t="inlineStr">
@@ -82028,27 +82027,22 @@
         </is>
       </c>
       <c r="N438" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O438" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P438" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="R438" t="n">
-        <v>0.001719022879661631</v>
+        <v>0</v>
       </c>
       <c r="S438" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U438" t="inlineStr">
-        <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
-        </is>
-      </c>
       <c r="AA438" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -82056,70 +82050,70 @@
       </c>
       <c r="AO438" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP438" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ438" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS438" t="inlineStr">
         <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_A</t>
         </is>
       </c>
       <c r="AT438" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU438" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV438" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW438" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX438" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY438" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ438" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA438" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB438" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC438" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -82151,12 +82145,12 @@
       </c>
       <c r="F439" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G439" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H439" t="inlineStr">
@@ -82181,7 +82175,7 @@
       </c>
       <c r="L439" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M439" t="inlineStr">
@@ -82190,32 +82184,32 @@
         </is>
       </c>
       <c r="N439" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O439" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P439" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="U439" t="inlineStr">
         <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A</t>
         </is>
       </c>
       <c r="V439" t="inlineStr">
         <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A</t>
         </is>
       </c>
       <c r="W439" t="inlineStr">
         <is>
-          <t>SRC_US_NNDSS</t>
+          <t>SRC_SG_CDA_WIDB</t>
         </is>
       </c>
       <c r="X439" t="inlineStr">
         <is>
-          <t>Hepatitis A, Confirmed</t>
+          <t>Acute Viral Hepatitis A</t>
         </is>
       </c>
       <c r="Y439" t="inlineStr">
@@ -82225,7 +82219,7 @@
       </c>
       <c r="Z439" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA439" t="inlineStr">
@@ -82240,7 +82234,7 @@
       </c>
       <c r="AC439" t="inlineStr">
         <is>
-          <t>country:US:national</t>
+          <t>country:SG:national</t>
         </is>
       </c>
       <c r="AD439" t="inlineStr">
@@ -82255,7 +82249,7 @@
       </c>
       <c r="AF439" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>conditional</t>
         </is>
       </c>
       <c r="AG439" t="inlineStr">
@@ -82275,17 +82269,17 @@
       </c>
       <c r="AJ439" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
         </is>
       </c>
       <c r="AK439" t="inlineStr">
         <is>
-          <t>Confirmed hepatitis A component reported by NNDSS.</t>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
         </is>
       </c>
       <c r="AM439" t="inlineStr">
         <is>
-          <t>provisional</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN439" t="b">
@@ -82293,70 +82287,70 @@
       </c>
       <c r="AO439" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP439" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ439" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS439" t="inlineStr">
         <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_A</t>
         </is>
       </c>
       <c r="AT439" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU439" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV439" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW439" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX439" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY439" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ439" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA439" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB439" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC439" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -82388,12 +82382,12 @@
       </c>
       <c r="F440" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G440" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H440" t="inlineStr">
@@ -82418,7 +82412,7 @@
       </c>
       <c r="L440" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="M440" t="inlineStr">
@@ -82427,81 +82421,98 @@
         </is>
       </c>
       <c r="N440" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="O440" t="n">
-        <v>19</v>
+        <v>6</v>
+      </c>
+      <c r="P440" t="n">
+        <v>6</v>
       </c>
       <c r="R440" t="n">
-        <v>0.01551935974374956</v>
+        <v>0.001719022879661631</v>
       </c>
       <c r="S440" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U440" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AA440" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO440" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP440" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR440" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS440" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ440" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS440" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
       <c r="AT440" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU440" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV440" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW440" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX440" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY440" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ440" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA440" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB440" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC440" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -82528,17 +82539,17 @@
       </c>
       <c r="E441" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F441" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G441" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H441" t="inlineStr">
@@ -82563,7 +82574,7 @@
       </c>
       <c r="L441" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="M441" t="inlineStr">
@@ -82572,20 +82583,42 @@
         </is>
       </c>
       <c r="N441" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O441" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="P441" t="n">
-        <v>2</v>
-      </c>
-      <c r="R441" t="n">
-        <v>0.03386531510194095</v>
-      </c>
-      <c r="S441" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+        <v>6</v>
+      </c>
+      <c r="U441" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="V441" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="W441" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X441" t="inlineStr">
+        <is>
+          <t>Hepatitis A, Confirmed</t>
+        </is>
+      </c>
+      <c r="Y441" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z441" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA441" t="inlineStr">
@@ -82593,72 +82626,130 @@
           <t>weekly</t>
         </is>
       </c>
+      <c r="AB441" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC441" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD441" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE441" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF441" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG441" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH441" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI441" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ441" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK441" t="inlineStr">
+        <is>
+          <t>Confirmed hepatitis A component reported by NNDSS.</t>
+        </is>
+      </c>
+      <c r="AM441" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN441" t="b">
+        <v>1</v>
+      </c>
       <c r="AO441" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP441" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ441" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS441" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_A</t>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
         </is>
       </c>
       <c r="AT441" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU441" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV441" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW441" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX441" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY441" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ441" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA441" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB441" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC441" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -82685,17 +82776,17 @@
       </c>
       <c r="E442" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F442" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G442" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H442" t="inlineStr">
@@ -82729,173 +82820,81 @@
         </is>
       </c>
       <c r="N442" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="O442" t="n">
-        <v>2</v>
-      </c>
-      <c r="P442" t="n">
-        <v>2</v>
-      </c>
-      <c r="U442" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A</t>
-        </is>
-      </c>
-      <c r="V442" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A</t>
-        </is>
-      </c>
-      <c r="W442" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X442" t="inlineStr">
-        <is>
-          <t>Acute Viral Hepatitis A</t>
-        </is>
-      </c>
-      <c r="Y442" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z442" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
-        </is>
-      </c>
-      <c r="AA442" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB442" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC442" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD442" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE442" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF442" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG442" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH442" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI442" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ442" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK442" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM442" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN442" t="b">
-        <v>1</v>
+        <v>19</v>
+      </c>
+      <c r="R442" t="n">
+        <v>0.01551935974374956</v>
+      </c>
+      <c r="S442" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO442" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP442" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ442" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS442" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_A</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR442" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS442" t="inlineStr"/>
       <c r="AT442" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU442" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV442" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW442" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX442" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY442" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ442" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA442" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB442" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC442" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -82927,12 +82926,12 @@
       </c>
       <c r="F443" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G443" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H443" t="inlineStr">
@@ -82957,90 +82956,102 @@
       </c>
       <c r="L443" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M443" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N443" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O443" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="P443" t="n">
+        <v>2</v>
       </c>
       <c r="R443" t="n">
-        <v>0</v>
+        <v>0.03386531510194095</v>
       </c>
       <c r="S443" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA443" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO443" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP443" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR443" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS443" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ443" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS443" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_A</t>
+        </is>
+      </c>
       <c r="AT443" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU443" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV443" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW443" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX443" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY443" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ443" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA443" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB443" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC443" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -83067,17 +83078,17 @@
       </c>
       <c r="E444" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F444" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G444" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H444" t="inlineStr">
@@ -83102,12 +83113,12 @@
       </c>
       <c r="L444" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M444" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N444" t="n">
@@ -83116,23 +83127,101 @@
       <c r="O444" t="n">
         <v>2</v>
       </c>
-      <c r="R444" t="n">
-        <v>0.03557618341728275</v>
-      </c>
-      <c r="S444" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="P444" t="n">
+        <v>2</v>
       </c>
       <c r="U444" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_115</t>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A</t>
+        </is>
+      </c>
+      <c r="V444" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A</t>
+        </is>
+      </c>
+      <c r="W444" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X444" t="inlineStr">
+        <is>
+          <t>Acute Viral Hepatitis A</t>
+        </is>
+      </c>
+      <c r="Y444" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z444" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA444" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB444" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC444" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD444" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE444" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF444" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG444" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH444" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI444" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ444" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK444" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM444" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN444" t="b">
+        <v>1</v>
       </c>
       <c r="AO444" t="inlineStr">
         <is>
@@ -83141,22 +83230,17 @@
       </c>
       <c r="AP444" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ444" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR444" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS444" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_115</t>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_A</t>
         </is>
       </c>
       <c r="AT444" t="n">
@@ -83164,47 +83248,47 @@
       </c>
       <c r="AU444" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV444" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW444" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX444" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY444" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ444" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA444" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB444" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC444" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -83231,17 +83315,17 @@
       </c>
       <c r="E445" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F445" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G445" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H445" t="inlineStr">
@@ -83275,175 +83359,81 @@
         </is>
       </c>
       <c r="N445" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O445" t="n">
-        <v>2</v>
-      </c>
-      <c r="U445" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_115</t>
-        </is>
-      </c>
-      <c r="V445" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_115</t>
-        </is>
-      </c>
-      <c r="W445" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X445" t="inlineStr">
-        <is>
-          <t>Hepatitis A</t>
-        </is>
-      </c>
-      <c r="Y445" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z445" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA445" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB445" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC445" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD445" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="R445" t="n">
+        <v>0</v>
+      </c>
+      <c r="S445" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO445" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP445" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR445" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS445" t="inlineStr"/>
+      <c r="AT445" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU445" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV445" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE445" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF445" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG445" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH445" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI445" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ445" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK445" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 115.</t>
-        </is>
-      </c>
-      <c r="AM445" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN445" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO445" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP445" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ445" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR445" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS445" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_115</t>
-        </is>
-      </c>
-      <c r="AT445" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU445" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
-      </c>
-      <c r="AV445" t="inlineStr">
-        <is>
-          <t>thl_ttr</t>
-        </is>
-      </c>
       <c r="AW445" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX445" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY445" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ445" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA445" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB445" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC445" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -83475,12 +83465,12 @@
       </c>
       <c r="F446" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G446" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H446" t="inlineStr">
@@ -83514,81 +83504,100 @@
         </is>
       </c>
       <c r="N446" t="n">
-        <v>47</v>
+        <v>2</v>
       </c>
       <c r="O446" t="n">
-        <v>47</v>
+        <v>2</v>
       </c>
       <c r="R446" t="n">
-        <v>0.09108458641822616</v>
+        <v>0.03557618341728275</v>
       </c>
       <c r="S446" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U446" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_115</t>
+        </is>
+      </c>
+      <c r="AA446" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO446" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP446" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ446" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR446" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS446" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS446" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_115</t>
+        </is>
+      </c>
       <c r="AT446" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU446" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV446" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW446" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX446" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY446" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ446" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA446" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB446" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC446" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -83615,17 +83624,17 @@
       </c>
       <c r="E447" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F447" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G447" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H447" t="inlineStr">
@@ -83659,22 +83668,39 @@
         </is>
       </c>
       <c r="N447" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O447" t="n">
-        <v>4</v>
-      </c>
-      <c r="R447" t="n">
-        <v>0.07075903303182025</v>
-      </c>
-      <c r="S447" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>2</v>
       </c>
       <c r="U447" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_201_MONTHLY</t>
+          <t>SER_FI_THL_TTR_115</t>
+        </is>
+      </c>
+      <c r="V447" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_115</t>
+        </is>
+      </c>
+      <c r="W447" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X447" t="inlineStr">
+        <is>
+          <t>Hepatitis A</t>
+        </is>
+      </c>
+      <c r="Y447" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z447" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA447" t="inlineStr">
@@ -83682,6 +83708,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB447" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC447" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD447" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE447" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF447" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG447" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH447" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI447" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ447" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK447" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 115.</t>
+        </is>
+      </c>
+      <c r="AM447" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN447" t="b">
+        <v>1</v>
+      </c>
       <c r="AO447" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -83694,7 +83778,7 @@
       </c>
       <c r="AQ447" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR447" t="inlineStr">
@@ -83704,7 +83788,7 @@
       </c>
       <c r="AS447" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_201_MONTHLY</t>
+          <t>SER_FI_THL_TTR_115</t>
         </is>
       </c>
       <c r="AT447" t="n">
@@ -83712,47 +83796,47 @@
       </c>
       <c r="AU447" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV447" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW447" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX447" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY447" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ447" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA447" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB447" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC447" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -83779,17 +83863,17 @@
       </c>
       <c r="E448" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F448" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G448" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H448" t="inlineStr">
@@ -83823,175 +83907,81 @@
         </is>
       </c>
       <c r="N448" t="n">
-        <v>4</v>
+        <v>49</v>
       </c>
       <c r="O448" t="n">
-        <v>4</v>
-      </c>
-      <c r="U448" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_201_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V448" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_201_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W448" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X448" t="inlineStr">
-        <is>
-          <t>Hepatitt A</t>
-        </is>
-      </c>
-      <c r="Y448" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z448" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA448" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB448" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC448" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD448" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE448" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF448" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG448" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH448" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI448" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ448" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK448" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM448" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN448" t="b">
-        <v>1</v>
+        <v>49</v>
+      </c>
+      <c r="R448" t="n">
+        <v>0.09496052626581025</v>
+      </c>
+      <c r="S448" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO448" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP448" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ448" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR448" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS448" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_201_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS448" t="inlineStr"/>
       <c r="AT448" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU448" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV448" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW448" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX448" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY448" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ448" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA448" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB448" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC448" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -84023,12 +84013,12 @@
       </c>
       <c r="F449" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G449" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H449" t="inlineStr">
@@ -84053,7 +84043,7 @@
       </c>
       <c r="L449" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M449" t="inlineStr">
@@ -84062,16 +84052,13 @@
         </is>
       </c>
       <c r="N449" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O449" t="n">
-        <v>7</v>
-      </c>
-      <c r="P449" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="R449" t="n">
-        <v>0.00200552669293857</v>
+        <v>0.07075903303182025</v>
       </c>
       <c r="S449" t="inlineStr">
         <is>
@@ -84080,80 +84067,85 @@
       </c>
       <c r="U449" t="inlineStr">
         <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+          <t>SER_NO_FHI_201_MONTHLY</t>
         </is>
       </c>
       <c r="AA449" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO449" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP449" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ449" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR449" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS449" t="inlineStr">
         <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+          <t>SER_NO_FHI_201_MONTHLY</t>
         </is>
       </c>
       <c r="AT449" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU449" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV449" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW449" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX449" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY449" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ449" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA449" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB449" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC449" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -84185,12 +84177,12 @@
       </c>
       <c r="F450" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G450" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H450" t="inlineStr">
@@ -84215,7 +84207,7 @@
       </c>
       <c r="L450" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M450" t="inlineStr">
@@ -84224,32 +84216,29 @@
         </is>
       </c>
       <c r="N450" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O450" t="n">
-        <v>7</v>
-      </c>
-      <c r="P450" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="U450" t="inlineStr">
         <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+          <t>SER_NO_FHI_201_MONTHLY</t>
         </is>
       </c>
       <c r="V450" t="inlineStr">
         <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+          <t>SER_NO_FHI_201_MONTHLY</t>
         </is>
       </c>
       <c r="W450" t="inlineStr">
         <is>
-          <t>SRC_US_NNDSS</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X450" t="inlineStr">
         <is>
-          <t>Hepatitis A, Confirmed</t>
+          <t>Hepatitt A</t>
         </is>
       </c>
       <c r="Y450" t="inlineStr">
@@ -84259,12 +84248,12 @@
       </c>
       <c r="Z450" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA450" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AB450" t="inlineStr">
@@ -84274,7 +84263,7 @@
       </c>
       <c r="AC450" t="inlineStr">
         <is>
-          <t>country:US:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD450" t="inlineStr">
@@ -84289,7 +84278,7 @@
       </c>
       <c r="AF450" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>conditional</t>
         </is>
       </c>
       <c r="AG450" t="inlineStr">
@@ -84309,17 +84298,17 @@
       </c>
       <c r="AJ450" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK450" t="inlineStr">
         <is>
-          <t>Confirmed hepatitis A component reported by NNDSS.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
         </is>
       </c>
       <c r="AM450" t="inlineStr">
         <is>
-          <t>provisional</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN450" t="b">
@@ -84327,70 +84316,75 @@
       </c>
       <c r="AO450" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP450" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ450" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR450" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS450" t="inlineStr">
         <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+          <t>SER_NO_FHI_201_MONTHLY</t>
         </is>
       </c>
       <c r="AT450" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU450" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV450" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW450" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX450" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY450" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ450" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA450" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB450" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC450" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -84422,118 +84416,517 @@
       </c>
       <c r="F451" t="inlineStr">
         <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G451" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H451" t="inlineStr">
+        <is>
+          <t>D007</t>
+        </is>
+      </c>
+      <c r="I451" t="inlineStr">
+        <is>
+          <t>Hepatitis A</t>
+        </is>
+      </c>
+      <c r="J451" t="inlineStr">
+        <is>
+          <t>甲型肝炎</t>
+        </is>
+      </c>
+      <c r="K451" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L451" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="M451" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N451" t="n">
+        <v>7</v>
+      </c>
+      <c r="O451" t="n">
+        <v>7</v>
+      </c>
+      <c r="P451" t="n">
+        <v>7</v>
+      </c>
+      <c r="R451" t="n">
+        <v>0.00200552669293857</v>
+      </c>
+      <c r="S451" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U451" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AA451" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO451" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP451" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ451" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS451" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AT451" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU451" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV451" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW451" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX451" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY451" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ451" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA451" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB451" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC451" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>D007</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>hepatitis-a</t>
+        </is>
+      </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>Hepatitis A</t>
+        </is>
+      </c>
+      <c r="E452" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F452" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G452" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H452" t="inlineStr">
+        <is>
+          <t>D007</t>
+        </is>
+      </c>
+      <c r="I452" t="inlineStr">
+        <is>
+          <t>Hepatitis A</t>
+        </is>
+      </c>
+      <c r="J452" t="inlineStr">
+        <is>
+          <t>甲型肝炎</t>
+        </is>
+      </c>
+      <c r="K452" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L452" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="M452" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N452" t="n">
+        <v>7</v>
+      </c>
+      <c r="O452" t="n">
+        <v>7</v>
+      </c>
+      <c r="P452" t="n">
+        <v>7</v>
+      </c>
+      <c r="U452" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="V452" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="W452" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X452" t="inlineStr">
+        <is>
+          <t>Hepatitis A, Confirmed</t>
+        </is>
+      </c>
+      <c r="Y452" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z452" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA452" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB452" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC452" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD452" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE452" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF452" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG452" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH452" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI452" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ452" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK452" t="inlineStr">
+        <is>
+          <t>Confirmed hepatitis A component reported by NNDSS.</t>
+        </is>
+      </c>
+      <c r="AM452" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN452" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO452" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP452" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ452" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS452" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AT452" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU452" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV452" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW452" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX452" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY452" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ452" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA452" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB452" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC452" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>D007</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>hepatitis-a</t>
+        </is>
+      </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>Hepatitis A</t>
+        </is>
+      </c>
+      <c r="E453" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F453" t="inlineStr">
+        <is>
           <t>JP</t>
         </is>
       </c>
-      <c r="G451" t="inlineStr">
+      <c r="G453" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="H451" t="inlineStr">
-        <is>
-          <t>D007</t>
-        </is>
-      </c>
-      <c r="I451" t="inlineStr">
-        <is>
-          <t>Hepatitis A</t>
-        </is>
-      </c>
-      <c r="J451" t="inlineStr">
+      <c r="H453" t="inlineStr">
+        <is>
+          <t>D007</t>
+        </is>
+      </c>
+      <c r="I453" t="inlineStr">
+        <is>
+          <t>Hepatitis A</t>
+        </is>
+      </c>
+      <c r="J453" t="inlineStr">
         <is>
           <t>甲型肝炎</t>
         </is>
       </c>
-      <c r="K451" t="inlineStr">
+      <c r="K453" t="inlineStr">
         <is>
           <t>Viral</t>
         </is>
       </c>
-      <c r="L451" t="inlineStr">
+      <c r="L453" t="inlineStr">
         <is>
           <t>2026-09-06</t>
         </is>
       </c>
-      <c r="M451" t="inlineStr">
+      <c r="M453" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="N451" t="n">
+      <c r="N453" t="n">
         <v>10</v>
       </c>
-      <c r="O451" t="n">
+      <c r="O453" t="n">
         <v>10</v>
       </c>
-      <c r="R451" t="n">
+      <c r="R453" t="n">
         <v>0.008168084075657663</v>
       </c>
-      <c r="S451" t="inlineStr">
+      <c r="S453" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO451" t="inlineStr">
+      <c r="AO453" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP451" t="inlineStr">
+      <c r="AP453" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR451" t="inlineStr">
+      <c r="AR453" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS451" t="inlineStr"/>
-      <c r="AT451" t="n">
+      <c r="AS453" t="inlineStr"/>
+      <c r="AT453" t="n">
         <v>0</v>
       </c>
-      <c r="AU451" t="inlineStr">
+      <c r="AU453" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV451" t="inlineStr">
+      <c r="AV453" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="AW451" t="inlineStr">
+      <c r="AW453" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="AX451" t="inlineStr">
+      <c r="AX453" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="AY451" t="inlineStr">
+      <c r="AY453" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="AZ451" t="inlineStr">
+      <c r="AZ453" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="BA451" t="inlineStr">
+      <c r="BA453" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="BB451" t="inlineStr">
+      <c r="BB453" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="BC451" t="inlineStr">
+      <c r="BC453" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -84655,7 +85048,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="10">
@@ -84665,7 +85058,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="11">
@@ -84685,7 +85078,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="13">
@@ -84717,7 +85110,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>19118</v>
+        <v>19123</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d007/2026-2029.xlsx
+++ b/diseases/d007/2026-2029.xlsx
@@ -84052,13 +84052,13 @@
         </is>
       </c>
       <c r="N449" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="O449" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="R449" t="n">
-        <v>0.07075903303182025</v>
+        <v>0.1592078243215956</v>
       </c>
       <c r="S449" t="inlineStr">
         <is>
@@ -84216,10 +84216,10 @@
         </is>
       </c>
       <c r="N450" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="O450" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="U450" t="inlineStr">
         <is>
@@ -85110,7 +85110,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>19123</v>
+        <v>19128</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d007/2026-2029.xlsx
+++ b/diseases/d007/2026-2029.xlsx
@@ -83504,13 +83504,13 @@
         </is>
       </c>
       <c r="N446" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O446" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="R446" t="n">
-        <v>0.03557618341728275</v>
+        <v>0.08894045854320688</v>
       </c>
       <c r="S446" t="inlineStr">
         <is>
@@ -83668,10 +83668,10 @@
         </is>
       </c>
       <c r="N447" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O447" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="U447" t="inlineStr">
         <is>
@@ -85110,7 +85110,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>19128</v>
+        <v>19131</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d007/2026-2029.xlsx
+++ b/diseases/d007/2026-2029.xlsx
@@ -76932,13 +76932,13 @@
         </is>
       </c>
       <c r="N411" t="n">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="O411" t="n">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="R411" t="n">
-        <v>0.251936090092966</v>
+        <v>0.2577499998643421</v>
       </c>
       <c r="S411" t="inlineStr">
         <is>
@@ -83907,13 +83907,13 @@
         </is>
       </c>
       <c r="N448" t="n">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="O448" t="n">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="R448" t="n">
-        <v>0.09496052626581025</v>
+        <v>0.1143402255037307</v>
       </c>
       <c r="S448" t="inlineStr">
         <is>
@@ -84929,6 +84929,799 @@
       <c r="BC453" t="inlineStr">
         <is>
           <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>D007</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>hepatitis-a</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>Hepatitis A</t>
+        </is>
+      </c>
+      <c r="E454" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F454" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G454" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H454" t="inlineStr">
+        <is>
+          <t>D007</t>
+        </is>
+      </c>
+      <c r="I454" t="inlineStr">
+        <is>
+          <t>Hepatitis A</t>
+        </is>
+      </c>
+      <c r="J454" t="inlineStr">
+        <is>
+          <t>甲型肝炎</t>
+        </is>
+      </c>
+      <c r="K454" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L454" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M454" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N454" t="n">
+        <v>1</v>
+      </c>
+      <c r="O454" t="n">
+        <v>1</v>
+      </c>
+      <c r="P454" t="n">
+        <v>1</v>
+      </c>
+      <c r="R454" t="n">
+        <v>0.01693265755097047</v>
+      </c>
+      <c r="S454" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA454" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO454" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP454" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ454" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS454" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_A</t>
+        </is>
+      </c>
+      <c r="AT454" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU454" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV454" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW454" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX454" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY454" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ454" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA454" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB454" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC454" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>D007</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>hepatitis-a</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>Hepatitis A</t>
+        </is>
+      </c>
+      <c r="E455" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F455" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G455" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H455" t="inlineStr">
+        <is>
+          <t>D007</t>
+        </is>
+      </c>
+      <c r="I455" t="inlineStr">
+        <is>
+          <t>Hepatitis A</t>
+        </is>
+      </c>
+      <c r="J455" t="inlineStr">
+        <is>
+          <t>甲型肝炎</t>
+        </is>
+      </c>
+      <c r="K455" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L455" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M455" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N455" t="n">
+        <v>1</v>
+      </c>
+      <c r="O455" t="n">
+        <v>1</v>
+      </c>
+      <c r="P455" t="n">
+        <v>1</v>
+      </c>
+      <c r="U455" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A</t>
+        </is>
+      </c>
+      <c r="V455" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A</t>
+        </is>
+      </c>
+      <c r="W455" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X455" t="inlineStr">
+        <is>
+          <t>Acute Viral Hepatitis A</t>
+        </is>
+      </c>
+      <c r="Y455" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z455" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA455" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB455" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC455" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD455" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE455" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF455" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG455" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH455" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI455" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ455" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK455" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM455" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN455" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO455" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP455" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ455" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS455" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_A</t>
+        </is>
+      </c>
+      <c r="AT455" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU455" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV455" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW455" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX455" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY455" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ455" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA455" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB455" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC455" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>D007</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>hepatitis-a</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>Hepatitis A</t>
+        </is>
+      </c>
+      <c r="E456" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F456" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G456" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H456" t="inlineStr">
+        <is>
+          <t>D007</t>
+        </is>
+      </c>
+      <c r="I456" t="inlineStr">
+        <is>
+          <t>Hepatitis A</t>
+        </is>
+      </c>
+      <c r="J456" t="inlineStr">
+        <is>
+          <t>甲型肝炎</t>
+        </is>
+      </c>
+      <c r="K456" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L456" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="M456" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N456" t="n">
+        <v>9</v>
+      </c>
+      <c r="O456" t="n">
+        <v>9</v>
+      </c>
+      <c r="P456" t="n">
+        <v>9</v>
+      </c>
+      <c r="R456" t="n">
+        <v>0.002578534319492447</v>
+      </c>
+      <c r="S456" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U456" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AA456" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO456" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP456" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ456" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS456" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AT456" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU456" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV456" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW456" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX456" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY456" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ456" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA456" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB456" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC456" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>D007</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>hepatitis-a</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>Hepatitis A</t>
+        </is>
+      </c>
+      <c r="E457" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F457" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G457" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H457" t="inlineStr">
+        <is>
+          <t>D007</t>
+        </is>
+      </c>
+      <c r="I457" t="inlineStr">
+        <is>
+          <t>Hepatitis A</t>
+        </is>
+      </c>
+      <c r="J457" t="inlineStr">
+        <is>
+          <t>甲型肝炎</t>
+        </is>
+      </c>
+      <c r="K457" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L457" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="M457" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N457" t="n">
+        <v>9</v>
+      </c>
+      <c r="O457" t="n">
+        <v>9</v>
+      </c>
+      <c r="P457" t="n">
+        <v>9</v>
+      </c>
+      <c r="U457" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="V457" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="W457" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X457" t="inlineStr">
+        <is>
+          <t>Hepatitis A, Confirmed</t>
+        </is>
+      </c>
+      <c r="Y457" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z457" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA457" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB457" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC457" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD457" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE457" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF457" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG457" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH457" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI457" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ457" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK457" t="inlineStr">
+        <is>
+          <t>Confirmed hepatitis A component reported by NNDSS.</t>
+        </is>
+      </c>
+      <c r="AM457" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN457" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO457" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP457" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ457" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS457" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AT457" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU457" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV457" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW457" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX457" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY457" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ457" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA457" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB457" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC457" t="inlineStr">
+        <is>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -84965,7 +85758,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -85048,7 +85841,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="10">
@@ -85058,7 +85851,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>452</v>
+        <v>456</v>
       </c>
     </row>
     <row r="11">
@@ -85078,7 +85871,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="13">
@@ -85110,7 +85903,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>19131</v>
+        <v>19154</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d007/2026-2029.xlsx
+++ b/diseases/d007/2026-2029.xlsx
@@ -69499,13 +69499,13 @@
         </is>
       </c>
       <c r="N370" t="n">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O370" t="n">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="R370" t="n">
-        <v>0.2751917291784705</v>
+        <v>0.2771296991022626</v>
       </c>
       <c r="S370" t="inlineStr">
         <is>
@@ -75133,13 +75133,13 @@
         </is>
       </c>
       <c r="N400" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="O400" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="R400" t="n">
-        <v>0.07712904820991559</v>
+        <v>0.08080186002943539</v>
       </c>
       <c r="S400" t="inlineStr">
         <is>
@@ -83907,13 +83907,13 @@
         </is>
       </c>
       <c r="N448" t="n">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="O448" t="n">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="R448" t="n">
-        <v>0.1143402255037307</v>
+        <v>0.1414718044368194</v>
       </c>
       <c r="S448" t="inlineStr">
         <is>
@@ -85903,7 +85903,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>19154</v>
+        <v>19170</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d007/2026-2029.xlsx
+++ b/diseases/d007/2026-2029.xlsx
@@ -7209,7 +7209,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
@@ -8150,7 +8150,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -9091,7 +9091,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
@@ -10032,7 +10032,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -10973,7 +10973,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK56" t="inlineStr">
@@ -17968,7 +17968,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -18515,7 +18515,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK96" t="inlineStr">
@@ -19456,7 +19456,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -20397,7 +20397,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK106" t="inlineStr">
@@ -21338,7 +21338,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -27948,7 +27948,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK146" t="inlineStr">
@@ -28495,7 +28495,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK149" t="inlineStr">
@@ -29436,7 +29436,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK154" t="inlineStr">
@@ -30377,7 +30377,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -31318,7 +31318,7 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK164" t="inlineStr">
@@ -37919,7 +37919,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK199" t="inlineStr">
@@ -38466,7 +38466,7 @@
       </c>
       <c r="AJ202" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK202" t="inlineStr">
@@ -39407,7 +39407,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK207" t="inlineStr">
@@ -40348,7 +40348,7 @@
       </c>
       <c r="AJ212" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK212" t="inlineStr">
@@ -41289,7 +41289,7 @@
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK217" t="inlineStr">
@@ -48275,7 +48275,7 @@
       </c>
       <c r="AJ254" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK254" t="inlineStr">
@@ -48822,7 +48822,7 @@
       </c>
       <c r="AJ257" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK257" t="inlineStr">
@@ -49763,7 +49763,7 @@
       </c>
       <c r="AJ262" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK262" t="inlineStr">
@@ -50704,7 +50704,7 @@
       </c>
       <c r="AJ267" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK267" t="inlineStr">
@@ -51645,7 +51645,7 @@
       </c>
       <c r="AJ272" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK272" t="inlineStr">
@@ -52586,7 +52586,7 @@
       </c>
       <c r="AJ277" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK277" t="inlineStr">
@@ -60039,7 +60039,7 @@
       </c>
       <c r="AJ318" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK318" t="inlineStr">
@@ -60583,7 +60583,7 @@
       </c>
       <c r="AJ321" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK321" t="inlineStr">
@@ -61521,7 +61521,7 @@
       </c>
       <c r="AJ326" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK326" t="inlineStr">
@@ -62459,7 +62459,7 @@
       </c>
       <c r="AJ331" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK331" t="inlineStr">
@@ -63397,7 +63397,7 @@
       </c>
       <c r="AJ336" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK336" t="inlineStr">
@@ -65719,7 +65719,7 @@
       </c>
       <c r="AJ350" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK350" t="inlineStr">
@@ -71084,7 +71084,7 @@
       </c>
       <c r="AJ378" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK378" t="inlineStr">
@@ -71628,7 +71628,7 @@
       </c>
       <c r="AJ381" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK381" t="inlineStr">
@@ -72566,7 +72566,7 @@
       </c>
       <c r="AJ386" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK386" t="inlineStr">
@@ -73504,7 +73504,7 @@
       </c>
       <c r="AJ391" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK391" t="inlineStr">
@@ -74442,7 +74442,7 @@
       </c>
       <c r="AJ396" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK396" t="inlineStr">
@@ -75133,13 +75133,13 @@
         </is>
       </c>
       <c r="N400" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="O400" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="R400" t="n">
-        <v>0.08080186002943539</v>
+        <v>0.08447467184895517</v>
       </c>
       <c r="S400" t="inlineStr">
         <is>
@@ -76377,7 +76377,7 @@
       </c>
       <c r="AJ408" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK408" t="inlineStr">
@@ -76893,12 +76893,12 @@
       </c>
       <c r="F411" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G411" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H411" t="inlineStr">
@@ -76932,13 +76932,13 @@
         </is>
       </c>
       <c r="N411" t="n">
-        <v>133</v>
+        <v>4</v>
       </c>
       <c r="O411" t="n">
-        <v>133</v>
+        <v>4</v>
       </c>
       <c r="R411" t="n">
-        <v>0.2577499998643421</v>
+        <v>0.05421081120786837</v>
       </c>
       <c r="S411" t="inlineStr">
         <is>
@@ -76971,42 +76971,42 @@
       </c>
       <c r="AV411" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW411" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX411" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY411" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ411" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA411" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB411" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC411" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -77038,12 +77038,12 @@
       </c>
       <c r="F412" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G412" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H412" t="inlineStr">
@@ -77077,100 +77077,81 @@
         </is>
       </c>
       <c r="N412" t="n">
-        <v>9</v>
+        <v>133</v>
       </c>
       <c r="O412" t="n">
-        <v>9</v>
+        <v>133</v>
       </c>
       <c r="R412" t="n">
-        <v>0.1592078243215956</v>
+        <v>0.2577499998643421</v>
       </c>
       <c r="S412" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U412" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_201_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA412" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO412" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP412" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ412" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR412" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS412" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_201_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS412" t="inlineStr"/>
       <c r="AT412" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU412" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV412" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW412" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX412" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY412" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ412" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA412" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB412" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC412" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -77197,7 +77178,7 @@
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F413" t="inlineStr">
@@ -77246,98 +77227,23 @@
       <c r="O413" t="n">
         <v>9</v>
       </c>
+      <c r="R413" t="n">
+        <v>0.1592078243215956</v>
+      </c>
+      <c r="S413" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U413" t="inlineStr">
         <is>
           <t>SER_NO_FHI_201_MONTHLY</t>
         </is>
       </c>
-      <c r="V413" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_201_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W413" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X413" t="inlineStr">
-        <is>
-          <t>Hepatitt A</t>
-        </is>
-      </c>
-      <c r="Y413" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z413" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA413" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB413" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC413" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD413" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE413" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF413" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG413" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH413" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI413" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ413" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK413" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM413" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN413" t="b">
-        <v>1</v>
       </c>
       <c r="AO413" t="inlineStr">
         <is>
@@ -77436,17 +77342,17 @@
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F414" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G414" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H414" t="inlineStr">
@@ -77480,22 +77386,39 @@
         </is>
       </c>
       <c r="N414" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="O414" t="n">
-        <v>5</v>
-      </c>
-      <c r="R414" t="n">
-        <v>0.09456302332359146</v>
-      </c>
-      <c r="S414" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>9</v>
       </c>
       <c r="U414" t="inlineStr">
         <is>
-          <t>SER_NZ_HEPATITIS_A_MONTHLY</t>
+          <t>SER_NO_FHI_201_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V414" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_201_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W414" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X414" t="inlineStr">
+        <is>
+          <t>Hepatitt A</t>
+        </is>
+      </c>
+      <c r="Y414" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z414" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA414" t="inlineStr">
@@ -77503,6 +77426,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB414" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC414" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD414" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE414" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF414" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG414" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH414" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI414" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ414" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK414" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM414" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN414" t="b">
+        <v>1</v>
+      </c>
       <c r="AO414" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -77510,7 +77491,7 @@
       </c>
       <c r="AP414" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ414" t="inlineStr">
@@ -77518,57 +77499,62 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR414" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS414" t="inlineStr">
         <is>
-          <t>SER_NZ_HEPATITIS_A_MONTHLY</t>
+          <t>SER_NO_FHI_201_MONTHLY</t>
         </is>
       </c>
       <c r="AT414" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU414" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV414" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW414" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX414" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY414" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ414" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA414" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB414" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC414" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -77595,7 +77581,7 @@
       </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F415" t="inlineStr">
@@ -77644,98 +77630,23 @@
       <c r="O415" t="n">
         <v>5</v>
       </c>
+      <c r="R415" t="n">
+        <v>0.09456302332359146</v>
+      </c>
+      <c r="S415" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U415" t="inlineStr">
         <is>
           <t>SER_NZ_HEPATITIS_A_MONTHLY</t>
         </is>
       </c>
-      <c r="V415" t="inlineStr">
-        <is>
-          <t>SER_NZ_HEPATITIS_A_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W415" t="inlineStr">
-        <is>
-          <t>SRC_NZ_PHS</t>
-        </is>
-      </c>
-      <c r="X415" t="inlineStr">
-        <is>
-          <t>Hepatitis A</t>
-        </is>
-      </c>
-      <c r="Y415" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z415" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA415" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB415" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC415" t="inlineStr">
-        <is>
-          <t>country:NZ:national</t>
-        </is>
-      </c>
-      <c r="AD415" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE415" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF415" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG415" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH415" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI415" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ415" t="inlineStr">
-        <is>
-          <t>NZ_PHS_current</t>
-        </is>
-      </c>
-      <c r="AK415" t="inlineStr">
-        <is>
-          <t>New Zealand PHF Science monthly hepatitis A notifications.</t>
-        </is>
-      </c>
-      <c r="AM415" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN415" t="b">
-        <v>1</v>
       </c>
       <c r="AO415" t="inlineStr">
         <is>
@@ -77829,17 +77740,17 @@
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F416" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G416" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H416" t="inlineStr">
@@ -77873,22 +77784,39 @@
         </is>
       </c>
       <c r="N416" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="O416" t="n">
-        <v>20</v>
-      </c>
-      <c r="R416" t="n">
-        <v>0.1868976085656669</v>
-      </c>
-      <c r="S416" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>5</v>
       </c>
       <c r="U416" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_A</t>
+          <t>SER_NZ_HEPATITIS_A_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V416" t="inlineStr">
+        <is>
+          <t>SER_NZ_HEPATITIS_A_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W416" t="inlineStr">
+        <is>
+          <t>SRC_NZ_PHS</t>
+        </is>
+      </c>
+      <c r="X416" t="inlineStr">
+        <is>
+          <t>Hepatitis A</t>
+        </is>
+      </c>
+      <c r="Y416" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z416" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA416" t="inlineStr">
@@ -77896,6 +77824,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB416" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC416" t="inlineStr">
+        <is>
+          <t>country:NZ:national</t>
+        </is>
+      </c>
+      <c r="AD416" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE416" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF416" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG416" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH416" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI416" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ416" t="inlineStr">
+        <is>
+          <t>NZ_PHS_current</t>
+        </is>
+      </c>
+      <c r="AK416" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science monthly hepatitis A notifications.</t>
+        </is>
+      </c>
+      <c r="AM416" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN416" t="b">
+        <v>1</v>
+      </c>
       <c r="AO416" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -77903,7 +77889,7 @@
       </c>
       <c r="AP416" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ416" t="inlineStr">
@@ -77911,62 +77897,57 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR416" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS416" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_A</t>
+          <t>SER_NZ_HEPATITIS_A_MONTHLY</t>
         </is>
       </c>
       <c r="AT416" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU416" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV416" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW416" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX416" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY416" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ416" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA416" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB416" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC416" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -77993,7 +77974,7 @@
       </c>
       <c r="E417" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F417" t="inlineStr">
@@ -78042,98 +78023,23 @@
       <c r="O417" t="n">
         <v>20</v>
       </c>
+      <c r="R417" t="n">
+        <v>0.1868976085656669</v>
+      </c>
+      <c r="S417" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U417" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_HEPATITIS_A</t>
         </is>
       </c>
-      <c r="V417" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_A</t>
-        </is>
-      </c>
-      <c r="W417" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X417" t="inlineStr">
-        <is>
-          <t>Hepatit A</t>
-        </is>
-      </c>
-      <c r="Y417" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z417" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA417" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB417" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC417" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD417" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE417" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF417" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG417" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH417" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI417" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ417" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_current</t>
-        </is>
-      </c>
-      <c r="AK417" t="inlineStr">
-        <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
-        </is>
-      </c>
-      <c r="AM417" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN417" t="b">
-        <v>1</v>
       </c>
       <c r="AO417" t="inlineStr">
         <is>
@@ -78232,17 +78138,17 @@
       </c>
       <c r="E418" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F418" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G418" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H418" t="inlineStr">
@@ -78276,22 +78182,39 @@
         </is>
       </c>
       <c r="N418" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="O418" t="n">
-        <v>13</v>
-      </c>
-      <c r="R418" t="n">
-        <v>0.05649400180367965</v>
-      </c>
-      <c r="S418" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>20</v>
       </c>
       <c r="U418" t="inlineStr">
         <is>
-          <t>SER_TW_HEPATITIS_A_0701</t>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_A</t>
+        </is>
+      </c>
+      <c r="V418" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_A</t>
+        </is>
+      </c>
+      <c r="W418" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X418" t="inlineStr">
+        <is>
+          <t>Hepatit A</t>
+        </is>
+      </c>
+      <c r="Y418" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z418" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA418" t="inlineStr">
@@ -78299,6 +78222,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB418" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC418" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD418" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE418" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF418" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG418" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH418" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI418" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ418" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK418" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM418" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN418" t="b">
+        <v>1</v>
+      </c>
       <c r="AO418" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -78306,7 +78287,7 @@
       </c>
       <c r="AP418" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ418" t="inlineStr">
@@ -78314,57 +78295,62 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR418" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS418" t="inlineStr">
         <is>
-          <t>SER_TW_HEPATITIS_A_0701</t>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_A</t>
         </is>
       </c>
       <c r="AT418" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU418" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV418" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW418" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX418" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY418" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ418" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA418" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB418" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC418" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -78391,7 +78377,7 @@
       </c>
       <c r="E419" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F419" t="inlineStr">
@@ -78440,98 +78426,23 @@
       <c r="O419" t="n">
         <v>13</v>
       </c>
+      <c r="R419" t="n">
+        <v>0.05649400180367965</v>
+      </c>
+      <c r="S419" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U419" t="inlineStr">
         <is>
           <t>SER_TW_HEPATITIS_A_0701</t>
         </is>
       </c>
-      <c r="V419" t="inlineStr">
-        <is>
-          <t>SER_TW_HEPATITIS_A_0701</t>
-        </is>
-      </c>
-      <c r="W419" t="inlineStr">
-        <is>
-          <t>SRC_TW_NIDSS</t>
-        </is>
-      </c>
-      <c r="X419" t="inlineStr">
-        <is>
-          <t>急性病毒性Ａ型肝炎</t>
-        </is>
-      </c>
-      <c r="Y419" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z419" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA419" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB419" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC419" t="inlineStr">
-        <is>
-          <t>country:TW:national</t>
-        </is>
-      </c>
-      <c r="AD419" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE419" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF419" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG419" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH419" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI419" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ419" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK419" t="inlineStr">
-        <is>
-          <t>Acute hepatitis A, code 0701. D067 remains deprecated.</t>
-        </is>
-      </c>
-      <c r="AM419" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN419" t="b">
-        <v>1</v>
       </c>
       <c r="AO419" t="inlineStr">
         <is>
@@ -78625,17 +78536,17 @@
       </c>
       <c r="E420" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F420" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G420" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H420" t="inlineStr">
@@ -78669,35 +78580,107 @@
         </is>
       </c>
       <c r="N420" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="O420" t="n">
-        <v>2</v>
-      </c>
-      <c r="P420" t="n">
-        <v>2</v>
-      </c>
-      <c r="R420" t="n">
-        <v>0.0005730076265538771</v>
-      </c>
-      <c r="S420" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>13</v>
       </c>
       <c r="U420" t="inlineStr">
         <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+          <t>SER_TW_HEPATITIS_A_0701</t>
+        </is>
+      </c>
+      <c r="V420" t="inlineStr">
+        <is>
+          <t>SER_TW_HEPATITIS_A_0701</t>
+        </is>
+      </c>
+      <c r="W420" t="inlineStr">
+        <is>
+          <t>SRC_TW_NIDSS</t>
+        </is>
+      </c>
+      <c r="X420" t="inlineStr">
+        <is>
+          <t>急性病毒性Ａ型肝炎</t>
+        </is>
+      </c>
+      <c r="Y420" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z420" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA420" t="inlineStr">
         <is>
-          <t>weekly</t>
-        </is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB420" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC420" t="inlineStr">
+        <is>
+          <t>country:TW:national</t>
+        </is>
+      </c>
+      <c r="AD420" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE420" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF420" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG420" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH420" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI420" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ420" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK420" t="inlineStr">
+        <is>
+          <t>Acute hepatitis A, code 0701. D067 remains deprecated.</t>
+        </is>
+      </c>
+      <c r="AM420" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN420" t="b">
+        <v>1</v>
       </c>
       <c r="AO420" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP420" t="inlineStr">
@@ -78707,12 +78690,12 @@
       </c>
       <c r="AQ420" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS420" t="inlineStr">
         <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+          <t>SER_TW_HEPATITIS_A_0701</t>
         </is>
       </c>
       <c r="AT420" t="n">
@@ -78720,47 +78703,47 @@
       </c>
       <c r="AU420" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV420" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW420" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX420" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY420" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ420" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA420" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB420" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC420" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -78787,7 +78770,7 @@
       </c>
       <c r="E421" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F421" t="inlineStr">
@@ -78839,98 +78822,23 @@
       <c r="P421" t="n">
         <v>2</v>
       </c>
+      <c r="R421" t="n">
+        <v>0.0005730076265538771</v>
+      </c>
+      <c r="S421" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U421" t="inlineStr">
         <is>
           <t>SER_US_HEPATITIS_A_CONFIRMED</t>
         </is>
       </c>
-      <c r="V421" t="inlineStr">
-        <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
-        </is>
-      </c>
-      <c r="W421" t="inlineStr">
-        <is>
-          <t>SRC_US_NNDSS</t>
-        </is>
-      </c>
-      <c r="X421" t="inlineStr">
-        <is>
-          <t>Hepatitis A, Confirmed</t>
-        </is>
-      </c>
-      <c r="Y421" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z421" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA421" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB421" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC421" t="inlineStr">
-        <is>
-          <t>country:US:national</t>
-        </is>
-      </c>
-      <c r="AD421" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE421" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF421" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG421" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH421" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI421" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ421" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK421" t="inlineStr">
-        <is>
-          <t>Confirmed hepatitis A component reported by NNDSS.</t>
-        </is>
-      </c>
-      <c r="AM421" t="inlineStr">
-        <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="AN421" t="b">
-        <v>1</v>
       </c>
       <c r="AO421" t="inlineStr">
         <is>
@@ -79024,17 +78932,17 @@
       </c>
       <c r="E422" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F422" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G422" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H422" t="inlineStr">
@@ -79059,7 +78967,7 @@
       </c>
       <c r="L422" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M422" t="inlineStr">
@@ -79068,81 +78976,173 @@
         </is>
       </c>
       <c r="N422" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="O422" t="n">
-        <v>14</v>
-      </c>
-      <c r="R422" t="n">
-        <v>0.01143531770592073</v>
-      </c>
-      <c r="S422" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="P422" t="n">
+        <v>2</v>
+      </c>
+      <c r="U422" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="V422" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="W422" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X422" t="inlineStr">
+        <is>
+          <t>Hepatitis A, Confirmed</t>
+        </is>
+      </c>
+      <c r="Y422" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z422" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA422" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB422" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC422" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD422" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE422" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF422" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG422" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH422" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI422" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ422" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK422" t="inlineStr">
+        <is>
+          <t>Confirmed hepatitis A component reported by NNDSS.</t>
+        </is>
+      </c>
+      <c r="AM422" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN422" t="b">
+        <v>1</v>
       </c>
       <c r="AO422" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP422" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR422" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS422" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ422" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS422" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
       <c r="AT422" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU422" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV422" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW422" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX422" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY422" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ422" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA422" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB422" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC422" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -79174,12 +79174,12 @@
       </c>
       <c r="F423" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G423" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H423" t="inlineStr">
@@ -79213,93 +79213,81 @@
         </is>
       </c>
       <c r="N423" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="O423" t="n">
-        <v>1</v>
-      </c>
-      <c r="P423" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="R423" t="n">
-        <v>0.01693265755097047</v>
+        <v>0.01143531770592073</v>
       </c>
       <c r="S423" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA423" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO423" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP423" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ423" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS423" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_A</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR423" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS423" t="inlineStr"/>
       <c r="AT423" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU423" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV423" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW423" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX423" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY423" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ423" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA423" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB423" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC423" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -79326,7 +79314,7 @@
       </c>
       <c r="E424" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F424" t="inlineStr">
@@ -79378,98 +79366,18 @@
       <c r="P424" t="n">
         <v>1</v>
       </c>
-      <c r="U424" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A</t>
-        </is>
-      </c>
-      <c r="V424" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A</t>
-        </is>
-      </c>
-      <c r="W424" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X424" t="inlineStr">
-        <is>
-          <t>Acute Viral Hepatitis A</t>
-        </is>
-      </c>
-      <c r="Y424" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z424" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R424" t="n">
+        <v>0.01693265755097047</v>
+      </c>
+      <c r="S424" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA424" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB424" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC424" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD424" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE424" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF424" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG424" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH424" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI424" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ424" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK424" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM424" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN424" t="b">
-        <v>1</v>
       </c>
       <c r="AO424" t="inlineStr">
         <is>
@@ -79563,17 +79471,17 @@
       </c>
       <c r="E425" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F425" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G425" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H425" t="inlineStr">
@@ -79598,7 +79506,7 @@
       </c>
       <c r="L425" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M425" t="inlineStr">
@@ -79607,25 +79515,42 @@
         </is>
       </c>
       <c r="N425" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="O425" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="P425" t="n">
-        <v>6</v>
-      </c>
-      <c r="R425" t="n">
-        <v>0.001719022879661631</v>
-      </c>
-      <c r="S425" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="U425" t="inlineStr">
         <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A</t>
+        </is>
+      </c>
+      <c r="V425" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A</t>
+        </is>
+      </c>
+      <c r="W425" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X425" t="inlineStr">
+        <is>
+          <t>Acute Viral Hepatitis A</t>
+        </is>
+      </c>
+      <c r="Y425" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z425" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA425" t="inlineStr">
@@ -79633,72 +79558,130 @@
           <t>weekly</t>
         </is>
       </c>
+      <c r="AB425" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC425" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD425" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE425" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF425" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG425" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH425" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI425" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ425" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK425" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM425" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN425" t="b">
+        <v>1</v>
+      </c>
       <c r="AO425" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP425" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ425" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS425" t="inlineStr">
         <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_A</t>
         </is>
       </c>
       <c r="AT425" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU425" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV425" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW425" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX425" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY425" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ425" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA425" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB425" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC425" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -79725,7 +79708,7 @@
       </c>
       <c r="E426" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F426" t="inlineStr">
@@ -79777,98 +79760,23 @@
       <c r="P426" t="n">
         <v>6</v>
       </c>
+      <c r="R426" t="n">
+        <v>0.001719022879661631</v>
+      </c>
+      <c r="S426" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U426" t="inlineStr">
         <is>
           <t>SER_US_HEPATITIS_A_CONFIRMED</t>
         </is>
       </c>
-      <c r="V426" t="inlineStr">
-        <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
-        </is>
-      </c>
-      <c r="W426" t="inlineStr">
-        <is>
-          <t>SRC_US_NNDSS</t>
-        </is>
-      </c>
-      <c r="X426" t="inlineStr">
-        <is>
-          <t>Hepatitis A, Confirmed</t>
-        </is>
-      </c>
-      <c r="Y426" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z426" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA426" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB426" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC426" t="inlineStr">
-        <is>
-          <t>country:US:national</t>
-        </is>
-      </c>
-      <c r="AD426" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE426" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF426" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG426" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH426" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI426" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ426" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK426" t="inlineStr">
-        <is>
-          <t>Confirmed hepatitis A component reported by NNDSS.</t>
-        </is>
-      </c>
-      <c r="AM426" t="inlineStr">
-        <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="AN426" t="b">
-        <v>1</v>
       </c>
       <c r="AO426" t="inlineStr">
         <is>
@@ -79962,17 +79870,17 @@
       </c>
       <c r="E427" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F427" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G427" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H427" t="inlineStr">
@@ -79997,7 +79905,7 @@
       </c>
       <c r="L427" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="M427" t="inlineStr">
@@ -80006,81 +79914,173 @@
         </is>
       </c>
       <c r="N427" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="O427" t="n">
-        <v>11</v>
-      </c>
-      <c r="R427" t="n">
-        <v>0.00898489248322343</v>
-      </c>
-      <c r="S427" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>6</v>
+      </c>
+      <c r="P427" t="n">
+        <v>6</v>
+      </c>
+      <c r="U427" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="V427" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="W427" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X427" t="inlineStr">
+        <is>
+          <t>Hepatitis A, Confirmed</t>
+        </is>
+      </c>
+      <c r="Y427" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z427" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA427" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB427" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC427" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD427" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE427" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF427" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG427" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH427" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI427" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ427" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK427" t="inlineStr">
+        <is>
+          <t>Confirmed hepatitis A component reported by NNDSS.</t>
+        </is>
+      </c>
+      <c r="AM427" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN427" t="b">
+        <v>1</v>
       </c>
       <c r="AO427" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP427" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR427" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS427" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ427" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS427" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
       <c r="AT427" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU427" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV427" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW427" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX427" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY427" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ427" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA427" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB427" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC427" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -80112,12 +80112,12 @@
       </c>
       <c r="F428" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G428" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H428" t="inlineStr">
@@ -80151,93 +80151,81 @@
         </is>
       </c>
       <c r="N428" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="O428" t="n">
-        <v>2</v>
-      </c>
-      <c r="P428" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="R428" t="n">
-        <v>0.03386531510194095</v>
+        <v>0.00898489248322343</v>
       </c>
       <c r="S428" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA428" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO428" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP428" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ428" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS428" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_A</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR428" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS428" t="inlineStr"/>
       <c r="AT428" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU428" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV428" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW428" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX428" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY428" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ428" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA428" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB428" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC428" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -80264,7 +80252,7 @@
       </c>
       <c r="E429" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F429" t="inlineStr">
@@ -80316,98 +80304,18 @@
       <c r="P429" t="n">
         <v>2</v>
       </c>
-      <c r="U429" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A</t>
-        </is>
-      </c>
-      <c r="V429" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A</t>
-        </is>
-      </c>
-      <c r="W429" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X429" t="inlineStr">
-        <is>
-          <t>Acute Viral Hepatitis A</t>
-        </is>
-      </c>
-      <c r="Y429" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z429" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R429" t="n">
+        <v>0.03386531510194095</v>
+      </c>
+      <c r="S429" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA429" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB429" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC429" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD429" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE429" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF429" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG429" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH429" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI429" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ429" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK429" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM429" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN429" t="b">
-        <v>1</v>
       </c>
       <c r="AO429" t="inlineStr">
         <is>
@@ -80501,17 +80409,17 @@
       </c>
       <c r="E430" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F430" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G430" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H430" t="inlineStr">
@@ -80536,7 +80444,7 @@
       </c>
       <c r="L430" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M430" t="inlineStr">
@@ -80545,25 +80453,42 @@
         </is>
       </c>
       <c r="N430" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="O430" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="P430" t="n">
-        <v>9</v>
-      </c>
-      <c r="R430" t="n">
-        <v>0.002578534319492447</v>
-      </c>
-      <c r="S430" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>2</v>
       </c>
       <c r="U430" t="inlineStr">
         <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A</t>
+        </is>
+      </c>
+      <c r="V430" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A</t>
+        </is>
+      </c>
+      <c r="W430" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X430" t="inlineStr">
+        <is>
+          <t>Acute Viral Hepatitis A</t>
+        </is>
+      </c>
+      <c r="Y430" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z430" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA430" t="inlineStr">
@@ -80571,72 +80496,130 @@
           <t>weekly</t>
         </is>
       </c>
+      <c r="AB430" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC430" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD430" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE430" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF430" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG430" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH430" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI430" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ430" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK430" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM430" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN430" t="b">
+        <v>1</v>
+      </c>
       <c r="AO430" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP430" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ430" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS430" t="inlineStr">
         <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_A</t>
         </is>
       </c>
       <c r="AT430" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU430" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV430" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW430" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX430" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY430" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ430" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA430" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB430" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC430" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -80663,7 +80646,7 @@
       </c>
       <c r="E431" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F431" t="inlineStr">
@@ -80715,98 +80698,23 @@
       <c r="P431" t="n">
         <v>9</v>
       </c>
+      <c r="R431" t="n">
+        <v>0.002578534319492447</v>
+      </c>
+      <c r="S431" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U431" t="inlineStr">
         <is>
           <t>SER_US_HEPATITIS_A_CONFIRMED</t>
         </is>
       </c>
-      <c r="V431" t="inlineStr">
-        <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
-        </is>
-      </c>
-      <c r="W431" t="inlineStr">
-        <is>
-          <t>SRC_US_NNDSS</t>
-        </is>
-      </c>
-      <c r="X431" t="inlineStr">
-        <is>
-          <t>Hepatitis A, Confirmed</t>
-        </is>
-      </c>
-      <c r="Y431" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z431" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA431" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB431" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC431" t="inlineStr">
-        <is>
-          <t>country:US:national</t>
-        </is>
-      </c>
-      <c r="AD431" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE431" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF431" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG431" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH431" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI431" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ431" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK431" t="inlineStr">
-        <is>
-          <t>Confirmed hepatitis A component reported by NNDSS.</t>
-        </is>
-      </c>
-      <c r="AM431" t="inlineStr">
-        <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="AN431" t="b">
-        <v>1</v>
       </c>
       <c r="AO431" t="inlineStr">
         <is>
@@ -80900,17 +80808,17 @@
       </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F432" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G432" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H432" t="inlineStr">
@@ -80935,7 +80843,7 @@
       </c>
       <c r="L432" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="M432" t="inlineStr">
@@ -80944,81 +80852,173 @@
         </is>
       </c>
       <c r="N432" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O432" t="n">
-        <v>8</v>
-      </c>
-      <c r="R432" t="n">
-        <v>0.00653446726052613</v>
-      </c>
-      <c r="S432" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>9</v>
+      </c>
+      <c r="P432" t="n">
+        <v>9</v>
+      </c>
+      <c r="U432" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="V432" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="W432" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X432" t="inlineStr">
+        <is>
+          <t>Hepatitis A, Confirmed</t>
+        </is>
+      </c>
+      <c r="Y432" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z432" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA432" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB432" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC432" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD432" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE432" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF432" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG432" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH432" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI432" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ432" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK432" t="inlineStr">
+        <is>
+          <t>Confirmed hepatitis A component reported by NNDSS.</t>
+        </is>
+      </c>
+      <c r="AM432" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN432" t="b">
+        <v>1</v>
       </c>
       <c r="AO432" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP432" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR432" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS432" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ432" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS432" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
       <c r="AT432" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU432" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV432" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW432" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX432" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY432" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ432" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA432" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB432" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC432" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -81050,12 +81050,12 @@
       </c>
       <c r="F433" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G433" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H433" t="inlineStr">
@@ -81089,93 +81089,81 @@
         </is>
       </c>
       <c r="N433" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="O433" t="n">
-        <v>1</v>
-      </c>
-      <c r="P433" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="R433" t="n">
-        <v>0.01693265755097047</v>
+        <v>0.00653446726052613</v>
       </c>
       <c r="S433" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA433" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO433" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP433" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ433" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS433" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_A</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR433" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS433" t="inlineStr"/>
       <c r="AT433" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU433" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV433" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW433" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX433" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY433" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ433" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA433" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB433" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC433" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -81202,7 +81190,7 @@
       </c>
       <c r="E434" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F434" t="inlineStr">
@@ -81254,98 +81242,18 @@
       <c r="P434" t="n">
         <v>1</v>
       </c>
-      <c r="U434" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A</t>
-        </is>
-      </c>
-      <c r="V434" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A</t>
-        </is>
-      </c>
-      <c r="W434" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X434" t="inlineStr">
-        <is>
-          <t>Acute Viral Hepatitis A</t>
-        </is>
-      </c>
-      <c r="Y434" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z434" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R434" t="n">
+        <v>0.01693265755097047</v>
+      </c>
+      <c r="S434" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA434" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB434" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC434" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD434" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE434" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF434" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG434" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH434" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI434" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ434" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK434" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM434" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN434" t="b">
-        <v>1</v>
       </c>
       <c r="AO434" t="inlineStr">
         <is>
@@ -81439,17 +81347,17 @@
       </c>
       <c r="E435" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F435" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G435" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H435" t="inlineStr">
@@ -81474,7 +81382,7 @@
       </c>
       <c r="L435" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M435" t="inlineStr">
@@ -81483,25 +81391,42 @@
         </is>
       </c>
       <c r="N435" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O435" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P435" t="n">
-        <v>3</v>
-      </c>
-      <c r="R435" t="n">
-        <v>0.0008595114398308156</v>
-      </c>
-      <c r="S435" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="U435" t="inlineStr">
         <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A</t>
+        </is>
+      </c>
+      <c r="V435" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A</t>
+        </is>
+      </c>
+      <c r="W435" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X435" t="inlineStr">
+        <is>
+          <t>Acute Viral Hepatitis A</t>
+        </is>
+      </c>
+      <c r="Y435" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z435" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA435" t="inlineStr">
@@ -81509,72 +81434,130 @@
           <t>weekly</t>
         </is>
       </c>
+      <c r="AB435" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC435" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD435" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE435" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF435" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG435" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH435" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI435" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ435" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK435" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM435" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN435" t="b">
+        <v>1</v>
+      </c>
       <c r="AO435" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP435" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ435" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS435" t="inlineStr">
         <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_A</t>
         </is>
       </c>
       <c r="AT435" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU435" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV435" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW435" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX435" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY435" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ435" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA435" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB435" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC435" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -81601,7 +81584,7 @@
       </c>
       <c r="E436" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F436" t="inlineStr">
@@ -81653,98 +81636,23 @@
       <c r="P436" t="n">
         <v>3</v>
       </c>
+      <c r="R436" t="n">
+        <v>0.0008595114398308156</v>
+      </c>
+      <c r="S436" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U436" t="inlineStr">
         <is>
           <t>SER_US_HEPATITIS_A_CONFIRMED</t>
         </is>
       </c>
-      <c r="V436" t="inlineStr">
-        <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
-        </is>
-      </c>
-      <c r="W436" t="inlineStr">
-        <is>
-          <t>SRC_US_NNDSS</t>
-        </is>
-      </c>
-      <c r="X436" t="inlineStr">
-        <is>
-          <t>Hepatitis A, Confirmed</t>
-        </is>
-      </c>
-      <c r="Y436" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z436" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA436" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB436" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC436" t="inlineStr">
-        <is>
-          <t>country:US:national</t>
-        </is>
-      </c>
-      <c r="AD436" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE436" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF436" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG436" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH436" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI436" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ436" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK436" t="inlineStr">
-        <is>
-          <t>Confirmed hepatitis A component reported by NNDSS.</t>
-        </is>
-      </c>
-      <c r="AM436" t="inlineStr">
-        <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="AN436" t="b">
-        <v>1</v>
       </c>
       <c r="AO436" t="inlineStr">
         <is>
@@ -81838,17 +81746,17 @@
       </c>
       <c r="E437" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F437" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G437" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H437" t="inlineStr">
@@ -81873,7 +81781,7 @@
       </c>
       <c r="L437" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="M437" t="inlineStr">
@@ -81882,81 +81790,173 @@
         </is>
       </c>
       <c r="N437" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="O437" t="n">
-        <v>21</v>
-      </c>
-      <c r="R437" t="n">
-        <v>0.01715297655888109</v>
-      </c>
-      <c r="S437" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="P437" t="n">
+        <v>3</v>
+      </c>
+      <c r="U437" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="V437" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="W437" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X437" t="inlineStr">
+        <is>
+          <t>Hepatitis A, Confirmed</t>
+        </is>
+      </c>
+      <c r="Y437" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z437" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA437" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB437" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC437" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD437" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE437" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF437" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG437" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH437" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI437" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ437" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK437" t="inlineStr">
+        <is>
+          <t>Confirmed hepatitis A component reported by NNDSS.</t>
+        </is>
+      </c>
+      <c r="AM437" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN437" t="b">
+        <v>1</v>
       </c>
       <c r="AO437" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP437" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR437" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS437" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ437" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS437" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
       <c r="AT437" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU437" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV437" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW437" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX437" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY437" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ437" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA437" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB437" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC437" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -81988,12 +81988,12 @@
       </c>
       <c r="F438" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G438" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H438" t="inlineStr">
@@ -82027,93 +82027,81 @@
         </is>
       </c>
       <c r="N438" t="n">
+        <v>21</v>
+      </c>
+      <c r="O438" t="n">
+        <v>21</v>
+      </c>
+      <c r="R438" t="n">
+        <v>0.01715297655888109</v>
+      </c>
+      <c r="S438" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO438" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP438" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR438" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS438" t="inlineStr"/>
+      <c r="AT438" t="n">
         <v>0</v>
       </c>
-      <c r="O438" t="n">
-        <v>0</v>
-      </c>
-      <c r="P438" t="n">
-        <v>0</v>
-      </c>
-      <c r="R438" t="n">
-        <v>0</v>
-      </c>
-      <c r="S438" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AA438" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AO438" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP438" t="inlineStr">
-        <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ438" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS438" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_A</t>
-        </is>
-      </c>
-      <c r="AT438" t="n">
-        <v>2</v>
-      </c>
       <c r="AU438" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV438" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW438" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX438" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY438" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ438" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA438" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB438" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC438" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -82140,7 +82128,7 @@
       </c>
       <c r="E439" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F439" t="inlineStr">
@@ -82192,98 +82180,18 @@
       <c r="P439" t="n">
         <v>0</v>
       </c>
-      <c r="U439" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A</t>
-        </is>
-      </c>
-      <c r="V439" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A</t>
-        </is>
-      </c>
-      <c r="W439" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X439" t="inlineStr">
-        <is>
-          <t>Acute Viral Hepatitis A</t>
-        </is>
-      </c>
-      <c r="Y439" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z439" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R439" t="n">
+        <v>0</v>
+      </c>
+      <c r="S439" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA439" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB439" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC439" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD439" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE439" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF439" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG439" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH439" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI439" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ439" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK439" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM439" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN439" t="b">
-        <v>1</v>
       </c>
       <c r="AO439" t="inlineStr">
         <is>
@@ -82377,17 +82285,17 @@
       </c>
       <c r="E440" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F440" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G440" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H440" t="inlineStr">
@@ -82412,7 +82320,7 @@
       </c>
       <c r="L440" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M440" t="inlineStr">
@@ -82421,25 +82329,42 @@
         </is>
       </c>
       <c r="N440" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O440" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P440" t="n">
-        <v>6</v>
-      </c>
-      <c r="R440" t="n">
-        <v>0.001719022879661631</v>
-      </c>
-      <c r="S440" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="U440" t="inlineStr">
         <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A</t>
+        </is>
+      </c>
+      <c r="V440" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A</t>
+        </is>
+      </c>
+      <c r="W440" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X440" t="inlineStr">
+        <is>
+          <t>Acute Viral Hepatitis A</t>
+        </is>
+      </c>
+      <c r="Y440" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z440" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA440" t="inlineStr">
@@ -82447,72 +82372,130 @@
           <t>weekly</t>
         </is>
       </c>
+      <c r="AB440" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC440" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD440" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE440" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF440" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG440" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH440" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI440" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ440" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK440" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM440" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN440" t="b">
+        <v>1</v>
+      </c>
       <c r="AO440" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP440" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ440" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS440" t="inlineStr">
         <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_A</t>
         </is>
       </c>
       <c r="AT440" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU440" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV440" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW440" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX440" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY440" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ440" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA440" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB440" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC440" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -82539,7 +82522,7 @@
       </c>
       <c r="E441" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F441" t="inlineStr">
@@ -82591,98 +82574,23 @@
       <c r="P441" t="n">
         <v>6</v>
       </c>
+      <c r="R441" t="n">
+        <v>0.001719022879661631</v>
+      </c>
+      <c r="S441" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U441" t="inlineStr">
         <is>
           <t>SER_US_HEPATITIS_A_CONFIRMED</t>
         </is>
       </c>
-      <c r="V441" t="inlineStr">
-        <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
-        </is>
-      </c>
-      <c r="W441" t="inlineStr">
-        <is>
-          <t>SRC_US_NNDSS</t>
-        </is>
-      </c>
-      <c r="X441" t="inlineStr">
-        <is>
-          <t>Hepatitis A, Confirmed</t>
-        </is>
-      </c>
-      <c r="Y441" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z441" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA441" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB441" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC441" t="inlineStr">
-        <is>
-          <t>country:US:national</t>
-        </is>
-      </c>
-      <c r="AD441" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE441" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF441" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG441" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH441" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI441" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ441" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK441" t="inlineStr">
-        <is>
-          <t>Confirmed hepatitis A component reported by NNDSS.</t>
-        </is>
-      </c>
-      <c r="AM441" t="inlineStr">
-        <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="AN441" t="b">
-        <v>1</v>
       </c>
       <c r="AO441" t="inlineStr">
         <is>
@@ -82776,17 +82684,17 @@
       </c>
       <c r="E442" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F442" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G442" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H442" t="inlineStr">
@@ -82811,7 +82719,7 @@
       </c>
       <c r="L442" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="M442" t="inlineStr">
@@ -82820,81 +82728,173 @@
         </is>
       </c>
       <c r="N442" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="O442" t="n">
-        <v>19</v>
-      </c>
-      <c r="R442" t="n">
-        <v>0.01551935974374956</v>
-      </c>
-      <c r="S442" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>6</v>
+      </c>
+      <c r="P442" t="n">
+        <v>6</v>
+      </c>
+      <c r="U442" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="V442" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="W442" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X442" t="inlineStr">
+        <is>
+          <t>Hepatitis A, Confirmed</t>
+        </is>
+      </c>
+      <c r="Y442" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z442" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA442" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB442" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC442" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD442" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE442" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF442" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG442" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH442" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI442" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ442" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK442" t="inlineStr">
+        <is>
+          <t>Confirmed hepatitis A component reported by NNDSS.</t>
+        </is>
+      </c>
+      <c r="AM442" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN442" t="b">
+        <v>1</v>
       </c>
       <c r="AO442" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP442" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR442" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS442" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ442" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS442" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
       <c r="AT442" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU442" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV442" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW442" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX442" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY442" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ442" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA442" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB442" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC442" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -82926,12 +82926,12 @@
       </c>
       <c r="F443" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G443" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H443" t="inlineStr">
@@ -82965,93 +82965,81 @@
         </is>
       </c>
       <c r="N443" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="O443" t="n">
-        <v>2</v>
-      </c>
-      <c r="P443" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="R443" t="n">
-        <v>0.03386531510194095</v>
+        <v>0.01551935974374956</v>
       </c>
       <c r="S443" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA443" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO443" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP443" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ443" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS443" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_A</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR443" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS443" t="inlineStr"/>
       <c r="AT443" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU443" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV443" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW443" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX443" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY443" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ443" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA443" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB443" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC443" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -83078,7 +83066,7 @@
       </c>
       <c r="E444" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F444" t="inlineStr">
@@ -83130,98 +83118,18 @@
       <c r="P444" t="n">
         <v>2</v>
       </c>
-      <c r="U444" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A</t>
-        </is>
-      </c>
-      <c r="V444" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A</t>
-        </is>
-      </c>
-      <c r="W444" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X444" t="inlineStr">
-        <is>
-          <t>Acute Viral Hepatitis A</t>
-        </is>
-      </c>
-      <c r="Y444" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z444" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R444" t="n">
+        <v>0.03386531510194095</v>
+      </c>
+      <c r="S444" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA444" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB444" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC444" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD444" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE444" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF444" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG444" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH444" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI444" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ444" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK444" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM444" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN444" t="b">
-        <v>1</v>
       </c>
       <c r="AO444" t="inlineStr">
         <is>
@@ -83315,17 +83223,17 @@
       </c>
       <c r="E445" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F445" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G445" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H445" t="inlineStr">
@@ -83350,90 +83258,182 @@
       </c>
       <c r="L445" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M445" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N445" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O445" t="n">
-        <v>0</v>
-      </c>
-      <c r="R445" t="n">
-        <v>0</v>
-      </c>
-      <c r="S445" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="P445" t="n">
+        <v>2</v>
+      </c>
+      <c r="U445" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A</t>
+        </is>
+      </c>
+      <c r="V445" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A</t>
+        </is>
+      </c>
+      <c r="W445" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X445" t="inlineStr">
+        <is>
+          <t>Acute Viral Hepatitis A</t>
+        </is>
+      </c>
+      <c r="Y445" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z445" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA445" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB445" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC445" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD445" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE445" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF445" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG445" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH445" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI445" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ445" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK445" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM445" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN445" t="b">
+        <v>1</v>
       </c>
       <c r="AO445" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP445" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR445" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS445" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ445" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS445" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_A</t>
+        </is>
+      </c>
       <c r="AT445" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU445" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV445" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW445" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX445" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY445" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ445" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA445" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB445" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC445" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -83465,12 +83465,12 @@
       </c>
       <c r="F446" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G446" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H446" t="inlineStr">
@@ -83504,100 +83504,81 @@
         </is>
       </c>
       <c r="N446" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O446" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R446" t="n">
-        <v>0.08894045854320688</v>
+        <v>0</v>
       </c>
       <c r="S446" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U446" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_115</t>
-        </is>
-      </c>
-      <c r="AA446" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO446" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP446" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ446" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR446" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS446" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_115</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS446" t="inlineStr"/>
       <c r="AT446" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU446" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV446" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW446" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX446" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY446" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ446" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA446" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB446" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC446" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -83624,7 +83605,7 @@
       </c>
       <c r="E447" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F447" t="inlineStr">
@@ -83673,98 +83654,23 @@
       <c r="O447" t="n">
         <v>5</v>
       </c>
+      <c r="R447" t="n">
+        <v>0.08894045854320688</v>
+      </c>
+      <c r="S447" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U447" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_115</t>
         </is>
       </c>
-      <c r="V447" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_115</t>
-        </is>
-      </c>
-      <c r="W447" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X447" t="inlineStr">
-        <is>
-          <t>Hepatitis A</t>
-        </is>
-      </c>
-      <c r="Y447" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z447" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA447" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB447" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC447" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD447" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE447" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF447" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG447" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH447" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI447" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ447" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK447" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 115.</t>
-        </is>
-      </c>
-      <c r="AM447" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN447" t="b">
-        <v>1</v>
       </c>
       <c r="AO447" t="inlineStr">
         <is>
@@ -83863,17 +83769,17 @@
       </c>
       <c r="E448" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F448" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G448" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H448" t="inlineStr">
@@ -83907,81 +83813,175 @@
         </is>
       </c>
       <c r="N448" t="n">
-        <v>73</v>
+        <v>5</v>
       </c>
       <c r="O448" t="n">
-        <v>73</v>
-      </c>
-      <c r="R448" t="n">
-        <v>0.1414718044368194</v>
-      </c>
-      <c r="S448" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>5</v>
+      </c>
+      <c r="U448" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_115</t>
+        </is>
+      </c>
+      <c r="V448" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_115</t>
+        </is>
+      </c>
+      <c r="W448" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X448" t="inlineStr">
+        <is>
+          <t>Hepatitis A</t>
+        </is>
+      </c>
+      <c r="Y448" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z448" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA448" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB448" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC448" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD448" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE448" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF448" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG448" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH448" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI448" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ448" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK448" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 115.</t>
+        </is>
+      </c>
+      <c r="AM448" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN448" t="b">
+        <v>1</v>
       </c>
       <c r="AO448" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP448" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ448" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR448" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS448" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS448" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_115</t>
+        </is>
+      </c>
       <c r="AT448" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU448" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV448" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW448" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX448" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY448" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ448" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA448" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB448" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC448" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -84013,12 +84013,12 @@
       </c>
       <c r="F449" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G449" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H449" t="inlineStr">
@@ -84052,100 +84052,81 @@
         </is>
       </c>
       <c r="N449" t="n">
-        <v>9</v>
+        <v>91</v>
       </c>
       <c r="O449" t="n">
-        <v>9</v>
+        <v>91</v>
       </c>
       <c r="R449" t="n">
-        <v>0.1592078243215956</v>
+        <v>0.1763552630650762</v>
       </c>
       <c r="S449" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U449" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_201_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA449" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO449" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP449" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ449" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR449" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS449" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_201_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS449" t="inlineStr"/>
       <c r="AT449" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU449" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV449" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW449" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX449" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY449" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ449" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA449" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB449" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC449" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -84172,7 +84153,7 @@
       </c>
       <c r="E450" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F450" t="inlineStr">
@@ -84216,103 +84197,28 @@
         </is>
       </c>
       <c r="N450" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="O450" t="n">
-        <v>9</v>
+        <v>11</v>
+      </c>
+      <c r="R450" t="n">
+        <v>0.1945873408375057</v>
+      </c>
+      <c r="S450" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U450" t="inlineStr">
         <is>
           <t>SER_NO_FHI_201_MONTHLY</t>
         </is>
       </c>
-      <c r="V450" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_201_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W450" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X450" t="inlineStr">
-        <is>
-          <t>Hepatitt A</t>
-        </is>
-      </c>
-      <c r="Y450" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z450" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA450" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB450" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC450" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD450" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE450" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF450" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG450" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH450" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI450" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ450" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK450" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM450" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN450" t="b">
-        <v>1</v>
       </c>
       <c r="AO450" t="inlineStr">
         <is>
@@ -84411,17 +84317,17 @@
       </c>
       <c r="E451" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F451" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G451" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H451" t="inlineStr">
@@ -84446,7 +84352,7 @@
       </c>
       <c r="L451" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M451" t="inlineStr">
@@ -84455,98 +84361,175 @@
         </is>
       </c>
       <c r="N451" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="O451" t="n">
-        <v>7</v>
-      </c>
-      <c r="P451" t="n">
-        <v>7</v>
-      </c>
-      <c r="R451" t="n">
-        <v>0.00200552669293857</v>
-      </c>
-      <c r="S451" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>11</v>
       </c>
       <c r="U451" t="inlineStr">
         <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+          <t>SER_NO_FHI_201_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V451" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_201_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W451" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X451" t="inlineStr">
+        <is>
+          <t>Hepatitt A</t>
+        </is>
+      </c>
+      <c r="Y451" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z451" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA451" t="inlineStr">
         <is>
-          <t>weekly</t>
-        </is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB451" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC451" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD451" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE451" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF451" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG451" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH451" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI451" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ451" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK451" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM451" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN451" t="b">
+        <v>1</v>
       </c>
       <c r="AO451" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP451" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ451" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR451" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS451" t="inlineStr">
         <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+          <t>SER_NO_FHI_201_MONTHLY</t>
         </is>
       </c>
       <c r="AT451" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU451" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV451" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW451" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX451" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY451" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ451" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA451" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB451" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC451" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -84573,7 +84556,7 @@
       </c>
       <c r="E452" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F452" t="inlineStr">
@@ -84625,98 +84608,23 @@
       <c r="P452" t="n">
         <v>7</v>
       </c>
+      <c r="R452" t="n">
+        <v>0.00200552669293857</v>
+      </c>
+      <c r="S452" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U452" t="inlineStr">
         <is>
           <t>SER_US_HEPATITIS_A_CONFIRMED</t>
         </is>
       </c>
-      <c r="V452" t="inlineStr">
-        <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
-        </is>
-      </c>
-      <c r="W452" t="inlineStr">
-        <is>
-          <t>SRC_US_NNDSS</t>
-        </is>
-      </c>
-      <c r="X452" t="inlineStr">
-        <is>
-          <t>Hepatitis A, Confirmed</t>
-        </is>
-      </c>
-      <c r="Y452" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z452" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA452" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB452" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC452" t="inlineStr">
-        <is>
-          <t>country:US:national</t>
-        </is>
-      </c>
-      <c r="AD452" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE452" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF452" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG452" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH452" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI452" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ452" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK452" t="inlineStr">
-        <is>
-          <t>Confirmed hepatitis A component reported by NNDSS.</t>
-        </is>
-      </c>
-      <c r="AM452" t="inlineStr">
-        <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="AN452" t="b">
-        <v>1</v>
       </c>
       <c r="AO452" t="inlineStr">
         <is>
@@ -84810,17 +84718,17 @@
       </c>
       <c r="E453" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F453" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G453" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H453" t="inlineStr">
@@ -84845,7 +84753,7 @@
       </c>
       <c r="L453" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="M453" t="inlineStr">
@@ -84854,81 +84762,173 @@
         </is>
       </c>
       <c r="N453" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="O453" t="n">
-        <v>10</v>
-      </c>
-      <c r="R453" t="n">
-        <v>0.008168084075657663</v>
-      </c>
-      <c r="S453" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>7</v>
+      </c>
+      <c r="P453" t="n">
+        <v>7</v>
+      </c>
+      <c r="U453" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="V453" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="W453" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X453" t="inlineStr">
+        <is>
+          <t>Hepatitis A, Confirmed</t>
+        </is>
+      </c>
+      <c r="Y453" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z453" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA453" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB453" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC453" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD453" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE453" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF453" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG453" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH453" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI453" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ453" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK453" t="inlineStr">
+        <is>
+          <t>Confirmed hepatitis A component reported by NNDSS.</t>
+        </is>
+      </c>
+      <c r="AM453" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN453" t="b">
+        <v>1</v>
       </c>
       <c r="AO453" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP453" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR453" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS453" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ453" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS453" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
       <c r="AT453" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU453" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV453" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW453" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX453" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY453" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ453" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA453" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB453" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC453" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -84960,12 +84960,12 @@
       </c>
       <c r="F454" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G454" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H454" t="inlineStr">
@@ -84999,93 +84999,81 @@
         </is>
       </c>
       <c r="N454" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="O454" t="n">
-        <v>1</v>
-      </c>
-      <c r="P454" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="R454" t="n">
-        <v>0.01693265755097047</v>
+        <v>0.008168084075657663</v>
       </c>
       <c r="S454" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA454" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO454" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP454" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ454" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS454" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_A</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR454" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS454" t="inlineStr"/>
       <c r="AT454" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU454" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV454" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW454" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX454" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY454" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ454" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA454" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB454" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC454" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -85112,7 +85100,7 @@
       </c>
       <c r="E455" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F455" t="inlineStr">
@@ -85164,98 +85152,18 @@
       <c r="P455" t="n">
         <v>1</v>
       </c>
-      <c r="U455" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A</t>
-        </is>
-      </c>
-      <c r="V455" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A</t>
-        </is>
-      </c>
-      <c r="W455" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X455" t="inlineStr">
-        <is>
-          <t>Acute Viral Hepatitis A</t>
-        </is>
-      </c>
-      <c r="Y455" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z455" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R455" t="n">
+        <v>0.01693265755097047</v>
+      </c>
+      <c r="S455" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA455" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB455" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC455" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD455" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE455" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF455" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG455" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH455" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI455" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ455" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK455" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM455" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN455" t="b">
-        <v>1</v>
       </c>
       <c r="AO455" t="inlineStr">
         <is>
@@ -85349,17 +85257,17 @@
       </c>
       <c r="E456" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F456" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G456" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H456" t="inlineStr">
@@ -85384,7 +85292,7 @@
       </c>
       <c r="L456" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="M456" t="inlineStr">
@@ -85393,25 +85301,42 @@
         </is>
       </c>
       <c r="N456" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="O456" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="P456" t="n">
-        <v>9</v>
-      </c>
-      <c r="R456" t="n">
-        <v>0.002578534319492447</v>
-      </c>
-      <c r="S456" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="U456" t="inlineStr">
         <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A</t>
+        </is>
+      </c>
+      <c r="V456" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A</t>
+        </is>
+      </c>
+      <c r="W456" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X456" t="inlineStr">
+        <is>
+          <t>Acute Viral Hepatitis A</t>
+        </is>
+      </c>
+      <c r="Y456" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z456" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA456" t="inlineStr">
@@ -85419,72 +85344,130 @@
           <t>weekly</t>
         </is>
       </c>
+      <c r="AB456" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC456" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD456" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE456" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF456" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG456" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH456" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI456" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ456" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK456" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM456" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN456" t="b">
+        <v>1</v>
+      </c>
       <c r="AO456" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP456" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ456" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS456" t="inlineStr">
         <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_A</t>
         </is>
       </c>
       <c r="AT456" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU456" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV456" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW456" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX456" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY456" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ456" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA456" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB456" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC456" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -85511,7 +85494,7 @@
       </c>
       <c r="E457" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F457" t="inlineStr">
@@ -85563,98 +85546,23 @@
       <c r="P457" t="n">
         <v>9</v>
       </c>
+      <c r="R457" t="n">
+        <v>0.002578534319492447</v>
+      </c>
+      <c r="S457" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U457" t="inlineStr">
         <is>
           <t>SER_US_HEPATITIS_A_CONFIRMED</t>
         </is>
       </c>
-      <c r="V457" t="inlineStr">
-        <is>
-          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
-        </is>
-      </c>
-      <c r="W457" t="inlineStr">
-        <is>
-          <t>SRC_US_NNDSS</t>
-        </is>
-      </c>
-      <c r="X457" t="inlineStr">
-        <is>
-          <t>Hepatitis A, Confirmed</t>
-        </is>
-      </c>
-      <c r="Y457" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z457" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA457" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB457" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC457" t="inlineStr">
-        <is>
-          <t>country:US:national</t>
-        </is>
-      </c>
-      <c r="AD457" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE457" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF457" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG457" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH457" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI457" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ457" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
-        </is>
-      </c>
-      <c r="AK457" t="inlineStr">
-        <is>
-          <t>Confirmed hepatitis A component reported by NNDSS.</t>
-        </is>
-      </c>
-      <c r="AM457" t="inlineStr">
-        <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="AN457" t="b">
-        <v>1</v>
       </c>
       <c r="AO457" t="inlineStr">
         <is>
@@ -85720,6 +85628,1181 @@
         </is>
       </c>
       <c r="BC457" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>D007</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>hepatitis-a</t>
+        </is>
+      </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>Hepatitis A</t>
+        </is>
+      </c>
+      <c r="E458" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F458" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G458" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H458" t="inlineStr">
+        <is>
+          <t>D007</t>
+        </is>
+      </c>
+      <c r="I458" t="inlineStr">
+        <is>
+          <t>Hepatitis A</t>
+        </is>
+      </c>
+      <c r="J458" t="inlineStr">
+        <is>
+          <t>甲型肝炎</t>
+        </is>
+      </c>
+      <c r="K458" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L458" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="M458" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N458" t="n">
+        <v>9</v>
+      </c>
+      <c r="O458" t="n">
+        <v>9</v>
+      </c>
+      <c r="P458" t="n">
+        <v>9</v>
+      </c>
+      <c r="U458" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="V458" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="W458" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X458" t="inlineStr">
+        <is>
+          <t>Hepatitis A, Confirmed</t>
+        </is>
+      </c>
+      <c r="Y458" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z458" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA458" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB458" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC458" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD458" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE458" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF458" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG458" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH458" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI458" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ458" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK458" t="inlineStr">
+        <is>
+          <t>Confirmed hepatitis A component reported by NNDSS.</t>
+        </is>
+      </c>
+      <c r="AM458" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN458" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO458" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP458" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ458" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS458" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AT458" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU458" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV458" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW458" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX458" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY458" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ458" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA458" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB458" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC458" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>D007</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>hepatitis-a</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>Hepatitis A</t>
+        </is>
+      </c>
+      <c r="E459" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F459" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G459" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H459" t="inlineStr">
+        <is>
+          <t>D007</t>
+        </is>
+      </c>
+      <c r="I459" t="inlineStr">
+        <is>
+          <t>Hepatitis A</t>
+        </is>
+      </c>
+      <c r="J459" t="inlineStr">
+        <is>
+          <t>甲型肝炎</t>
+        </is>
+      </c>
+      <c r="K459" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L459" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M459" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N459" t="n">
+        <v>7</v>
+      </c>
+      <c r="O459" t="n">
+        <v>7</v>
+      </c>
+      <c r="R459" t="n">
+        <v>0.005717658852960364</v>
+      </c>
+      <c r="S459" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO459" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP459" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR459" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS459" t="inlineStr"/>
+      <c r="AT459" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU459" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV459" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW459" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX459" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY459" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ459" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA459" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB459" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC459" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>D007</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>hepatitis-a</t>
+        </is>
+      </c>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>Hepatitis A</t>
+        </is>
+      </c>
+      <c r="E460" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F460" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G460" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H460" t="inlineStr">
+        <is>
+          <t>D007</t>
+        </is>
+      </c>
+      <c r="I460" t="inlineStr">
+        <is>
+          <t>Hepatitis A</t>
+        </is>
+      </c>
+      <c r="J460" t="inlineStr">
+        <is>
+          <t>甲型肝炎</t>
+        </is>
+      </c>
+      <c r="K460" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L460" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M460" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N460" t="n">
+        <v>1</v>
+      </c>
+      <c r="O460" t="n">
+        <v>1</v>
+      </c>
+      <c r="P460" t="n">
+        <v>1</v>
+      </c>
+      <c r="R460" t="n">
+        <v>0.01693265755097047</v>
+      </c>
+      <c r="S460" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA460" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO460" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP460" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ460" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS460" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_A</t>
+        </is>
+      </c>
+      <c r="AT460" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU460" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV460" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW460" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX460" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY460" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ460" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA460" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB460" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC460" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>D007</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>hepatitis-a</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>Hepatitis A</t>
+        </is>
+      </c>
+      <c r="E461" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F461" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G461" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H461" t="inlineStr">
+        <is>
+          <t>D007</t>
+        </is>
+      </c>
+      <c r="I461" t="inlineStr">
+        <is>
+          <t>Hepatitis A</t>
+        </is>
+      </c>
+      <c r="J461" t="inlineStr">
+        <is>
+          <t>甲型肝炎</t>
+        </is>
+      </c>
+      <c r="K461" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L461" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M461" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N461" t="n">
+        <v>1</v>
+      </c>
+      <c r="O461" t="n">
+        <v>1</v>
+      </c>
+      <c r="P461" t="n">
+        <v>1</v>
+      </c>
+      <c r="U461" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A</t>
+        </is>
+      </c>
+      <c r="V461" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A</t>
+        </is>
+      </c>
+      <c r="W461" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X461" t="inlineStr">
+        <is>
+          <t>Acute Viral Hepatitis A</t>
+        </is>
+      </c>
+      <c r="Y461" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z461" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA461" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB461" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC461" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD461" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE461" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF461" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG461" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH461" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI461" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ461" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK461" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM461" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN461" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO461" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP461" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ461" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS461" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_A; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_A</t>
+        </is>
+      </c>
+      <c r="AT461" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU461" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV461" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW461" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX461" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY461" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ461" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA461" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB461" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC461" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>D007</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>hepatitis-a</t>
+        </is>
+      </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>Hepatitis A</t>
+        </is>
+      </c>
+      <c r="E462" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F462" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G462" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H462" t="inlineStr">
+        <is>
+          <t>D007</t>
+        </is>
+      </c>
+      <c r="I462" t="inlineStr">
+        <is>
+          <t>Hepatitis A</t>
+        </is>
+      </c>
+      <c r="J462" t="inlineStr">
+        <is>
+          <t>甲型肝炎</t>
+        </is>
+      </c>
+      <c r="K462" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L462" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="M462" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N462" t="n">
+        <v>4</v>
+      </c>
+      <c r="O462" t="n">
+        <v>4</v>
+      </c>
+      <c r="P462" t="n">
+        <v>4</v>
+      </c>
+      <c r="R462" t="n">
+        <v>0.001146015253107754</v>
+      </c>
+      <c r="S462" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U462" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AA462" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO462" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP462" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ462" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS462" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AT462" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU462" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV462" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW462" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX462" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY462" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ462" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA462" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB462" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC462" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>D007</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>hepatitis-a</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>Hepatitis A</t>
+        </is>
+      </c>
+      <c r="E463" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F463" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G463" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H463" t="inlineStr">
+        <is>
+          <t>D007</t>
+        </is>
+      </c>
+      <c r="I463" t="inlineStr">
+        <is>
+          <t>Hepatitis A</t>
+        </is>
+      </c>
+      <c r="J463" t="inlineStr">
+        <is>
+          <t>甲型肝炎</t>
+        </is>
+      </c>
+      <c r="K463" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L463" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="M463" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N463" t="n">
+        <v>4</v>
+      </c>
+      <c r="O463" t="n">
+        <v>4</v>
+      </c>
+      <c r="P463" t="n">
+        <v>4</v>
+      </c>
+      <c r="U463" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="V463" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="W463" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X463" t="inlineStr">
+        <is>
+          <t>Hepatitis A, Confirmed</t>
+        </is>
+      </c>
+      <c r="Y463" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z463" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA463" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB463" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC463" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD463" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE463" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF463" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG463" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH463" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI463" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ463" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK463" t="inlineStr">
+        <is>
+          <t>Confirmed hepatitis A component reported by NNDSS.</t>
+        </is>
+      </c>
+      <c r="AM463" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN463" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO463" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP463" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ463" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS463" t="inlineStr">
+        <is>
+          <t>SER_US_HEPATITIS_A_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AT463" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU463" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV463" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW463" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX463" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY463" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ463" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA463" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB463" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC463" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -85758,7 +86841,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
@@ -85841,7 +86924,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>274</v>
+        <v>278</v>
       </c>
     </row>
     <row r="10">
@@ -85851,7 +86934,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>456</v>
+        <v>462</v>
       </c>
     </row>
     <row r="11">
@@ -85871,7 +86954,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="13">
@@ -85903,7 +86986,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>19170</v>
+        <v>19207</v>
       </c>
     </row>
     <row r="16">
